--- a/HealthReport.xlsx
+++ b/HealthReport.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122FB675-342F-4F3A-92E5-16E32B897BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A2E3E6-3789-4C59-8771-72EEAB5F5E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HealthReport" sheetId="1" r:id="rId1"/>
     <sheet name="OS" sheetId="5" r:id="rId2"/>
     <sheet name="DB" sheetId="6" r:id="rId3"/>
+    <sheet name="INST" sheetId="7" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="ChecklistTotal">SUM(#REF!)</definedName>
@@ -32,7 +33,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -358,7 +358,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="238">
   <si>
     <r>
       <rPr>
@@ -385,1179 +385,856 @@
     <t>主机名</t>
   </si>
   <si>
+    <t>内存</t>
+  </si>
+  <si>
+    <t>APC2DB</t>
+  </si>
+  <si>
+    <t>数据库版本</t>
+  </si>
+  <si>
+    <t>数据库架构</t>
+  </si>
+  <si>
+    <t>SINGLE INSTANCE</t>
+  </si>
+  <si>
+    <t>主备库角色</t>
+  </si>
+  <si>
+    <t>ARCHIVELOG</t>
+  </si>
+  <si>
+    <t>1513.200  GB</t>
+  </si>
+  <si>
+    <t>数据库字符集</t>
+  </si>
+  <si>
+    <t>AMERICAN_AMERICA.US7ASCII</t>
+  </si>
+  <si>
+    <t>数据库名</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRIMARY,MAXIMUM PERFORMANCE</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Issue summary</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库集群检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库实例分析</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库备份检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库安全检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件使用分析</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他项检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>重要</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻微</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机系统分析</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Issue list</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>No.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题描述及建议</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题类别</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机系统分析</t>
+  </si>
+  <si>
+    <t>数据库实例分析</t>
+  </si>
+  <si>
+    <t>其他项检查</t>
+  </si>
+  <si>
+    <t>数据库安全检查</t>
+  </si>
+  <si>
+    <t>数据库备份检查</t>
+  </si>
+  <si>
+    <t>检查项</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataGuard检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>内存使用检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件系统使用率</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引资源节点使用率</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机透明大页检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>内核参数</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源限制</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库状态检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>表空间使用率</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>影响</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU负载检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘IO负载检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMA使用检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">       Health  Report</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机名</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>内存使用</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
     <t>IP地址</t>
-  </si>
-  <si>
-    <t>系统平台</t>
-  </si>
-  <si>
-    <t>操作系统补丁</t>
-  </si>
-  <si>
-    <t>dcs0tdb6</t>
-  </si>
-  <si>
-    <t>10.224.209.155</t>
-  </si>
-  <si>
-    <t>Solaris[tm] OE (64-bit)</t>
-  </si>
-  <si>
-    <t>SunOS. Oracle Solaris 11.4 SPARC</t>
-  </si>
-  <si>
-    <t>CPU核数</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>CPU频率</t>
-  </si>
-  <si>
-    <t>2800</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统日志</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库架构</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统版本</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>内存</t>
-  </si>
-  <si>
-    <t>260352 Megabytes</t>
-  </si>
-  <si>
-    <t>APC2DB</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>交换分区</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>ULIMIT限制</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引资源使用率</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>透明大页</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘IO负载</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统大页</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMA使用</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>时钟同步</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>时区</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库名称</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库日志检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪回区使用</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群状态</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASM使用率</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>并行度&gt;1的表</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>DBA权限用户检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYSDBA权限用户检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库审计空间检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库审计对象检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCNHealthCheck检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>并行度&gt;1的索引</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>数据库版本</t>
-  </si>
-  <si>
-    <t>数据库架构</t>
-  </si>
-  <si>
-    <t>SINGLE INSTANCE</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否开启归档</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否开启闪回</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据文件数量</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>表数量</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>主备库角色</t>
-  </si>
-  <si>
-    <t>是否开启归档</t>
-  </si>
-  <si>
-    <t>ARCHIVELOG</t>
-  </si>
-  <si>
-    <t>数据库总大小GB</t>
-  </si>
-  <si>
-    <t>1513.200  GB</t>
-  </si>
-  <si>
-    <t>数据库表数量</t>
-  </si>
-  <si>
-    <t>3072.000  GB</t>
-  </si>
-  <si>
-    <t>数据库字符集</t>
-  </si>
-  <si>
-    <t>AMERICAN_AMERICA.US7ASCII</t>
-  </si>
-  <si>
-    <t>数据库名</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Oracle Database 19c Enterprise</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRIMARY,MAXIMUM PERFORMANCE</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Issue summary</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库集群检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库实例分析</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库备份检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库安全检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>软件使用分析</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他项检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>重要</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>轻微</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机系统分析</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Health  Report</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Issue list</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>No.</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题描述及建议</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题类别</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机系统分析</t>
-  </si>
-  <si>
-    <t>数据库实例分析</t>
-  </si>
-  <si>
-    <t>其他项检查</t>
-  </si>
-  <si>
-    <t>数据库安全检查</t>
-  </si>
-  <si>
-    <t>数据库备份检查</t>
-  </si>
-  <si>
-    <t>检查项</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>DataGuard检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>结果</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>内存使用检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>文件系统使用率</t>
-  </si>
-  <si>
-    <t>文件系统使用率</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>索引资源节点使用率</t>
-  </si>
-  <si>
-    <t>索引资源节点使用率</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机透明大页检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>内核参数</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>资源限制</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>NUMA使用检查</t>
-  </si>
-  <si>
-    <t>数据库状态检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>表空间使用率</t>
-  </si>
-  <si>
-    <t>表空间使用率</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>影响</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU负载检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘IO负载检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>NUMA使用检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机内核参数</t>
-  </si>
-  <si>
-    <t>*************system parameter*************
-set noexec_user_stack=1
-set maxfastscan=0x2000
-set ssd:ssd_io_time=0x3c
-set ssd:ssd_max_throttle=32
-set shmsys:shminfo_shmmax=536870912
-set shmsys:shminfo_shmmni=256
-set semsys:seminfo_semmni=256
-set semsys:seminfo_semmsl=4096
-set msgsys:msginfo_msgmap=16384
-set msgsys:msginfo_msgmax=2097152
-set msgsys:msginfo_msgmnb=134217728
-set msgsys:msginfo_msgmni=8192
-set msgsys:msginfo_msgssz=4096
-set msgsys:msginfo_msgtql=131072
-set msgsys:msginfo_msgseg=19712
-set rlim_fd_max=100
-set rlim_fd_cur=65536
-set zfs:zfs_arc_max=53687091200
-set disable_ism_large_pages=0xF4
-set vxfs:vx_maxlink = 65534
-set lwp_default_stksize=0xa000
-set rpcmod:svc_default_stksize=0xa000
-set panic_on_oops=1
-*************network parameter (root)*************
-57344
-57344
-*************system parameter*************
-set noexec_user_stack=1
-set maxfastscan=0x2000
-set ssd:ssd_io_time=0x3c
-set ssd:ssd_max_throttle=32
-set shmsys:shminfo_shmmax=536870912
-set shmsys:shminfo_shmmni=256
-set semsys:seminfo_semmni=256
-set semsys:seminfo_semmsl=4096
-set msgsys:msginfo_msgmap=16384
-set msgsys:msginfo_msgmax=2097152
-set msgsys:msginfo_msgmnb=134217728
-set msgsys:msginfo_msgmni=8192
-set msgsys:msginfo_msgssz=4096
-set msgsys:msginfo_msgtql=131072
-set msgsys:msginfo_msgseg=19712
-set rlim_fd_max=65536
-set rlim_fd_cur=65536
-set zfs:zfs_arc_max=53687091200
-set disable_ism_large_pages=0xF1
-set vxfs:vx_maxlink = 65534
-set lwp_default_stksize=0xa000
-set rpcmod:svc_default_stksize=0xa000
-*************network parameter (root)*************
-57344
-57344</t>
-  </si>
-  <si>
-    <t>主机资源限制</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>CPU负载</t>
-  </si>
-  <si>
-    <t>内存使用</t>
-  </si>
-  <si>
-    <t>磁盘IO负载检查</t>
-  </si>
-  <si>
-    <t>透明大页开启检查</t>
-  </si>
-  <si>
-    <t>[always] state never</t>
-  </si>
-  <si>
-    <t>主机大页使用检查</t>
-  </si>
-  <si>
-    <t>NUMA turned off</t>
-  </si>
-  <si>
-    <t>NTP时钟同步检查</t>
-  </si>
-  <si>
-    <t>数据库名称
-DB_UNIQUE_NAME</t>
-  </si>
-  <si>
-    <t>TABLESPACE_NAME             MAXEXTEND(GB)        AllOCATED(GB)             USED(GB)         USED_RATE(%)
--------------------- -------------------- -------------------- -------------------- --------------------
-APF_TBS                             6.060                 .548                 .509                8.400
-APF_TBS_BK                          6.060                 .196                 .034                 .560
-AUDIT_TS                            6.350                1.661                1.540               24.260
-N_USERS                            12.110                3.615                3.443               28.430
-CIM_LOB_DTS                        12.110                7.131               11.760               95.820
-N_CIM_128K_DTS                     12.110               11.135               10.304               85.090
-N_EAPDEV                           12.110                8.498                8.007               66.120
-N_RLTDEV                           12.110                2.834                2.686               22.180
-N_MCRDEV                           12.110                 .197                 .000                 .000
-N_CIM_100M_ITS                     12.110                3.322                3.029               25.010
-N_CIM_128K_ITS                     12.110                7.326                3.364               27.780
-MCS_8M_DTS                         24.220                 .785                 .231                 .950
-SYSAUX                             29.310                4.287                2.033                6.940
-USERS                              32.000                 .164                 .155                 .480
-SYSTEM                             32.000                 .820                 .810                2.530
-UNDOTBS1                           32.000               24.067                1.597                4.990
-N_CIM_1M_DTS                       42.240               35.212               34.155               80.860
-N_APCDEV                           54.360               50.843               48.558               89.330
-N_CIM_8M_ITS                      102.260               88.848               86.481               84.570
-N_CIM_100M_DTS                    272.500              253.950              234.614               86.100
-N_CIM_20M_ITS                     354.260              283.651              262.401               74.070
-N_CIM_8M_DTS                      383.170              353.876              328.532               85.740
-N_CIM_1M_ITS                      415.350              368.183              336.640               81.050</t>
-  </si>
-  <si>
-    <t>数据文件大小检查</t>
-  </si>
-  <si>
-    <t>FILE_NAME                                                              STATUS                   CUR_GB AUT               MAX_GB
----------------------------------------------------------------------- ---------- -------------------- --- --------------------
-/apc2db_db/db_11g/APF_TBS01.dbf                                        AVAILABLE                  .550 YES                6.060
-/apc2db_db/db_11g/APF_TBS_BK01.dbf                                     AVAILABLE                  .200 YES                6.060
-/apc2db_db/db_11g/AUDIT_TS_01.dbf                                      AVAILABLE                 1.660 YES                6.350
-/apc2db_db/db_11g/CIM_LOB_DTS_01.dbf                                   AVAILABLE                 3.910 YES                6.060
-/apc2db_db/db_11g/CIM_LOB_DTS_02.dbf                                   AVAILABLE                 3.220 YES                6.060
-/apc2db_db/db_11g/MCS_8M_DTS_01.dbf                                    AVAILABLE                  .200 YES                6.060
-/apc2db_db/db_11g/MCS_8M_DTS_02.dbf                                    AVAILABLE                  .200 YES                6.060
-/apc2db_db/db_11g/MCS_8M_DTS_03.dbf                                    AVAILABLE                  .200 YES                6.060
-/apc2db_db/db_11g/MCS_8M_DTS_04.dbf                                    AVAILABLE                  .200 YES                6.060
-/apc2db_db/db_11g/N_APCDEV01.dbf                                       AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_APCDEV02.dbf                                       AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_APCDEV03.dbf                                       AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_APCDEV04.dbf                                       AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_APCDEV05.dbf                                       AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_APCDEV06.dbf                                       AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_APCDEV07.dbf                                       AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_APCDEV08.dbf                                       AVAILABLE                 5.810 YES                5.910
-/apc2db_db/db_11g/N_APCDEV09.dbf                                       AVAILABLE                 2.640 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_01.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_02.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_03.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_04.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_05.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_06.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_07.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_08.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_09.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_10.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_11.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_12.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_13.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_14.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_15.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_16.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_17.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_18.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_19.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_20.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_21.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_22.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_23.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_24.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_25.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_26.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_27.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_28.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_29.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_30.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_31.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_32.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_33.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_34.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_35.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_36.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_37.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_38.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_39.dbf                                AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_40.dbf                                AVAILABLE                 4.590 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_41.dbf                                AVAILABLE                 4.590 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_42.dbf                                AVAILABLE                 2.930 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_43.dbf                                AVAILABLE                 2.930 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_44.dbf                                AVAILABLE                 1.370 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_DTS_45.dbf                                AVAILABLE                 1.370 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_ITS_01.dbf                                AVAILABLE                 2.540 YES                6.060
-/apc2db_db/db_11g/N_CIM_100M_ITS_02.dbf                                AVAILABLE                  .780 YES                6.060
-/apc2db_db/db_11g/N_CIM_128K_DTS_01.dbf                                AVAILABLE                 5.760 YES                6.060
-/apc2db_db/db_11g/N_CIM_128K_DTS_02.dbf                                AVAILABLE                 5.370 YES                6.060
-/apc2db_db/db_11g/N_CIM_128K_ITS_01.dbf                                AVAILABLE                 3.810 YES                6.060
-/apc2db_db/db_11g/N_CIM_128K_ITS_02.dbf                                AVAILABLE                 3.520 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_DTS_01.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_DTS_02.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_DTS_03.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_DTS_04.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_DTS_05.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_DTS_06.dbf                                  AVAILABLE                 4.490 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_DTS_07.dbf                                  AVAILABLE                  .590 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_01.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_02.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_03.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_04.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_05.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_06.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_07.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_08.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_09.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_10.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_11.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_12.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_13.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_14.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_15.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_16.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_17.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_18.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_19.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_20.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_21.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_22.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_23.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_24.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_25.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_26.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_27.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_28.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_29.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_30.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_31.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_32.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_33.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_34.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_35.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_36.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_37.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_38.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_39.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_40.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_41.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_42.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_43.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_44.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_45.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_46.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_47.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_48.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_49.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_50.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_51.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_52.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_53.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_54.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_55.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_56.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_57.dbf                                  AVAILABLE                 5.420 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_58.dbf                                  AVAILABLE                 5.420 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_59.dbf                                  AVAILABLE                 3.570 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_60.dbf                                  AVAILABLE                 3.470 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_61.dbf                                  AVAILABLE                 1.320 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_62.dbf                                  AVAILABLE                 1.320 YES                5.910
-/apc2db_db/db_11g/N_CIM_1M_ITS_63.dbf                                  AVAILABLE                 1.470 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_64.dbf                                  AVAILABLE                 1.470 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_65.dbf                                  AVAILABLE                 1.470 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_66.dbf                                  AVAILABLE                 1.470 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_67.dbf                                  AVAILABLE                 1.470 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_68.dbf                                  AVAILABLE                 1.470 YES                6.060
-/apc2db_db/db_11g/N_CIM_1M_ITS_69.dbf                                  AVAILABLE                 1.370 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_01.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_02.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_03.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_04.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_05.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_06.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_07.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_08.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_09.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_10.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_11.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_12.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_13.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_14.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_15.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_16.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_17.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_18.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_19.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_20.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_21.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_22.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_23.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_24.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_25.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_26.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_27.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_28.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_29.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_30.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_31.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_32.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_33.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_34.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_35.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_36.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_37.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_38.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_39.dbf                                 AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_40.dbf                                 AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_20M_ITS_41.dbf                                 AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_20M_ITS_42.dbf                                 AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_20M_ITS_43.dbf                                 AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_20M_ITS_44.dbf                                 AVAILABLE                 5.420 YES                5.910
-/apc2db_db/db_11g/N_CIM_20M_ITS_45.dbf                                 AVAILABLE                 5.420 YES                5.910
-/apc2db_db/db_11g/N_CIM_20M_ITS_46.dbf                                 AVAILABLE                 3.610 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_47.dbf                                 AVAILABLE                 3.610 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_48.dbf                                 AVAILABLE                 3.610 YES                6.060
-/apc2db_db/db_11g/N_CIM_20M_ITS_49.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_20M_ITS_50.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_20M_ITS_51.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_20M_ITS_52.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_20M_ITS_53.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_20M_ITS_54.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_20M_ITS_55.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_20M_ITS_56.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_20M_ITS_57.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_20M_ITS_58.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_20M_ITS_59.dbf                                 AVAILABLE                  .200 YES                5.860
-/apc2db_db/db_11g/N_CIM_8M_DTS_01.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_02.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_03.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_04.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_05.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_06.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_07.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_08.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_09.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_10.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_11.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_12.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_13.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_14.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_15.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_16.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_17.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_18.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_19.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_20.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_21.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_22.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_23.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_24.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_25.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_26.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_27.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_28.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_29.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_30.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_31.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_32.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_33.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_34.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_35.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_36.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_37.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_38.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_39.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_40.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_41.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_42.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_43.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_44.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_45.dbf                                  AVAILABLE                 6.060 YES                6.060
-/apc2db_db/db_11g/N_CIM_8M_DTS_46.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_47.dbf                                  AVAILABLE                 5.910 YES                5.910
-/apc2db_db/db_11g/N_CIM_8M_DTS_48.dbf                                  AVAILABLE                 5.960 YES                5.960
-/apc2db_db/db_11g/N_CIM_8M_DTS_49.dbf                                  AVAILABLE                 5.960 YES                5.960
-/apc2db_db/db_11g/N_CIM_8M_DTS_50.dbf                                  AVAILABLE                 5.960 YES                5.960</t>
-  </si>
-  <si>
-    <t>控制文件检查</t>
-  </si>
-  <si>
-    <t>/apc2db_db/CTL_11g/control01.ctl</t>
-  </si>
-  <si>
-    <t>数据库用户大小</t>
-  </si>
-  <si>
-    <t>OWNER                          USER_SIZE_GB
------------------------------- ------------
-APCDEV                                48.57
-APPQOSSYS                               .00
-AUDSYS                                  .00
-CIMMGR                              1309.13
-DBSFWUSER                               .00
-DBSNMP                                  .00
-EAPDEV                                  .86
-F1MCSAPP                                .01
-F2ISSUETAG                             7.08
-GSMADMIN_INTERNAL                       .01
-MCSAPP                                  .06
-MCSMGR                                  .23
-ORAAUD                                  .15
-OUTLN                                   .00
-PERFSTAT9I                              .00
-RLTDEV                                 2.69
-RTDELT                                  .03
-RTDUSER                                 .51
-SYS                                    5.89
-SYSTEM                                  .03
-VCSUSER                                 .00
-WMSYS                                   .01
-WSSAPP                                  .21
-XDB                                     .04</t>
-  </si>
-  <si>
-    <t>REDO文件性能检查</t>
-  </si>
-  <si>
-    <t>GROUP#              THREAD#            SEQUENCE#                   MB ARC STATUS
--------------------- -------------------- -------------------- -------------------- --- ----------
-               6.000                1.000              266.000              400.000 YES INACTIVE
-               7.000                1.000              267.000              400.000 YES INACTIVE
-               8.000                1.000              268.000              400.000 NO  CURRENT
-               9.000                1.000              264.000              400.000 YES INACTIVE
-              10.000                1.000              265.000              400.000 YES INACTIVE</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据文件状态检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户大小</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户状态</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户表数量</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>REDO文件检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>RMAN备份检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG同步延迟检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG同步报错检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUENCE设置检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUENCE使用检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库状态</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库组件</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能特性</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>字符集</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库参数</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>游标&gt;300M检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户临期检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>PROFILE密码函数设置</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>无效对象检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引失效检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制文件冗余检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务使用系统表空间检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recovery区使用检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误口令登录锁定检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>病毒勒索攻击隐患检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>实例名</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>监听检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库负载</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库补丁</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数文件</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>归档切换检查</t>
-  </si>
-  <si>
-    <t>DT         DY      Total  h0  h1  h2  h3  h4  h5  h6  h7  h8  h9 h10 h11 h12 h13 h14 h15 h16 h17 h18 h19 h20 h21 h22 h23
----------- ------- ----- --- --- --- --- --- --- --- --- --- --- --- --- --- --- --- --- --- --- --- --- --- --- --- ---
-2023-03-04 Sat        114  23  13  32  31  35  45  20  30  20  33  45  0   0   0   0   0   0   0   0   0   0   0
-2023-03-06 Mon         1   1   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0
-2023-03-08 Wed         1   1   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0
-2023-03-10 Fri         1   0   0   0   0   0   0   0   0   1   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0
-2023-03-12 Sun         1   0   0   0   0   0   0   1   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0
-2023-03-14 Tue         1   0   0   0   0   0   0   0   0   0   1   0   0   0   0   0   0   0   0   0   0   0   0   0   0
-2023-03-16 Thu         1   0   0   0   0   0   0   0   0   0   0   0   1   0   0   0   0   0   0   0   0   0   0   0   0
-2023-03-18 Sat         1   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   0   1   0   0   0   0   0   0   0</t>
-  </si>
-  <si>
-    <t>数据库资源使用限制检查</t>
-  </si>
-  <si>
-    <t>INST_ID RESOURCE_NAME                  CURRENT_UTILIZATION MAX_UTILIZATION LIMIT_VALUE
-------- ------------------------------ ------------------- --------------- ---------------
-      1 processes                                     2495            2499       2500
-      1 sessions                                       340             474       3776
-      1 ges_procs                                        0               0          0
-      1 ges_rsv_msgs                                     0               0          0
-      1 parallel_max_servers                             6               6      32767</t>
-  </si>
-  <si>
-    <t>数据库性能负载分析</t>
-  </si>
-  <si>
-    <t>Load Profile                    Per Second   Per Transaction  Per Exec  Per Call
-~~~~~~~~~~~~~~~            ---------------   --------------- --------- ---------
-             DB Time(s):               0.0               0.0      0.00      0.01
-              DB CPU(s):               0.0               0.0      0.00      0.00
-      Background CPU(s):               0.0               0.5      0.02      0.00
-      Redo size (bytes):      31,111,576.3          36,932.7
-  Logical read (blocks):              73.9           1,731.3
-          Block changes:               7.2             169.1
- Physical read (blocks):               0.0               0.1
-Physical write (blocks):               0.6              14.3
-       Read IO requests:               0.0               0.1
-      Write IO requests:               0.3               6.0
-           Read IO (MB):               0.0               0.0
-          Write IO (MB):               0.0               0.1
-           IM scan rows:               0.0               0.0
-Session Logical Read IM:               0.0               0.0
-             User calls:               0.2               4.6
-           Parses (SQL):               1.1              25.1
-      Hard parses (SQL):               0.0               0.9
-     SQL Work Area (MB):               0.0               0.3
-                 Logons:              30.0               0.1
-            User logons:               0.0               0.0
-         Executes (SQL):               1.1              25.9
-              Rollbacks:               0.0               0.9
-           Transactions:               0.0</t>
-  </si>
-  <si>
-    <t>数据库性能运行效率</t>
-  </si>
-  <si>
-    <t>Instance Efficiency Percentages (Target 100%)
-~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~
-            Buffer Nowait %:   60.00       Redo NoWait %:   60.00
-            Buffer  Hit   %:   60.00    In-memory Sort %:  100.00
-            Library Hit   %:   65.94        Soft Parse %:   66.55
-         Execute to Parse %:    2.81         Latch Hit %:   99.93
-Parse CPU to Parse Elapsd %:   53.85     % Non-Parse CPU:   99.95
-          Flash Cache Hit %:    0.00</t>
-  </si>
-  <si>
-    <t>数据库Top等待</t>
-  </si>
-  <si>
-    <t>Top 10 Foreground Events by Total Wait Time
-~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~
-                                           Total Wait       Avg   % DB Wait
-Event                                Waits Time (sec)      Wait   time Class
------------------------------- ----------- ---------- --------- ------ --------
-SQL*Net message from dblink          1,310        7.3    5.55ms   65.1 Network
-DB CPU                                            3.9             35.3
-log file sync                            9         .4   46.00ms    3.7 Commit
-SQL*Net break/reset to client          524         .1  228.04us    1.1 Applicat
-SQL*Net break/reset to dblink          262          0   16.21us     .0 Applicat
-PGA memory operation                    69          0   16.13us     .0 Other
-SQL*Net message to dblink              786          0  922.39ns     .0 Network
-SQL*Net message to client              786          0  745.55ns     .0 Network
-Disk file operations I/O                 1          0    7.00us     .0 User I/O
-ADR block file read                      0          0               .0 Other</t>
-  </si>
-  <si>
-    <t>数据库Top SQL(耗时)</t>
-  </si>
-  <si>
-    <t>监听状态及日志检查</t>
-  </si>
-  <si>
-    <t>....</t>
-  </si>
-  <si>
-    <t>并行度&gt;1的表</t>
-  </si>
-  <si>
-    <t>并行度&gt;1的索引</t>
-  </si>
-  <si>
-    <t>OWNER                          TABLE_NAME                     INDEX_NAME                               DEGREE     STATUS
------------------------------- ------------------------------ ---------------------------------------- ---------- --------
-APCDEV                         APC_ASML_SPEC_HIS_TABLE        INX_APC_ASML_SPEC_HIS_TABLE              3          VALID
-APCDEV                         APC_ASML_SPEC_TABLE            PK_APC_ASML_SPEC_TABLE                   3          VALID
-APCDEV                         APC_CANON_SPEC_HIS_TABLE       INX_APC_CANON_HIS_TABLE                  3          VALID
-APCDEV                         APC_CANON_SPEC_TABLE           PK_APC_CANON_SPEC_TABLE                  3          VALID
-APCDEV                         APC_CONSTANT_TABLE             PK_APC_CONSTANT_TABLE                    3          VALID
-APCDEV                         APC_GUI_ACTIVE_VERSION         PK_APC_GUI_ACTIVE_VERSION                3          VALID
-APCDEV                         APC_OFFSET_CANON               PK_APC_OFFSET_CANON                      3          VALID
-APCDEV                         APC_OFFSET_TABLE               PK_APC_OFFSET_TABLE                      3          VALID
-APCDEV                         APC_PROD_LAYER_INFO            PK_PROD_LAYER                            3          VALID
-APCDEV                         APC_SPEC_CONSTANT_TABLE        INX_APC_SPEC_CONSTANT_TABLE              3          VALID
-APCDEV                         APC_USER_GROUP                 PK_APC_USER_GROUP                        3          VALID
-APCDEV                         EQP_SSC_TABLE                  PK_EQP_SSC_TABLE                         3          VALID
-APCDEV                         EQP_SSC_TREND_TABLE            PK_EQP_SSC_TREND_TABLE                   3          VALID
-APCDEV                         EXPTOOLID_OVL_TABLE            PK_EQP                                   3          VALID
-APCDEV                         EXPTOOLID_TABLE                EXPTOOLID_TABLE_NO_CONSTR                3          VALID
-APCDEV                         FOCUS_RETICLE_TABLE            PK_FOCUS_RETICLE                         3          VALID
-APCDEV                         FOCUS_TABLE                    PK_FOCUS_TABLE                           3          VALID
-APCDEV                         LAYER_EDCPLAN_RELATION         LAYER_EDC_UNI                            3          VALID
-APCDEV                         LOGI_PROCESS_MS_REPORT         PROD_LAYER                               3          VALID
-APCDEV                         LOGI_PROCESS_MS_REPORT         INX_SYSID                                3          VALID
-APCDEV                         LOGI_PROCESS_MS_REPORT         LOGILOT_UNIQUE                           3          VALID
-APCDEV                         LOOK_UP_TABLE                  PK_LOOK_UP_TABLE                         3          VALID
-APCDEV                         LOT_OVL_PIE_TABLE              PK_LOT_OVL_PIE_TABLE                     3          VALID
-APCDEV                         OVL_PIE_TABLE_2017BAK          OVL_PIE_INDEX_1                          3          VALID
-APCDEV                         OVL_PIE_TABLE_2017BAK          PK_OVL_PIE_TABLE                         3          VALID
-APCDEV                         OVL_PRODUCTION_DATA_CANON      INX_OVL_PRODUCTION_DATA_CANON            3          VALID
-APCDEV                         PCMBX_ALL_TABLE                PK_PCMBX                                 3          VALID
-APCDEV                         PROCESS_CONDITION_CANON        INX_PROCESS_CONDITION_CANON              3          VALID
-APCDEV                         PROCESS_INIT_OVL_TABLE         PK_PROCESS_INIT_OVL_TABLE                3          VALID
-APCDEV                         PROCESS_INIT_TABLE             PK_PROCESS_INIT_TABLE                    3          VALID
-APCDEV                         PROCESS_OVL_REPORT             PK_PROCESS_OVL_REPORT                    3          VALID
-APCDEV                         PROCESS_OVL_REPORT             PROCESS_OVL_INDEX1                       3          VALID
-APCDEV                         PROCESS_OVL_REPORT             PROD_LAYER_LOTID                         3          VALID
-APCDEV                         PROCESS_OVL_REPORT             PROCESS_OVL_REPORT_INX1                  3          VALID
-APCDEV                         PRODUCT_TABLE                  PK_PRODUCT_TABLE                         3          VALID
-APCDEV                         PROD_OVL_LOOKUP_TABLE          PK_PROD_OVL_LOOKUP_TABLE                 3          VALID
-APCDEV                         REWORK_LOT_KEYIN_CANON         PK_REWORK_CANON                          3          VALID
-APCDEV                         REWORK_LOT_KEYIN_TABLE         PK_REWORK                                3          VALID
-APCDEV                         SCANNER_MONITOR_CANON          PK_SCANNER_MONITOR_CANON                 3          VALID
-APCDEV                         SCANNER_MONITOR_TABLE          PK_SCANNER_MONITOR_TABLE                 3          VALID
-APCDEV                         SCANNER_PM_TABLE               PK_SCANNER_PM_TABLE                      3          VALID
-APCDEV                         SCANNER_STATUS_CANON           PK_SCANNER_STATUS_CANON                  3          VALID
-APCDEV                         SCANNER_STATUS_TABLE           PK_SCANNER_STATUS_TABLE                  3          VALID
-CIMMGR                         CIM_GROUPS                     PK_CIM_GROUPS                            3          VALID
-CIMMGR                         CIM_SYSTEMS                    PK_CIM_SYSTEMS                           3          VALID
-CIMMGR                         CIM_SYS_ENTITIES               PK_CIM_SYS_ENTITIES                      3          VALID
-CIMMGR                         CIM_SYS_FUNCTIONS              PK_CIM_SYS_FUNCTIONS                     3          VALID
-CIMMGR                         CIM_USERS                      PK_CIM_USERS                             3          VALID
-CIMMGR                         CIM_USER_GROUPS                PK_CIM_USER_GROUPS                       3          VALID
-CIMMGR                         EAP_CFG_GLOBAL_FAB             PK_EAP_CFG_GLOBAL_FAB                    3          VALID
-CIMMGR                         EAP_CFG_MODEL_EQP              EAP_CFG_MODEL_EQP_INDEX1                 3          VALID
-CIMMGR                         EAP_CFG_MODEL_EQP              PK_EAP_CFG_MODEL_EQP                     3          VALID
-CIMMGR                         EAP_CFG_MODEL_EQPTYPE          PK_EAP_CFG_MODEL_EQPTYPE                 3          VALID
-CIMMGR                         EAP_CFG_SECONDEQ_EQP           PK_EAP_CFG_SECONDEQ_EQP                  3          VALID
-CIMMGR                         EAP_CFG_SERVER_FAB             PK_EAP_CFG_SERVER_FAB                    3          VALID
-CIMMGR                         EAP_CFG_WORKSTATION            PK_EAP_CFG_WORKSTATION                   3          VALID
-CIMMGR                         EAP_CFG_SMIF                   PK_EAP_CFG_SMIF                          3          VALID
-CIMMGR                         EAP_CFG_SERVER                 PK_EAP_CFG_SERVER                        3          VALID
-CIMMGR                         RMS_DRAFT_RECIPE_SPEC          PK_RMS_DRAFT_RECIPE_SPEC                 3          VALID
-CIMMGR                         RMS_RECIPE_COMPARE_TYPE        PK_RMS_RECIPE_COMPARE_TYPE               3          VALID
-CIMMGR                         RMS_RECIPE_FORMAT              PK_RMS_RECIPE_FORMAT                     3          VALID
-CIMMGR                         RMS_RECORD_LOCK                PK_RMS_RECORD_LOCK                       3          VALID
-CIMMGR                         RMS_RECIPE_MISMATCH_HISTORY    PK_RMS_RECIPE_MISMATCH_HISTORY           3          VALID
-CIMMGR                         EMS_PARANAME_TABLE             UK_PARA_INX                              3          VALID
-CIMMGR                         EMS_PARANAME_TABLE             PK_EMS_PARANAME_TABLE                    3          VALID
-CIMMGR                         EMS_SPEC_TABLE                 PK_EMS_SPEC_TABLE                        3          VALID
-CIMMGR                         EMS_SPEC_TABLE                 EMS_SPEC_INDEX1                          3          VALID
-CIMMGR                         EMS_SPEC_TABLE                 EMS_SPEC_INDEX2                          3          VALID
-CIMMGR                         EMS_SPEC_HISTORY_TABLE         EMS_SPEC_HISTORY_INDEX1                  3          VALID
-CIMMGR                         ELS_EQP_INFO                   PK_ELS_EQP_INFO                          3          VALID
-CIMMGR                         WRC_USER_ATTRIBUTE             PK_WRC_USER_ATTRIBUTE                    3          VALID
-CIMMGR                         WRC_TANK_STATUS                PK_WRC_TANK_STATUS                       3          VALID
-CIMMGR                         WRC_RECIPE_TANK                PK_WRC_RECIPE_TANK                       3          VALID
-CIMMGR                         WRC_RECIPE_STATUS              PK_WRC_RECIPE_STATUS                     3          VALID
-CIMMGR                         RMS_KEYWORDS_FILTER            PK_RMS_KEYWORDS_FILTER                   3          VALID
-CIMMGR                         RCP_RECP_RECPGROUP             PK_RCP_RECP_RECPGROUP                    3          VALID
-CIMMGR                         RCP_RECP_EXCEPTION             RECP_EXCEPTION                           3          VALID
-CIMMGR                         RCP_RECPGROUP_LIST             PK_RCP_RECPGROUP_LIST                    3          VALID
-CIMMGR                         RCP_IMP_RECIPE                 PK_PROD_STEQ_STAGE_RECIPE                3          VALID
-CIMMGR                         RCP_IMP_INFO                   PK_PROD_STEPSEQ                          3          VALID
-CIMMGR                         RCP_EQP_RECPGROUP              CHAM_RECPGRP                             3          VALID
-CIMMGR                         RCP_CHAMBER_EQPTYPE            PK_RCP_CHAMBER_EQPTYPE                   3          VALID
-CIMMGR                         EQP_PARMSPEC_TABLE_LOG         PK_EQP_PARMSPEC_TABLE_LOG                3          VALID
-CIMMGR                         EQP_PARMSPEC_TABLE             PK_EQP_PARMSPEC_TABLE                    3          VALID
-CIMMGR                         EAP_MON_LOT_ATTRIBUTES         PK_EAP_MON_LOT_ATTRIBUTES                3          VALID
-CIMMGR                         EAP_MON_EQP_ATTRIBUTES         PK_EAP_MON_EQP_ATTRIBUTES                3          VALID
-CIMMGR                         ELS_OVL_TABLE                  PK_ELS_OVL_TABLE                         3          VALID
-CIMMGR                         SCS_USER_ENTITY_PRIVS          PK_SCS_USER_ENTITY_PRIVS                 3          VALID
-CIMMGR                         SCS_USER_SYS_PRIVS             PK_SCS_USER_SYS_PRIVS                    3          VALID
-CIMMGR                         RMS_RECIPE_BODY                PK_RMS_RECIPE_BODY                       3          VALID
-CIMMGR                         RMS_RECIPE_SPEC                PK_RMS_RECIPE_SPEC                       3          VALID
-CIMMGR                         ELS_DYNAMIC_TABLE              PK_ELS_DYNAMIC_TABLE                     3          VALID
-CIMMGR                         ELS_DYNAMIC_TABLE              LASTMODIFY_INDX                          3          VALID
-CIMMGR                         ELS_DYNAMIC_TABLE              ELS_DYNAMIC_LOTID_INDEX                  3          VALID
-CIMMGR                         ELS_DUV_TABLE                  PK_ELS_DUV_TABLE                         3          VALID
-CIMMGR                         WSS_RULE_LOG                   WSS_RULE_LOG_INX1                        3          VALID
-CIMMGR                         WSS_RULE_LOG                   WSS_RULE_LOG_INX2                        3          VALID
-CIMMGR                         WSS_RULE_INFO                  WSS_RULE_INFO_INX1                       3          VALID
-CIMMGR                         WSS_RULE_DETAIL                WSS_RULE_DETAIL_INX1                     3          VALID
-CIMMGR                         WSS_REPLY_LOG                  WSS_REPLY_LOG_INX1                       3          VALID
-CIMMGR                         WSS_REPLY_LOG                  WSS_REPLY_LOG_INX2                       3          VALID
-CIMMGR                         PCC_PARA_SPEC                  PK_PCC_PARA_SPEC                         3          VALID
-CIMMGR                         PCC_PARA_INFO                  PK_PCC_PARA_INFO                         3          VALID
-CIMMGR                         PCC_PARA_INFO                  UNQ_PCC_PARA_INFO                        3          VALID
-CIMMGR                         ELS_CDSEM_TABLE                PK_ELS_CDSEM_TABLE                       3          VALID
-CIMMGR                         ELS_ADI_TABLE                  PK_ELS_ADI_TABLE                         3          VALID
-CIMMGR                         EAP_MON_SPEC_MAPPING           PK_EAP_MON_SPEC_MAPPING                  3          VALID
-CIMMGR                         EAP_MON_FLOW_SPEC              PK_EAP_MON_FLOW_SPEC                     3          VALID
-WSSAPP                         WSS_REPLY_LOG                  WSS_REPLY_LOG_INX1                       3          VALID
-WSSAPP                         WSS_REPLY_LOG                  WSS_REPLY_LOG_INX2                       3          VALID
-WSSAPP                         WSS_RULE_DETAIL                WSS_RULE_DETAIL_INX1                     3          VALID
-WSSAPP                         WSS_RULE_INFO                  WSS_RULE_INFO_INX1                       3          VALID
-WSSAPP                         WSS_RULE_LOG                   WSS_RULE_LOG_INX1                        3          VALID
-WSSAPP                         WSS_RULE_LOG                   WSS_RULE_LOG_INX2                        3          VALID
-EAPDEV                         EQP_ETCHRATERECIPE_TABLE       PK_EQP_ETCHRATERECIPE_TABLE              3          VALID
-EAPDEV                         EQP_METROLOGY_RECIPE_TABLE     PK_EQP_METROLOGY_RECIPE_TABLE            3          VALID
-EAPDEV                         EQP_PROCESS_PROD_TABLE         PK_EQP_PROCESS_PROD_TABLE                3          VALID
-EAPDEV                         EQP_PROCESS_RECIPE_TABLE       PK_EQP_PROCESS_RECIPE_TABLE              3          VALID
-EAPDEV                         SORTER_USER_TABLE              PK_SORTER_USER_TABLE                     3          VALID
-F1MCSAPP                       OST_DAILY                      OST_DAILY_INDEX                          3          VALID
-F1MCSAPP                       OST_DETAIL                     OST_DETAIL_INDEX                         3          VALID
-F1MCSAPP                       SCARREJECTLOT_DETAIL           SCARREJECTLOT_DETAIL_INDEX               3          VALID
-F1MCSAPP                       SCARTIMEOUT_INFO_DETAIL        SCARTIMEOUT_INFO_DETAIL_INDEX            3          VALID
-F2ISSUETAG                     ISSUETAG_DETAIL                ISSUETAG_DETAIL_INDEX1                   3          VALID
-MCSAPP                         OST_DAILY                      OST_DAILY_INDEX                          3          VALID
-MCSAPP                         OST_DETAIL                     OST_DETAIL_INDEX                         3          VALID
-MCSAPP                         SCARREJECTLOT_DETAIL           SCARREJECTLOT_DETAIL_INDEX               3          VALID
-MCSAPP                         SCARTIMEOUT_INFO_DETAIL        SCARTIMEOUT_INFO_DETAIL_INDEX            3          VALID
-RLTDEV                         EQP_HISTORY_TABLE              EQP_HISTORY_TABLE_INDEX1                 3          VALID
-CIMMGR                         PCC_PARA_MULTISPEC             PK_PCC_PARA_MULTISPEC                    3          VALID
-APCDEV                         OVL_PIE_TABLE_BK               OVL_PIE_INDEX22                          3          VALID
-CIMMGR                         EMS_LIMIT_CONFIG_TABLE         PK_EMS_LIMIT_CONFIG_TABLE                3          VALID
-WSSAPP                         WSS_RESULT_HISTORY             WSS_RESULT_HISTORY_INX1                  3          VALID
-WSSAPP                         WSS_RESULT_HISTORY             WSS_RESULT_HISTORY_INX2                  3          VALID
-APCDEV                         REWORK_LOT_KEYIN_NIKON         PK_REWORK_NIKON                          3          VALID
-APCDEV                         OVL_PIE_TABLE                  OVL_PIE_INDEX_MID_1                      3          VALID
-APCDEV                         OVL_PIE_TABLE                  PK_OVL_PIE_TABLE_MID                     3          VALID
-CIMMGR                         EMS_AMAT_CENTURA_DATA          EMS_AMAT_CENTURA_D_IX2                   2          N/A
-CIMMGR                         EMS_AMAT_CENTURA_OODATA        PK_EMS_AMAT_CENTURA_WAFERINX             2          N/A
-CIMMGR                         EMS_AMAT_DPS_METAL_DATA        EMS_DPS_METAL_D_IX2                      2          N/A
-CIMMGR                         EMS_AMAT_DPS_METAL_OODATA      PK_EMS_AMAT_DPS_METAL_INX                2          N/A
-CIMMGR                         EMS_AMAT_DPS_POLY_DATA         EMS_AMAT_DPS_POLY_D_IX2                  2          N/A
-CIMMGR                         EMS_AMAT_DPS_POLY_OODATA       PK_EMS_AMAT_DPS_POLY_INX                 2          N/A
-CIMMGR                         EMS_AMAT_EMAX_DATA             EMS_AMAT_EMAX_D_IX2                      2          N/A
-CIMMGR                         EMS_AMAT_EMAX_OODATA           PK_EMS_AMAT_EMAX_WAFERINX                2          N/A
-CIMMGR                         EMS_AMAT_ENDURA_DATA           EMS_AMAT_ENDURA_D_IX2                    2          N/A
-CIMMGR                         EMS_AMAT_ENDURA_OODATA         PK_EMS_AMAT_ENDURA_WAFERINX              2          N/A
-CIMMGR                         EMS_AMAT_MIRRA_DATA            EMS_AMAT_MIRRA_D_IX2                     2          N/A
-CIMMGR                         EMS_AMAT_MIRRA_OODATA          PK_EMS_AMAT_MIRRA_WAFERINX               2          N/A
-CIMMGR                         EMS_AMAT_PRODUCER_DATA         EMS_AMAT_PRODUCER_D_IX2                  2          N/A
-CIMMGR                         EMS_AMAT_PRODUCER_OODATA       PK_EMS_AMAT_PRODUCER_WAFERINX            2          N/A
-CIMMGR                         EMS_AMAT_QUANTUM_DATA          EMS_AMAT_QUANTUM_D_IX2                   2          N/A
-CIMMGR                         EMS_AMAT_QUANTUM_LEAP_DATA     EMS_AMAT_QUANTUM_LEAP_D_IX2              2          N/A
-CIMMGR                         EMS_AMAT_QUANTUM_LEAP_OODATA   PK_EMS_AMAT_QUANTUM_LEAP_INX             2          N/A
-CIMMGR                         EMS_AMAT_QUANTUM_OODATA        PK_EMS_AMAT_QUANTUM_WAFERINX             2          N/A
-CIMMGR                         EMS_AMAT_RTP_DATA              EMS_AMAT_RTP_D_IX2                       2          N/A
-CIMMGR                         EMS_AMAT_RTP_OODATA            PK_EMS_AMAT_RTP_WAFERINX                 2          N/A
-CIMMGR                         EMS_AMAT_SUPERE_DATA           EMS_AMAT_SUPERE_D_IX2                    2          N/A
-CIMMGR                         EMS_AMAT_SUPERE_OODATA         PK_EMS_AMAT_SUPERE_WAFERINX              2          N/A
-CIMMGR                         EMS_ASML_INLINE_1400_DATA      EMS_ASML_INLINE_1400_D_IX2               2          N/A
-CIMMGR                         EMS_ASML_INLINE_1400_OODATA    PK_EMS_ASML_INLINE_1400_INX              2          N/A
-CIMMGR                         EMS_ASML_INLINE_DATA           EMS_ASML_INLINE_D_IX2                    2          N/A
-CIMMGR                         EMS_ASML_INLINE_OODATA         PK_EMS_ASML_INLINE_WAFERINX              2          N/A
-CIMMGR                         EMS_ASM_FURNACE_DATA           EMS_ASM_FURNACE_D_IX2                    2          N/A
-CIMMGR                         EMS_ASM_FURNACE_OODATA         PK_EMS_ASM_FURNACE_WAFERINX              2          N/A
-CIMMGR                         EMS_AXCELIS_GEMINI_DATA        EMS_AXCELIS_GEMINI_D_IX2                 2          N/A
-CIMMGR                         EMS_AXCELIS_GEMINI_OODATA      PK_EMS_AXCELIS_GEMINI_INX                2          N/A
-CIMMGR                         EMS_AXCELIS_GSD200E2_DATA      EMS_AXCELIS_GSD200E2_D_IX2               2          N/A
-CIMMGR                         EMS_AXCELIS_GSD200E2_OODATA    PK_EMS_AXCELIS_GSD200E2_INX              2          N/A
-CIMMGR                         EMS_AXCELIS_XE_DATA            EMS_AXCELIS_XE_D_IX2                     2          N/A
-CIMMGR                         EMS_CANON_INLINE_DATA          EMS_CANON_INLINE_D_IX2                   2          N/A
-CIMMGR                         EMS_CANON_INLINE_OODATA        PK_EMS_CANON_INLINE_WAFERINX             2          N/A
-CIMMGR                         EMS_CETC_HJP200_DATA           EMS_CETC_HJP200_D_IX2                    2          N/A
-CIMMGR                         EMS_DNS_WS820_DATA             EMS_DNS_WS820_D_IX2                      2          N/A
-CIMMGR                         EMS_DNS_WS820_OODATA           PK_EMS_DNS_WS820_WAFERINX                2          N/A
-CIMMGR                         EMS_KE_FURNACE_DATA            EMS_KE_FURNACE_D_IX2                     2          N/A
-CIMMGR                         EMS_KE_FURNACE_OODATA          PK_EMS_KE_FURNACE_INX                    2          N/A
-CIMMGR                         EMS_LAM_2300_DATA              EMS_LAM_2300_D_IX2                       2          N/A
-CIMMGR                         EMS_LAM_2300_OODATA            PK_EMS_LAM_2300_WAFERINX                 2          N/A
-CIMMGR                         EMS_LAM_9400A_DATA             EMS_LAM_9400A_D_IX2                      2          N/A
-CIMMGR                         EMS_LAM_9400_DATA              EMS_LAM_9400_D_IX2                       2          N/A
-CIMMGR                         EMS_LAM_9400_OODATA            PK_EMS_LAM_9400_WAFERINX                 2          N/A
-CIMMGR                         EMS_LAM_9600A_DATA             EMS_LAM_9600A_D_IX2                      2          N/A
-CIMMGR                         EMS_LAM_9600_DATA              EMS_LAM_9600_D_IX2                       2          N/A
-CIMMGR                         EMS_LAM_9600_OODATA            PK_EMS_LAM_9600_WAFERINX                 2          N/A
-CIMMGR                         EMS_LAM_EXCELAN_DATA           EMS_LAM_EXCELAN_D_IX2                    2          N/A
-CIMMGR                         EMS_LAM_EXCELAN_OODATA         PK_EMS_LAM_EXCELAN_WAFERINX              2          N/A
-CIMMGR                         EMS_LMN_MARKER_DATA            EMS_LMN_MARKER_D_IX2                     2          N/A
-CIMMGR                         EMS_LMN_MARKER_OODATA          PK_EMS_LMN_MARKER_WAFERINX               2          N/A
-CIMMGR                         EMS_MATTSON_ASPEN_DATA         EMS_MATTSON_ASPEN_D_IX2                  2          N/A
-CIMMGR                         EMS_MATTSON_ASPEN_OODATA       PK_EMS_MATTSON_ASPEN_WAFERINX            2          N/A
-CIMMGR                         EMS_MATTSON_AWP3GEN_DATA       EMS_MATTSON_AWP3GEN_D_IX2                2          N/A
-CIMMGR                         EMS_MATTSON_AWP3GEN_OODATA     PK_EMS_MATTSON_AWP3GEN_INX               2          N/A
-CIMMGR                         EMS_NISSIN_2000AH_DATA         EMS_NISSIN_2000AH_D_IX2                  2          N/A
-CIMMGR                         EMS_NISSIN_2000AH_OODATA       PK_EMS_NISSIN_2000AH_INX                 2          N/A
-CIMMGR                         EMS_NISSIN_EX2300_DATA         EMS_NISSIN_EX2300_D_IX2                  2          N/A
-CIMMGR                         EMS_NISSIN_EX2300_OODATA       PK_EMS_NISSIN_EX2300_WAFERINX            2          N/A
-CIMMGR                         EMS_NOVELLOUS_GAMMAR_DATA      EMS_NOVELLOUS_GAMMAR_D_IX2               2          N/A
-CIMMGR                         EMS_NOVELLOUS_GAMMAR_OODATA    PK_EMS_NOVELLOUS_GAMMAR_INX              2          N/A
-CIMMGR                         EMS_NOVELLUS_C2_DATA           EMS_NOVELLUS_C2_D_IX2                    2          N/A
-CIMMGR                         EMS_NOVELLUS_C2_OODATA         PK_EMS_NOVELLUS_C2_WAFERINX              2          N/A
-CIMMGR                         EMS_PIOTECH_PF300T_DATA        EMS_PIOTECH_PF300T_D_IX2                 2          N/A
-CIMMGR                         EMS_PROZ_ASMLXT_DATA           EMS_PROZ_ASMLXT_D_IX2                    2          N/A
-CIMMGR                         EMS_SES_BW2000_OODATA          PK_EMS_SES_BW2000_WAFERINX               2          N/A
-CIMMGR                         EMS_SES_PEAGUS_OODATA          PK_EMS_SES_PEAGUS_WAFERINX               2          N/A
-CIMMGR                         EMS_SES_PEGASUS_DATA           EMS_SES_PEAGSUS_DATA_INX2                2          N/A
-CIMMGR                         EMS_SES_PEGASUS_OODATA         PK_EMS_SES_PEGASUS_WAFERINX              2          N/A
-CIMMGR                         EMS_SEZ_SP223_DATA             EMS_SEZ_SP223_D_IX2                      2          N/A
-CIMMGR                         EMS_SEZ_SP223_OODATA           PK_EMS_SEZ_SP223_WAFERINX                2          N/A
-CIMMGR                         EMS_SHIBAURA_CDE80_DATA        EMS_SHIBAURA_CDE80_D_IX2                 2          N/A
-CIMMGR                         EMS_SHIBAURA_CDE80_OODATA      PK_EMS_SHIBAURA_CDE80_INX                2          N/A
-CIMMGR                         EMS_TEL_8S_DATA                EMS_TEL_8S_D_IX2                         2          N/A
-CIMMGR                         EMS_TEL_8S_OODATA              PK_EMS_TEL_8S_WAFERINX                   2          N/A
-CIMMGR                         EMS_TEL_ACT8_DATA              EMS_TEL_ACT8_D_IX2                       2          N/A
-CIMMGR                         EMS_TEL_ACT8_OODATA            PK_EMS_TEL_ACT8_WAFERINX                 2          N/A
-CIMMGR                         EMS_TEL_DRM_DATA               EMS_TEL_DRM_D_IX2                        2          N/A
-CIMMGR                         EMS_TEL_DRM_OODATA             PK_EMS_TEL_DRM_WAFERINX                  2          N/A
-CIMMGR                         EMS_TEL_FURNANCE_DATA          EMS_TEL_FURNANCE_D_IX2                   2          N/A
-CIMMGR                         EMS_TEL_FURNANCE_OODATA        PK_EMS_TEL_FURNANCE_WAFERINX             2          N/A
-CIMMGR                         EMS_TEL_FURNANCE_PLUS_DATA     EMS_TEL_FURNANCE_PLUS_D_IX2              2          N/A
-CIMMGR                         EMS_TEL_FURNANCE_PLUS_OODATA   PK_EMS_TEL_FURNANCE_PLUS_INX             2          N/A
-CIMMGR                         EMS_TEL_GCIB_DATA              EMS_TEL_GCIB_D_IX2                       2          N/A
-CIMMGR                         EMS_TEL_MARK8_DATA             EMS_TEL_MARK8_D_IX2                      2          N/A
-CIMMGR                         EMS_TEL_MARK8_OODATA           PK_EMS_TEL_MARK8_WAFERINX                2          N/A
-CIMMGR                         EMS_TEL_MB2_DATA               EMS_TEL_MB2_D_IX2                        2          N/A
-CIMMGR                         EMS_TEL_MB2_OODATA             PK_EMS_TEL_MB2_WAFERINX                  2          N/A
-CIMMGR                         EMS_TEL_UNITYEP_DATA           EMS_TEL_UNITYEP_D_IX2                    2          N/A
-CIMMGR                         EMS_TEL_UNITYEP_OODATA         PK_EMS_TEL_UNITYEP_WAFERINX              2          N/A
-CIMMGR                         EMS_USHIO_UV_DATA              EMS_USHIO_UV_D_IX2                       2          N/A
-CIMMGR                         EMS_VARIAN_VIISTA810_DATA      EMS_VARIAN_VIISTA810_D_IX2               2          N/A
-CIMMGR                         WSS_RESULT_HISTORY             WSS_RESULT_HISTORY_INX1                  3          VALID
-APCDEV                         APC_NIKON_SPEC_HIS_TABLE       INX_APC_NIKON_HIS_TABLE                  3          VALID
-APCDEV                         APC_NIKON_SPEC_TABLE           PK_APC_NIKON_SPEC_TABLE                  3          VALID
-APCDEV                         APC_OFFSET_NIKON               PK_APC_OFFSET_NIKON                      3          VALID
-APCDEV                         OVL_PRODUCTION_DATA_NIKON      INX_OVL_PRODUCTION_DATA_NIKON            3          VALID
-APCDEV                         PROCESS_CONDITION_NIKON        INX_PROCESS_CONDITION_NIKON              3          VALID
-APCDEV                         SCANNER_STATUS_NIKON           PK_SCANNER_STATUS_NIKON                  3          VALID</t>
-  </si>
-  <si>
-    <t>无效索引检查</t>
-  </si>
-  <si>
-    <t>Oracle序列检查</t>
-  </si>
-  <si>
-    <t>SEQUENCE_OWNER                 CNT_LESS_200
------------------------------- ------------
-CIMMGR                                   35
-MCSMGR                                   24
-GSMADMIN_INTERNAL                        16
-WSSAPP                                    1
-RLTDEV                                    1
-RTDUSER                                   1</t>
-  </si>
-  <si>
-    <t>闪回区配置</t>
-  </si>
-  <si>
-    <t>NAME                                          SPACE_LIMIT       SPACE_USED SPACE_RECLAIMABLE  NUMBER_OF_FILES               CON_ID
----------------------------------------- ---------------- ---------------- ----------------- ---------------- --------------------
-/apc2db_arc/flashback/apc2db              322,122,547,200       26,689,536                 0                1                 .000</t>
-  </si>
-  <si>
-    <t>FlashRecovery区使用情况</t>
-  </si>
-  <si>
-    <t>FILE_TYPE                                PERCENT_SPACE_USED PERCENT_SPACE_RECLAIMABLE  NUMBER_OF_FILES               CON_ID
----------------------------------------- ------------------ ------------------------- ---------------- --------------------
-CONTROL FILE                                             91                         0                0                 .000
-REDO LOG                                                  0                         0                0                 .000
-ARCHIVED LOG                                              0                         0                0                 .000
-BACKUP PIECE                                              0                         0                1                 .000
-IMAGE COPY                                                0                         0                0                 .000
-FLASHBACK LOG                                             0                         0                0                 .000
-FOREIGN ARCHIVED LOG                                      0                         0                0                 .000
-AUXILIARY DATAFILE COPY                                   0                         0                0                 .000</t>
-  </si>
-  <si>
-    <t>数据库日志检查</t>
-  </si>
-  <si>
-    <t>Please check alert log file.</t>
-  </si>
-  <si>
-    <t>数据库RMAN备份</t>
-  </si>
-  <si>
-    <t>DBA权限用户检查</t>
-  </si>
-  <si>
-    <t>GRANTEE                        GRANTED_ROLE    ADMIN_OPTION
------------------------------- --------------- --------------------
-SYS                            DBA             YES
-SYSTEM                         DBA             YES</t>
-  </si>
-  <si>
-    <t>SYSDBA权限用户检查</t>
-  </si>
-  <si>
-    <t>数据库审计空间检查</t>
-  </si>
-  <si>
-    <t>SEGMENT_NAME    SIZE_IN_MEGABYTES TABLESPACE_NAME
---------------- ----------------- ------------------------------
-AUD$                      1280.00 AUDIT_TS
-FGA_LOG$                      .06 SYSTEM</t>
-  </si>
-  <si>
-    <t>数据库审计对象检查</t>
-  </si>
-  <si>
-    <t>COUNT(*)
---------------------
-                .000</t>
-  </si>
-  <si>
-    <t>业务对象存放系统表空间</t>
-  </si>
-  <si>
-    <t>OWNER                          TABLESPACE_NAME                SEGMENT_NAME                   SEGMENT_TYPE
------------------------------- ------------------------------ ------------------------------ ------------------------------
-GSMADMIN_INTERNAL              SYSTEM                         SHARD_TS                       TABLE
-GSMADMIN_INTERNAL              SYSTEM                         SYS_C00946932                  INDEX</t>
-  </si>
-  <si>
-    <t>错误口令登录锁定帐户PROFILE检查</t>
-  </si>
-  <si>
-    <t>USERNAME                       PROFILE              RESOURCE_NAME                  RESOURCE_T LIMIT
------------------------------- -------------------- ------------------------------ ---------- ------------------------------
-SPLUNKAUDIT                    DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-ORAAUD                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-EAPDISSCS                      DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-PERFSTAT                       DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-DPA4ORACLE                     DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-ITILUSER                       DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-APCDEV                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-WSSAPP                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-AMSAPP                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-EAPDEV                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-F2ISSUETAG                     DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-MCSAPP                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-F1MCSAPP                       DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-RLTDEV                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-CIMRPT                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-SCSAPP                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-CIMMGR                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-RTDUSER                        DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-EAPQUERY                       DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-RCPAPP                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-PERFSTAT9I                     DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-VCSUSER                        DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-F2REPUSER                      DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-YMSEAP2                        DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-EMSAPP                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-ALSAPP                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-CIMCFG                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-PSCAPP                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-MESUSER                        DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-EAPSA                          DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-RMSAPP                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-RTDELT                         DEFAULT              FAILED_LOGIN_ATTEMPTS          PASSWORD   UNLIMITED
-MCSMGR                         SESS_100             FAILED_LOGIN_ATTEMPTS          PASSWORD   DEFAULT</t>
-  </si>
-  <si>
-    <t>病毒勒索攻击检查</t>
-  </si>
-  <si>
-    <t>SCNHealthCheck检查</t>
-  </si>
-  <si>
-    <t>--------------------------------------------------------------
-ScnHealthCheck
---------------------------------------------------------------
-Current Date: 2023/03/22 16:41:14
-Current SCN:   10046958859857
-Version:       19.0.0.0.0
---------------------------------------------------------------
-Result: C - SCN Headroom is good
-Apply the latest recommended patches
-based on your maintenance schedule
-For further information review MOS document id 1393363.1
---------------------------------------------------------------</t>
-  </si>
-  <si>
-    <t>DataGuard同步延迟检查</t>
-  </si>
-  <si>
-    <t>DataGuard同步报错检查</t>
-  </si>
-  <si>
-    <t>----</t>
-  </si>
-  <si>
-    <t>sm0ora11节点的/ghome和/soft使用率超80%
-建议最近一段时间持续关注</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库运行效率</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU使用</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dbname</t>
+  </si>
+  <si>
+    <t>Dbmaa</t>
+  </si>
+  <si>
+    <t>Dbver</t>
+  </si>
+  <si>
+    <t>Dbstatus</t>
+  </si>
+  <si>
+    <t>Dblang</t>
+  </si>
+  <si>
+    <t>Logmode</t>
+  </si>
+  <si>
+    <t>Flashback</t>
+  </si>
+  <si>
+    <t>Dbtblcount</t>
+  </si>
+  <si>
+    <t>Dbrole</t>
+  </si>
+  <si>
+    <t>Dbtbsusage</t>
+  </si>
+  <si>
+    <t>Dbredocheck</t>
+  </si>
+  <si>
+    <t>Tmpfile_size</t>
+  </si>
+  <si>
+    <t>Dbcontrolfile</t>
+  </si>
+  <si>
+    <t>User_info</t>
+  </si>
+  <si>
+    <t>Tab_info</t>
+  </si>
+  <si>
+    <t>Dbresource</t>
+  </si>
+  <si>
+    <t>Dbsequence</t>
+  </si>
+  <si>
+    <t>Db_seq_usage</t>
+  </si>
+  <si>
+    <t>Dboption</t>
+  </si>
+  <si>
+    <t>Dbfeatures</t>
+  </si>
+  <si>
+    <t>Db_expir_user</t>
+  </si>
+  <si>
+    <t>Db_password_verif</t>
+  </si>
+  <si>
+    <t>Dbdbapriv</t>
+  </si>
+  <si>
+    <t>Dbsysdba</t>
+  </si>
+  <si>
+    <t>Dbauditsegment</t>
+  </si>
+  <si>
+    <t>Dbauditcont</t>
+  </si>
+  <si>
+    <t>Db_nosys_in_system</t>
+  </si>
+  <si>
+    <t>Dbrecoverydest</t>
+  </si>
+  <si>
+    <t>Dbflashrecoveryuseage</t>
+  </si>
+  <si>
+    <t>Dbproductuserfailedlogin</t>
+  </si>
+  <si>
+    <t>Dbvirscheck</t>
+  </si>
+  <si>
+    <t>Dbscnhealthcheck</t>
+  </si>
+  <si>
+    <t>Dbrmancheck</t>
+  </si>
+  <si>
+    <t>Dbdglagcheck</t>
+  </si>
+  <si>
+    <t>Dbdgerrcheck</t>
+  </si>
+  <si>
+    <t>Dbcrscheck</t>
+  </si>
+  <si>
+    <t>Dbasmusage</t>
+  </si>
+  <si>
+    <t>NodeID</t>
+  </si>
+  <si>
+    <t>Hostname</t>
+  </si>
+  <si>
+    <t>Ipaddr</t>
+  </si>
+  <si>
+    <t>Os</t>
+  </si>
+  <si>
+    <t>Relver</t>
+  </si>
+  <si>
+    <t>Cores</t>
+  </si>
+  <si>
+    <t>Cpumhz</t>
+  </si>
+  <si>
+    <t>Memtotal</t>
+  </si>
+  <si>
+    <t>Swaptotal</t>
+  </si>
+  <si>
+    <t>Osparameter</t>
+  </si>
+  <si>
+    <t>Ulimit</t>
+  </si>
+  <si>
+    <t>Tmzone</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oslog</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>PSU&amp;RU</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instname</t>
+  </si>
+  <si>
+    <t>Loadprofile</t>
+  </si>
+  <si>
+    <t>Instefficiency</t>
+  </si>
+  <si>
+    <t>Db_cursormem</t>
+  </si>
+  <si>
+    <t>Topevent</t>
+  </si>
+  <si>
+    <t>Topsqlbyelapstime</t>
+  </si>
+  <si>
+    <t>Dbpsu</t>
+  </si>
+  <si>
+    <t>Dbpatch</t>
+  </si>
+  <si>
+    <t>Dblsnrinfo</t>
+  </si>
+  <si>
+    <t>Dbparameter</t>
+  </si>
+  <si>
+    <t>Db_parameter_file</t>
+  </si>
+  <si>
+    <t>Dbredoswitch</t>
+  </si>
+  <si>
+    <t>Dberrlog</t>
+  </si>
+  <si>
+    <t>Top等待</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Top SQL(耗时)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>****</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU Info</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU 主频</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Filesystem</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inodeusage</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cpustat</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selinux状态</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selinux</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>防火墙状态</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firewall</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>NSSwitch配置检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nsswitch</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lo_mtu</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Machine_platform</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU_PERF_MODE</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOZEROCONF</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Memstat</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iostat</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thpstat</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hugpage</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Numa</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ntp</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>lo网卡MTU检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU性能模式检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZEROCONF路由检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>安全漏洞RPM包检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>RPM_PACKAGES</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>myzdb100</t>
+  </si>
+  <si>
+    <t>10.0.2.15
+1.1.1.100</t>
+  </si>
+  <si>
+    <t>Linux x86_64</t>
+  </si>
+  <si>
+    <t>Linux.Red Hat Enterprise Linux release 8.8 (Ootpa)</t>
+  </si>
+  <si>
+    <t>12th Gen Intel(R) Core(TM) i5-12400F 4</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>7 GB</t>
+  </si>
+  <si>
+    <t>主机平台</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作系统</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical Server</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oracle Database 19c Enterprise Edition Version 19.11.0.0.0</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源使用检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dbcursize</t>
+  </si>
+  <si>
+    <t>Dbf_size</t>
+  </si>
+  <si>
+    <t>Dbf_cnt</t>
+  </si>
+  <si>
+    <t>Dbf_stat</t>
+  </si>
+  <si>
+    <t>数据库当前使用大小</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据文件总大小</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时表空间文件大小</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库大小
+(当前已使用)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>User_size</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAB_PARALLEL</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>INVALID_OBJ</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>INVALID_INX</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>INX_PARALLEL</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -1569,7 +1246,7 @@
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="3"/>
@@ -1772,13 +1449,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFE6E6FA"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Microsoft YaHei Light"/>
@@ -1793,8 +1463,70 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE6E6FA"/>
+      <name val="幼圆"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Cascadia Code Light"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0066FF"/>
+      <name val="Corbel"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0066FF"/>
+      <name val="Microsoft YaHei Light"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFE6E6FA"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Cascadia Code Light"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1842,23 +1574,8 @@
         <fgColor rgb="FF555555"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4876FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFAEB9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00BF5F"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1919,6 +1636,236 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="thick">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="slantDashDot">
+        <color rgb="FFD8EFF1"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="slantDashDot">
+        <color rgb="FFD8EFF1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="slantDashDot">
+        <color rgb="FFD8EFF1"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="2" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0">
@@ -1976,7 +1923,7 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2040,15 +1987,9 @@
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="13" applyFont="1" applyFill="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="7" fontId="22" fillId="4" borderId="0" xfId="11" applyFont="1" applyFill="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="21" fillId="4" borderId="0" xfId="4" applyFont="1" applyFill="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2079,22 +2020,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="4" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="19" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="19"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" xfId="19" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="19" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" xfId="19" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2110,12 +2039,6 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="37" fontId="21" fillId="6" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="14" applyFill="1" applyBorder="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2128,38 +2051,179 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="37" fontId="21" fillId="2" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="14" applyBorder="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="37" fontId="21" fillId="6" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="14" applyFill="1" applyBorder="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="14" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="13" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="22" fillId="4" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="13" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="22" fillId="4" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="9" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="21" fillId="6" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="21" fillId="2" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="21" fillId="6" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="5" xfId="14" applyFont="1" applyBorder="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="3" xfId="14" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="4" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="19" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="9" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="9" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="19" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="4" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="19" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="7" fontId="22" fillId="4" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="7" fontId="22" fillId="4" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -2327,6 +2391,8 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFF2543A"/>
+      <color rgb="FFBE1F16"/>
       <color rgb="FF0066FF"/>
       <color rgb="FFD8EFF1"/>
       <color rgb="FFEAEAEA"/>
@@ -3189,13 +3255,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3306,10 +3372,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3418,10 +3484,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3603,6 +3669,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3610,7 +3677,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -4732,7 +4798,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1227795</xdr:colOff>
+      <xdr:colOff>1056345</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>834610</xdr:rowOff>
     </xdr:to>
@@ -4782,7 +4848,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1199283</xdr:colOff>
+      <xdr:colOff>1132608</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>11906</xdr:rowOff>
     </xdr:to>
@@ -5081,40 +5147,37 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:P40"/>
+  <dimension ref="B1:P52"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
     <col min="2" max="2" width="5.25" style="18" customWidth="1"/>
-    <col min="3" max="3" width="15.375" customWidth="1"/>
-    <col min="4" max="4" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="6.875" customWidth="1"/>
-    <col min="6" max="6" width="8.5" customWidth="1"/>
-    <col min="7" max="7" width="13.875" customWidth="1"/>
-    <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="12.5" customWidth="1"/>
-    <col min="10" max="10" width="10.375" customWidth="1"/>
-    <col min="11" max="11" width="16.25" customWidth="1"/>
-    <col min="12" max="12" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="4" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="6.375" customWidth="1"/>
+    <col min="8" max="8" width="15.625" customWidth="1"/>
+    <col min="9" max="10" width="12.625" customWidth="1"/>
+    <col min="11" max="11" width="16.375" customWidth="1"/>
+    <col min="12" max="12" width="6.75" customWidth="1"/>
     <col min="13" max="13" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="25"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="27"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
     </row>
     <row r="2" spans="2:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="14"/>
@@ -5146,172 +5209,168 @@
       <c r="K3" s="5"/>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="14"/>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21" t="s">
+      <c r="D4" s="49"/>
+      <c r="E4" s="101" t="s">
+        <v>214</v>
+      </c>
+      <c r="F4" s="101"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="53"/>
+      <c r="J4" s="100" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="100"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="14"/>
+      <c r="C5" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="51"/>
+      <c r="E5" s="102" t="s">
+        <v>215</v>
+      </c>
+      <c r="F5" s="102"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="50"/>
+      <c r="J5" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="K5" s="96"/>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="14"/>
+      <c r="C6" s="50" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="50"/>
+      <c r="E6" s="96" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" s="96"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="14"/>
-      <c r="C5" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21" t="s">
+      <c r="I6" s="50"/>
+      <c r="J6" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="19"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="14"/>
-      <c r="C6" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19" t="s">
-        <v>20</v>
-      </c>
+      <c r="K6" s="96"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="14"/>
-      <c r="C7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19" t="s">
-        <v>32</v>
-      </c>
+      <c r="C7" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="96" t="s">
+        <v>217</v>
+      </c>
+      <c r="F7" s="96"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="50"/>
+      <c r="J7" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="96"/>
       <c r="L7" s="8"/>
       <c r="P7" s="1">
-        <f>IFERROR(COUNTIFS(HealthReport!$H$27:$H$39,"&gt;0",HealthReport!$L$27:$L$39,"&gt;0")/SumItemsToBuy,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <f>19.8/12</f>
+        <v>1.6500000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="14"/>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="50"/>
+      <c r="E8" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" s="96"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="50"/>
+      <c r="J8" s="96" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="96"/>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="14"/>
+      <c r="C9" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="50"/>
+      <c r="E9" s="96" t="s">
+        <v>219</v>
+      </c>
+      <c r="F9" s="96"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="50"/>
+      <c r="J9" s="96" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="96"/>
+      <c r="L9" s="8"/>
+    </row>
+    <row r="10" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="14"/>
+      <c r="C10" s="50" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="50"/>
+      <c r="E10" s="96" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" s="96"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="52" t="s">
+        <v>232</v>
+      </c>
+      <c r="I10" s="50"/>
+      <c r="J10" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="14"/>
-      <c r="C9" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="24"/>
-      <c r="H9" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="8"/>
-    </row>
-    <row r="10" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="14"/>
-      <c r="C10" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="24"/>
-      <c r="H10" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19" t="s">
-        <v>25</v>
-      </c>
+      <c r="K10" s="96"/>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="2:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="14"/>
       <c r="C11" s="19"/>
       <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="19" t="s">
-        <v>26</v>
-      </c>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="19"/>
       <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19" t="s">
-        <v>27</v>
-      </c>
+      <c r="J11" s="95"/>
+      <c r="K11" s="95"/>
       <c r="L11" s="8"/>
     </row>
     <row r="12" spans="2:16" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
@@ -5330,7 +5389,7 @@
     <row r="13" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="15"/>
       <c r="C13" s="5" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
@@ -5349,13 +5408,13 @@
       <c r="B14" s="15"/>
       <c r="C14" s="8"/>
       <c r="D14" s="20" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
@@ -5367,16 +5426,16 @@
     <row r="15" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="15"/>
       <c r="C15" s="19" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D15" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -5388,16 +5447,16 @@
     <row r="16" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="15"/>
       <c r="C16" s="19" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D16" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E16" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
@@ -5409,10 +5468,10 @@
     <row r="17" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="15"/>
       <c r="C17" s="19" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D17" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="6">
         <v>0</v>
@@ -5430,7 +5489,7 @@
     <row r="18" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15"/>
       <c r="C18" s="19" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D18" s="6">
         <v>0</v>
@@ -5451,7 +5510,7 @@
     <row r="19" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
       <c r="C19" s="19" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D19" s="6">
         <v>0</v>
@@ -5472,7 +5531,7 @@
     <row r="20" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="15"/>
       <c r="C20" s="19" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D20" s="6">
         <v>0</v>
@@ -5493,7 +5552,7 @@
     <row r="21" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="15"/>
       <c r="C21" s="19" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D21" s="6">
         <v>0</v>
@@ -5514,7 +5573,7 @@
     <row r="22" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="15"/>
       <c r="C22" s="19" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D22" s="6">
         <v>0</v>
@@ -5561,7 +5620,7 @@
     <row r="25" spans="2:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="16"/>
       <c r="C25" s="5" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
@@ -5574,431 +5633,647 @@
       <c r="L25" s="11"/>
     </row>
     <row r="26" spans="2:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="H26" s="32" t="s">
+      <c r="B26" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="60">
+      <c r="H26" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="47">
         <f>SUM(HealthReport!$F$27:$F$39)/130</f>
         <v>0.52307692307692311</v>
       </c>
     </row>
-    <row r="27" spans="2:12" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="40">
+    <row r="27" spans="2:12" ht="38.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="34">
         <v>1</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="43"/>
-      <c r="F27" s="44">
+      <c r="C27" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="37"/>
+      <c r="F27" s="38">
         <v>10</v>
       </c>
-      <c r="G27" s="45" t="str" cm="1">
+      <c r="G27" s="70" t="str" cm="1">
         <f t="array" ref="G27">_xlfn.IFS(HealthReport!$F27&gt;=10,"PASS",HealthReport!$F27=8,"轻微",HealthReport!$F27=5,"普通",HealthReport!$F27=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-    </row>
-    <row r="28" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="47">
+      <c r="H27" s="98"/>
+      <c r="I27" s="98"/>
+      <c r="J27" s="98"/>
+      <c r="K27" s="98"/>
+      <c r="L27" s="75" t="str">
+        <f>HYPERLINK("#OS!B5","Detail")</f>
+        <v>Detail</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="39">
         <v>2</v>
       </c>
-      <c r="C28" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="48"/>
-      <c r="F28" s="50">
+      <c r="C28" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="40"/>
+      <c r="F28" s="42">
         <v>10</v>
       </c>
-      <c r="G28" s="51" t="str" cm="1">
+      <c r="G28" s="71" t="str" cm="1">
         <f t="array" ref="G28">_xlfn.IFS(HealthReport!$F28&gt;=10,"PASS",HealthReport!$F28=8,"轻微",HealthReport!$F28=5,"普通",HealthReport!$F28=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="52"/>
-    </row>
-    <row r="29" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="40">
+      <c r="H28" s="93"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="93"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="76" t="str">
+        <f>HYPERLINK("#OS!B5","Detail")</f>
+        <v>Detail</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="34">
         <v>3</v>
       </c>
-      <c r="C29" s="43" t="s">
+      <c r="C29" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="E29" s="43"/>
-      <c r="F29" s="44">
+      <c r="E29" s="37"/>
+      <c r="F29" s="38">
         <v>10</v>
       </c>
-      <c r="G29" s="45" t="str" cm="1">
+      <c r="G29" s="70" t="str" cm="1">
         <f t="array" ref="G29">_xlfn.IFS(HealthReport!$F29&gt;=10,"PASS",HealthReport!$F29=8,"轻微",HealthReport!$F29=5,"普通",HealthReport!$F29=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46"/>
-    </row>
-    <row r="30" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="47">
+      <c r="H29" s="94"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="94"/>
+      <c r="K29" s="94"/>
+      <c r="L29" s="75" t="str">
+        <f>HYPERLINK("#OS!B5","Detail")</f>
+        <v>Detail</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="39">
         <v>4</v>
       </c>
-      <c r="C30" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" s="48"/>
-      <c r="F30" s="50">
+      <c r="C30" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="40"/>
+      <c r="F30" s="42">
         <v>5</v>
       </c>
-      <c r="G30" s="51" t="str" cm="1">
+      <c r="G30" s="71" t="str" cm="1">
         <f t="array" ref="G30">_xlfn.IFS(HealthReport!$F30&gt;=10,"PASS",HealthReport!$F30=8,"轻微",HealthReport!$F30=5,"普通",HealthReport!$F30=0,"重要")</f>
         <v>普通</v>
       </c>
-      <c r="H30" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="52" t="str">
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="76" t="str">
         <f>HYPERLINK("#OS!B5","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="40">
+    <row r="31" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="34">
         <v>5</v>
       </c>
-      <c r="C31" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="E31" s="43"/>
-      <c r="F31" s="44">
+      <c r="C31" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="37"/>
+      <c r="F31" s="38">
         <v>10</v>
       </c>
-      <c r="G31" s="45" t="str" cm="1">
+      <c r="G31" s="70" t="str" cm="1">
         <f t="array" ref="G31">_xlfn.IFS(HealthReport!$F31&gt;=10,"PASS",HealthReport!$F31=8,"轻微",HealthReport!$F31=5,"普通",HealthReport!$F31=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="46" t="str">
+      <c r="H31" s="94"/>
+      <c r="I31" s="94"/>
+      <c r="J31" s="94"/>
+      <c r="K31" s="94"/>
+      <c r="L31" s="75" t="str">
         <f t="shared" ref="L31:L39" si="0">HYPERLINK("#OS!A1","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
-    <row r="32" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="47">
+    <row r="32" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="39">
         <v>6</v>
       </c>
-      <c r="C32" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="48"/>
-      <c r="F32" s="50">
+      <c r="C32" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="40"/>
+      <c r="F32" s="42">
         <v>10</v>
       </c>
-      <c r="G32" s="51" t="str" cm="1">
+      <c r="G32" s="71" t="str" cm="1">
         <f t="array" ref="G32">_xlfn.IFS(HealthReport!$F32&gt;=10,"PASS",HealthReport!$F32=8,"轻微",HealthReport!$F32=5,"普通",HealthReport!$F32=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="52" t="str">
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="93"/>
+      <c r="K32" s="93"/>
+      <c r="L32" s="76" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
-    <row r="33" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="40">
+    <row r="33" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="34">
         <v>7</v>
       </c>
-      <c r="C33" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="43"/>
-      <c r="F33" s="44">
+      <c r="C33" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="37"/>
+      <c r="F33" s="38">
         <v>8</v>
       </c>
-      <c r="G33" s="45" t="str" cm="1">
+      <c r="G33" s="70" t="str" cm="1">
         <f t="array" ref="G33">_xlfn.IFS(HealthReport!$F33&gt;=10,"PASS",HealthReport!$F33=8,"轻微",HealthReport!$F33=5,"普通",HealthReport!$F33=0,"重要")</f>
         <v>轻微</v>
       </c>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46" t="str">
+      <c r="H33" s="94"/>
+      <c r="I33" s="94"/>
+      <c r="J33" s="94"/>
+      <c r="K33" s="94"/>
+      <c r="L33" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
-    <row r="34" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="47">
+    <row r="34" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="39">
         <v>8</v>
       </c>
-      <c r="C34" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="E34" s="48"/>
-      <c r="F34" s="50">
+      <c r="C34" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="40"/>
+      <c r="F34" s="42">
         <v>5</v>
       </c>
-      <c r="G34" s="51" t="str" cm="1">
+      <c r="G34" s="71" t="str" cm="1">
         <f t="array" ref="G34">_xlfn.IFS(HealthReport!$F34&gt;=10,"PASS",HealthReport!$F34=8,"轻微",HealthReport!$F34=5,"普通",HealthReport!$F34=0,"重要")</f>
         <v>普通</v>
       </c>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="52" t="str">
+      <c r="H34" s="93"/>
+      <c r="I34" s="93"/>
+      <c r="J34" s="93"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="76" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
-    <row r="35" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="40">
+    <row r="35" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="34">
         <v>9</v>
       </c>
-      <c r="C35" s="43" t="s">
+      <c r="C35" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="D35" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="43"/>
-      <c r="F35" s="44">
+      <c r="E35" s="37"/>
+      <c r="F35" s="38">
         <v>0</v>
       </c>
-      <c r="G35" s="45" t="str" cm="1">
+      <c r="G35" s="70" t="str" cm="1">
         <f t="array" ref="G35">_xlfn.IFS(HealthReport!$F35&gt;=10,"PASS",HealthReport!$F35=8,"轻微",HealthReport!$F35=5,"普通",HealthReport!$F35=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46" t="str">
+      <c r="H35" s="94"/>
+      <c r="I35" s="94"/>
+      <c r="J35" s="94"/>
+      <c r="K35" s="94"/>
+      <c r="L35" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
-    <row r="36" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="47">
+    <row r="36" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="39">
         <v>10</v>
       </c>
-      <c r="C36" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="E36" s="48"/>
-      <c r="F36" s="50">
+      <c r="C36" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="40"/>
+      <c r="F36" s="42">
         <v>0</v>
       </c>
-      <c r="G36" s="51" t="str" cm="1">
+      <c r="G36" s="71" t="str" cm="1">
         <f t="array" ref="G36">_xlfn.IFS(HealthReport!$F36&gt;=10,"PASS",HealthReport!$F36=8,"轻微",HealthReport!$F36=5,"普通",HealthReport!$F36=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52" t="str">
+      <c r="H36" s="93"/>
+      <c r="I36" s="93"/>
+      <c r="J36" s="93"/>
+      <c r="K36" s="93"/>
+      <c r="L36" s="76" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
-    <row r="37" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="40">
+    <row r="37" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="34">
         <v>11</v>
       </c>
-      <c r="C37" s="43" t="s">
-        <v>52</v>
+      <c r="C37" s="37" t="s">
+        <v>34</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>67</v>
-      </c>
-      <c r="E37" s="43"/>
-      <c r="F37" s="44">
+        <v>45</v>
+      </c>
+      <c r="E37" s="37"/>
+      <c r="F37" s="38">
         <v>0</v>
       </c>
-      <c r="G37" s="45" t="str" cm="1">
+      <c r="G37" s="70" t="str" cm="1">
         <f t="array" ref="G37">_xlfn.IFS(HealthReport!$F37&gt;=10,"PASS",HealthReport!$F37=8,"轻微",HealthReport!$F37=5,"普通",HealthReport!$F37=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="46" t="str">
+      <c r="H37" s="94"/>
+      <c r="I37" s="94"/>
+      <c r="J37" s="94"/>
+      <c r="K37" s="94"/>
+      <c r="L37" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
-    <row r="38" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="47">
+    <row r="38" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="39">
         <v>12</v>
       </c>
-      <c r="C38" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="50">
+      <c r="C38" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="41"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="42">
         <v>0</v>
       </c>
-      <c r="G38" s="51" t="str" cm="1">
+      <c r="G38" s="71" t="str" cm="1">
         <f t="array" ref="G38">_xlfn.IFS(HealthReport!$F38&gt;=10,"PASS",HealthReport!$F38=8,"轻微",HealthReport!$F38=5,"普通",HealthReport!$F38=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="52" t="str">
+      <c r="H38" s="93"/>
+      <c r="I38" s="93"/>
+      <c r="J38" s="93"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="76" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
-    <row r="39" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="17">
         <v>13</v>
       </c>
-      <c r="C39" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="56">
+      <c r="C39" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="43"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="45">
         <v>0</v>
       </c>
-      <c r="G39" s="57" t="str" cm="1">
+      <c r="G39" s="72" t="str" cm="1">
         <f t="array" ref="G39">_xlfn.IFS(HealthReport!$F39&gt;=10,"PASS",HealthReport!$F39=8,"轻微",HealthReport!$F39=5,"普通",HealthReport!$F39=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="58"/>
-      <c r="L39" s="58" t="str">
+      <c r="H39" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="I39" s="94"/>
+      <c r="J39" s="94"/>
+      <c r="K39" s="94"/>
+      <c r="L39" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
-    <row r="40" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G40" s="18"/>
+    <row r="40" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="39"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="93"/>
+      <c r="J40" s="93"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="76"/>
+    </row>
+    <row r="41" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="17"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="72"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="94"/>
+      <c r="J41" s="94"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="77"/>
+    </row>
+    <row r="42" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="39"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="93"/>
+      <c r="I42" s="93"/>
+      <c r="J42" s="93"/>
+      <c r="K42" s="93"/>
+      <c r="L42" s="76"/>
+    </row>
+    <row r="43" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="17"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="72"/>
+      <c r="H43" s="94"/>
+      <c r="I43" s="94"/>
+      <c r="J43" s="94"/>
+      <c r="K43" s="94"/>
+      <c r="L43" s="77"/>
+    </row>
+    <row r="44" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="74"/>
+      <c r="C44" s="74"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="74"/>
+      <c r="H44" s="93"/>
+      <c r="I44" s="93"/>
+      <c r="J44" s="93"/>
+      <c r="K44" s="93"/>
+      <c r="L44" s="78"/>
+    </row>
+    <row r="45" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="17"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="72"/>
+      <c r="H45" s="94"/>
+      <c r="I45" s="94"/>
+      <c r="J45" s="94"/>
+      <c r="K45" s="94"/>
+      <c r="L45" s="77"/>
+    </row>
+    <row r="46" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="39"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="93"/>
+      <c r="I46" s="93"/>
+      <c r="J46" s="93"/>
+      <c r="K46" s="93"/>
+      <c r="L46" s="76"/>
+    </row>
+    <row r="47" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="17"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="72"/>
+      <c r="H47" s="94"/>
+      <c r="I47" s="94"/>
+      <c r="J47" s="94"/>
+      <c r="K47" s="94"/>
+      <c r="L47" s="77"/>
+    </row>
+    <row r="48" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="74"/>
+      <c r="C48" s="74"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="93"/>
+      <c r="I48" s="93"/>
+      <c r="J48" s="93"/>
+      <c r="K48" s="93"/>
+      <c r="L48" s="78"/>
+    </row>
+    <row r="49" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="17"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="72"/>
+      <c r="H49" s="94"/>
+      <c r="I49" s="94"/>
+      <c r="J49" s="94"/>
+      <c r="K49" s="94"/>
+      <c r="L49" s="77"/>
+    </row>
+    <row r="50" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="39"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="93"/>
+      <c r="I50" s="93"/>
+      <c r="J50" s="93"/>
+      <c r="K50" s="93"/>
+      <c r="L50" s="76"/>
+    </row>
+    <row r="51" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="17"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="72"/>
+      <c r="H51" s="94"/>
+      <c r="I51" s="94"/>
+      <c r="J51" s="94"/>
+      <c r="K51" s="94"/>
+      <c r="L51" s="77"/>
+    </row>
+    <row r="52" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="74"/>
+      <c r="C52" s="74"/>
+      <c r="D52" s="74"/>
+      <c r="E52" s="74"/>
+      <c r="F52" s="74"/>
+      <c r="G52" s="74"/>
+      <c r="H52" s="93"/>
+      <c r="I52" s="93"/>
+      <c r="J52" s="93"/>
+      <c r="K52" s="93"/>
+      <c r="L52" s="78"/>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="1">
+  <mergeCells count="42">
+    <mergeCell ref="H44:K44"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="J11:K11"/>
     <mergeCell ref="H30:K30"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H49:K49"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="B13:B24">
-    <cfRule type="notContainsBlanks" dxfId="7" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="7" priority="40">
       <formula>LEN(TRIM(B13))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:C14">
-    <cfRule type="notContainsBlanks" dxfId="6" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="6" priority="41">
       <formula>LEN(TRIM(B14))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:L12 J13:L17 H17 H18:L24">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="17">
+    <cfRule type="notContainsBlanks" dxfId="5" priority="54">
       <formula>LEN(TRIM(B12))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G11 G13:G19">
-    <cfRule type="notContainsBlanks" dxfId="4" priority="18">
+    <cfRule type="notContainsBlanks" dxfId="4" priority="55">
       <formula>LEN(TRIM(G8))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H15">
-    <cfRule type="notContainsBlanks" dxfId="3" priority="10">
+    <cfRule type="notContainsBlanks" dxfId="3" priority="47">
       <formula>LEN(TRIM(H14))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:I16">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="16">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="53">
       <formula>LEN(TRIM(H16))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I15">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="7">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="44">
       <formula>LEN(TRIM(I13))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L11 P7">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="19">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="56">
       <formula>LEN(TRIM(L4))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="226" yWindow="621" count="13">
+  <dataValidations xWindow="250" yWindow="706" count="13">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Title of this worksheet is in cells B1 through C1. Enter School Supplies in table starting in cell B8. Enter budget in cell C5" sqref="C1" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell C5. Shopping List Total in cell C6 and Remaining Cash in cell C7 are automatically calculated based on entries in Checklist table" sqref="H3:K3 E12:F14 C13:D14 C3:F3" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell at right" sqref="C4 C7 H4:I4 H7:I7 C15 C18" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in cell at right" sqref="C5 C8 H5:I5 H8:I8 C16 C19" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in this cell" sqref="D8:F8 J5:K5 J8:K8 D16:F16 D5:F5 D19:F19" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in this cell" sqref="D7:F7 J4:K4 J7:K7 D15:F15 D4:F4 D18:F18" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in cell at right" sqref="C6 C9:C12 H6:I6 C17 H10:I12 C20:C24" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in this cell" sqref="J6:K6 D17:F17 D9:F12 D6:F6 D20:F24 J10:K12" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in this cell" sqref="J5 D16:F16 D19:F19 D8:E8 J8 D5:E5" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in this cell" sqref="J4 D15:F15 D18:F18 D7:E7 J7 D4:E4" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in cell at right" sqref="C6 C20:C24 H6:I6 C17 H10:I12 C9:C12" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in this cell" sqref="F12 D17:F17 J6 D20:F24 J12:K12 J10:J11 D6:E6 D9:E12" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells E5 through H7" sqref="P7 H12:I12 G8:G19 C12:F12 L4:L11 H18:I24 H17 H13 H14:I14 H16:I16 H15 J12:L24" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Shopping details in table below. Category list is automatically updated from Category table" sqref="C25" xr:uid="{00000000-0002-0000-0000-00000A000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells below" sqref="H13" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
@@ -6013,35 +6288,13 @@
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
-  <ignoredErrors>
-    <ignoredError sqref="F8:F9" numberStoredAsText="1"/>
-  </ignoredErrors>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{D7E11CA3-AE2E-4AE0-8760-69AFD47E19CB}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>5</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>10</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F27:F39</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="126" id="{904FC827-5D32-400A-97DB-D891D8D2E589}">
+          <x14:cfRule type="iconSet" priority="27" id="{3AD485F5-512A-4830-BA74-F6B14C2FEF34}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6057,10 +6310,10 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>H27 J27 H28:J29 H33:J39 I31:J32 H30</xm:sqref>
+          <xm:sqref>B44:C44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="128" id="{91FC4C5D-AF8B-4E30-B194-1E2B2576DFF5}">
+          <x14:cfRule type="iconSet" priority="16" id="{0F123DC0-E9CB-494F-9537-5267D0443334}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6076,10 +6329,10 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>K28:K29 K31:K39</xm:sqref>
+          <xm:sqref>B48:C48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="127" id="{D6CA9112-E31E-493B-AC44-8CFD7A9AFAFB}">
+          <x14:cfRule type="iconSet" priority="5" id="{C75CBC66-D7CA-4A28-8777-654881069477}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6095,7 +6348,596 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>L28:L39</xm:sqref>
+          <xm:sqref>B52:C52</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="26" id="{42B44E61-BD45-4B3B-A366-60DC3FA6E891}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D44</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="15" id="{14B6D97C-3FC8-4777-B197-85596580A20F}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D48</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="4" id="{2B77CF01-0B59-4A94-968C-F819B9BFC886}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D52</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="25" id="{9AE0B0A0-31AC-419A-8920-AF3FF686551C}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>E44</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="14" id="{BAA9148E-4C74-4C1C-A14C-98B823C60A38}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>E48</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="3" id="{A442FCE3-8944-4D53-8BFE-78C12683D968}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>E52</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="38" id="{D7E11CA3-AE2E-4AE0-8760-69AFD47E19CB}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>5</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>8</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Flags" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F27:F43</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="24" id="{3D962523-5725-48F8-9A20-D1500F15E2BB}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F44</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="21" id="{385FA039-B741-4960-9F2A-71D6C39C50C7}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>5</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>8</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Flags" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F45:F47</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="13" id="{CCF709D9-2591-4DAA-9315-C7A0355D6EA8}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F48</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="10" id="{EE2C29C5-1120-417B-89C1-A4074EDF4D05}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>5</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>8</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Flags" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F49:F51</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{382D81D0-7236-4E93-AC9C-80DF5A6DE10A}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F52</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="29" id="{EC29932F-78D6-4AC8-9D56-2F5F67B5688C}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>G44</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="17" id="{DEE3C81E-B484-4A72-9E13-E137E9862E3F}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>G48</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="6" id="{9D2BC978-9B76-40DC-BBE3-4FE422176FDC}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>G52</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="163" id="{904FC827-5D32-400A-97DB-D891D8D2E589}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H27:H40</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="33" id="{63B576F9-8DAA-41CF-AE73-5AB45F4F4032}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H41</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="31" id="{26C2D381-0C21-4A34-BF51-D0D70A2BBE5D}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H42</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="32" id="{6416AA23-656B-4E60-B17B-E9CCF66906E3}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H43</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="23" id="{55F288BA-48B1-4F42-A62E-AAE73E9A550A}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H44</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="20" id="{E30994DE-231B-4B68-996D-3E763907FA3C}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H45</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="18" id="{5729C3FD-9889-4497-A536-FFF0436A57F1}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H46</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="19" id="{40AFAEA4-3FCA-4567-9EEA-1BB8BD606A55}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H47</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="12" id="{893EE127-E4CD-4D52-A058-33508E1A8A65}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H48</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="9" id="{E49E2337-1248-464F-93AA-524E7A88F776}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H49</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="7" id="{D4D8A87E-191B-49BE-8020-6766AF5D5BF4}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H50</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="8" id="{58674D53-21A4-454B-A030-FB1AC98A28E7}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H51</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{2B6F2A62-C5BD-445A-8744-A65F0CE63FC7}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H52</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="164" id="{D6CA9112-E31E-493B-AC44-8CFD7A9AFAFB}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L27:L43</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="22" id="{807675E3-8123-408A-902D-C5F91F09F34C}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L45:L47</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="11" id="{96A2AA7D-5F86-4DB5-9EFC-E3D5A371360F}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L49:L51</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -6105,118 +6947,320 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7AA4F4-B1FA-4569-9A5C-4430E8288027}">
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.25" style="36" customWidth="1"/>
-    <col min="2" max="26" width="70" style="35" customWidth="1"/>
-    <col min="27" max="16384" width="9" style="36"/>
+    <col min="1" max="1" width="19.125" style="84" customWidth="1"/>
+    <col min="2" max="2" width="18.375" style="87" customWidth="1"/>
+    <col min="3" max="4" width="90.625" style="56" customWidth="1"/>
+    <col min="5" max="5" width="9" style="32" customWidth="1"/>
+    <col min="6" max="28" width="70" style="32" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="35" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="85" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="79"/>
+      <c r="D1" s="80"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="61"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="83" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="86" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="61"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="83" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" s="86" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="58"/>
+      <c r="D4" s="81"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="59" t="str">
+      <c r="B5" s="86" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="58"/>
+      <c r="D5" s="61"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="83" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="86" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="58"/>
+      <c r="D6" s="62"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="83" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="58"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="46" t="str">
         <f>HYPERLINK("#HealthReport!B30","Retrun")</f>
         <v>Retrun</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="83" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="58"/>
+      <c r="D8" s="61"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="83" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="86" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" s="82"/>
+      <c r="D9" s="62"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="B10" s="86" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="58"/>
+      <c r="D10" s="62"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="86" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" s="58"/>
+      <c r="D11" s="61"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="86" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="58"/>
+      <c r="D12" s="60"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="86" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="58"/>
+      <c r="D13" s="81"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="86" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="58"/>
+      <c r="D14" s="66"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="83" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="86" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" s="58"/>
+      <c r="D15" s="61"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="83" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="86" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="58"/>
+      <c r="D16" s="62"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="86" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="58"/>
+      <c r="D17" s="61"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="86" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="58"/>
+      <c r="D18" s="61"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="86" t="s">
+        <v>205</v>
+      </c>
+      <c r="C19" s="82"/>
+      <c r="D19" s="62"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="35" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>76</v>
-      </c>
+      <c r="B20" s="86" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="82"/>
+      <c r="D20" s="62"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="86" t="s">
+        <v>207</v>
+      </c>
+      <c r="C21" s="58"/>
+      <c r="D21" s="62"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="83" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="86" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="59"/>
+      <c r="D22" s="66"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="86" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="82"/>
+      <c r="D23" s="61"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="83" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="86" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="82"/>
+      <c r="D24" s="62"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="83" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="86" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="82"/>
+      <c r="D25" s="61"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="83" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="86" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="82"/>
+      <c r="D26" s="61"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="83" t="s">
+        <v>209</v>
+      </c>
+      <c r="B27" s="86" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="82"/>
+      <c r="D27" s="62"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="83" t="s">
+        <v>210</v>
+      </c>
+      <c r="B28" s="86" t="s">
+        <v>201</v>
+      </c>
+      <c r="C28" s="82"/>
+      <c r="D28" s="62"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="83" t="s">
+        <v>211</v>
+      </c>
+      <c r="B29" s="86" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29" s="82"/>
+      <c r="D29" s="62"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="83" t="s">
+        <v>212</v>
+      </c>
+      <c r="B30" s="86" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" s="61"/>
+      <c r="D30" s="62"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -6226,279 +7270,738 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965D7FAC-338D-40AE-9A03-D56E1C0E6070}">
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:AB44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.25" style="36" customWidth="1"/>
-    <col min="2" max="26" width="87.5" style="35" customWidth="1"/>
-    <col min="27" max="16384" width="9" style="36"/>
+    <col min="1" max="1" width="25.5" style="84" customWidth="1"/>
+    <col min="2" max="2" width="20" style="89" customWidth="1"/>
+    <col min="3" max="4" width="90.625" style="56" customWidth="1"/>
+    <col min="5" max="27" width="87.5" style="32" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="35" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="375" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="38" t="s">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="88" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="57"/>
+      <c r="D1" s="60"/>
+      <c r="AB1" s="32"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="85" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="61"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="86" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="62"/>
+      <c r="AB3" s="32"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="83" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="85" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="59"/>
+      <c r="D4" s="62"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="83" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="85" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="59"/>
+      <c r="D5" s="62"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" s="83" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="85" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="59"/>
+      <c r="D6" s="62"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="83" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="85" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="59"/>
+      <c r="D7" s="62"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="83" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="85" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="62"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="83" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" s="85" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="59"/>
+      <c r="D9" s="62"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="83" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="59"/>
+      <c r="D10" s="62"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="83" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="85" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="59"/>
+      <c r="D11" s="62"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="83" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
+      <c r="B12" s="85" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" s="59"/>
+      <c r="D12" s="62"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="83" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="59"/>
+      <c r="D13" s="62"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="83" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="59"/>
+      <c r="D14" s="62"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="85" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="59"/>
+      <c r="D15" s="62"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" s="83" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="59"/>
+      <c r="D16" s="62"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="83" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="85" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="59"/>
+      <c r="D17" s="62"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="83" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="85" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="59"/>
+      <c r="D18" s="62"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="85" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="59"/>
+      <c r="D19" s="62"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="83" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="35" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="B20" s="85" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" s="59"/>
+      <c r="D20" s="62"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="390" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="B21" s="85" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="59"/>
+      <c r="D21" s="62"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="83" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="85" t="s">
+        <v>234</v>
+      </c>
+      <c r="C22" s="59"/>
+      <c r="D22" s="62"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="83" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="88" t="s">
+        <v>237</v>
+      </c>
+      <c r="C23" s="59"/>
+      <c r="D23" s="62"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="83" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="88" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="59"/>
+      <c r="D24" s="62"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="83" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="88" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="59"/>
+      <c r="D25" s="62"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="83" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="88" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="59"/>
+      <c r="D26" s="62"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="83" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="88" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="59"/>
+      <c r="D27" s="62"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="83" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="88" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" s="59"/>
+      <c r="D28" s="62"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="88" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="59"/>
+      <c r="D29" s="62"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="83" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="88" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="59"/>
+      <c r="D30" s="62"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="83" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="88" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" s="59"/>
+      <c r="D31" s="62"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="83" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="88" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="59"/>
+      <c r="D32" s="62"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="59"/>
+      <c r="D33" s="62"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" s="59"/>
+      <c r="D34" s="62"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="83" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="88" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" s="59"/>
+      <c r="D35" s="62"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="83" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="88" t="s">
+        <v>147</v>
+      </c>
+      <c r="C36" s="59"/>
+      <c r="D36" s="62"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="83" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="88" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="59"/>
+      <c r="D37" s="62"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="88" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="59"/>
+      <c r="D38" s="62"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="83" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" s="88" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="59"/>
+      <c r="D39" s="62"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="83" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="88" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40" s="59"/>
+      <c r="D40" s="62"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="83" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="88" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" s="59"/>
+      <c r="D41" s="62"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="83" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B42" s="88" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" s="59"/>
+      <c r="D42" s="62"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="83" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="88" t="s">
+        <v>156</v>
+      </c>
+      <c r="C43" s="59"/>
+      <c r="D43" s="62"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="83" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" s="88" t="s">
+        <v>157</v>
+      </c>
+      <c r="C44" s="63"/>
+      <c r="D44" s="64"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="14" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81493CED-92E7-4A64-BF87-00E3B3B76718}">
+  <dimension ref="A1:AB17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.125" style="90" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="4" width="90.625" style="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="58"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="66"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="83" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="83" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="58"/>
+      <c r="D4" s="66"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" s="83" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+    </row>
+    <row r="8" spans="1:28" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="83" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="32"/>
+      <c r="Y8" s="32"/>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="32"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="83" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="83" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="66"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="83" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="66"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="83" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" s="65"/>
+      <c r="D13" s="66"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="83" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" s="91"/>
+      <c r="D14" s="92"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="83" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" s="67"/>
+      <c r="D15" s="68"/>
+    </row>
+    <row r="16" spans="1:28" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="83" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="105" x14ac:dyDescent="0.25">
-      <c r="A7" s="34" t="s">
+      <c r="B16" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="59"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
+      <c r="AA16" s="32"/>
+    </row>
+    <row r="17" spans="1:27" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="35" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="150" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="375" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="225" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A18" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="165" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="B21" s="37" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" s="35" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="B28" s="35" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="B29" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="180" x14ac:dyDescent="0.25">
-      <c r="A30" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="35" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="B31" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="34" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="34" t="s">
-        <v>137</v>
-      </c>
+      <c r="B17" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="59"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="32"/>
+      <c r="W17" s="32"/>
+      <c r="X17" s="32"/>
+      <c r="Y17" s="32"/>
+      <c r="Z17" s="32"/>
+      <c r="AA17" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>

--- a/HealthReport.xlsx
+++ b/HealthReport.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A2E3E6-3789-4C59-8771-72EEAB5F5E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF45CFF-FB3D-4560-83D3-D2B13E7ED167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HealthReport" sheetId="1" r:id="rId1"/>
@@ -15,14 +15,14 @@
   </sheets>
   <definedNames>
     <definedName name="ChecklistTotal">SUM(#REF!)</definedName>
-    <definedName name="ColumnTitle1">HealthReport!$B$27:$L$39</definedName>
+    <definedName name="ColumnTitle1">HealthReport!$B$29:$L$41</definedName>
     <definedName name="ColumnTitle2">#REF!</definedName>
     <definedName name="ColumnTitle3">#REF!</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">HealthReport!$26:$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">HealthReport!$28:$28</definedName>
     <definedName name="RowTitleRegion1..C7">HealthReport!$C$4</definedName>
     <definedName name="SchoolYear">YEAR(TODAY())&amp;" - "&amp;YEAR(TODAY())+1</definedName>
-    <definedName name="SumItemsBought">COUNTIF(HealthReport!$L$27:$L$39,"&gt;0")</definedName>
-    <definedName name="SumItemsToBuy">COUNTIF(HealthReport!$H$27:$H$39,"&gt;0")</definedName>
+    <definedName name="SumItemsBought">COUNTIF(HealthReport!$L$29:$L$41,"&gt;0")</definedName>
+    <definedName name="SumItemsToBuy">COUNTIF(HealthReport!$H$29:$H$41,"&gt;0")</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="D27" authorId="0" shapeId="0" xr:uid="{9E41461E-B5F3-45AE-9099-A170B522429B}">
+    <comment ref="D29" authorId="0" shapeId="0" xr:uid="{9E41461E-B5F3-45AE-9099-A170B522429B}">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{CE8FA50E-BD3B-4973-83DB-480955872E6D}">
+    <comment ref="D30" authorId="0" shapeId="0" xr:uid="{CE8FA50E-BD3B-4973-83DB-480955872E6D}">
       <text>
         <r>
           <rPr>
@@ -97,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D29" authorId="0" shapeId="0" xr:uid="{BD3948E2-8A4C-436C-A251-46605C2AC180}">
+    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{BD3948E2-8A4C-436C-A251-46605C2AC180}">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D30" authorId="0" shapeId="0" xr:uid="{219BEDE6-F20F-41C0-8CEA-3DD317C4798C}">
+    <comment ref="D32" authorId="0" shapeId="0" xr:uid="{219BEDE6-F20F-41C0-8CEA-3DD317C4798C}">
       <text>
         <r>
           <rPr>
@@ -149,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{6038BBA1-4371-4944-962E-EF8DAAF1E365}">
+    <comment ref="D33" authorId="0" shapeId="0" xr:uid="{6038BBA1-4371-4944-962E-EF8DAAF1E365}">
       <text>
         <r>
           <rPr>
@@ -175,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D32" authorId="0" shapeId="0" xr:uid="{72672DE2-604C-4E12-8D14-22FBCC7B2E8D}">
+    <comment ref="D34" authorId="0" shapeId="0" xr:uid="{72672DE2-604C-4E12-8D14-22FBCC7B2E8D}">
       <text>
         <r>
           <rPr>
@@ -201,7 +201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D33" authorId="0" shapeId="0" xr:uid="{021971E8-0EF3-4147-A1FE-688FB0860E9A}">
+    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{021971E8-0EF3-4147-A1FE-688FB0860E9A}">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D34" authorId="0" shapeId="0" xr:uid="{388B4670-C978-444C-9E73-9808F46CB808}">
+    <comment ref="D36" authorId="0" shapeId="0" xr:uid="{388B4670-C978-444C-9E73-9808F46CB808}">
       <text>
         <r>
           <rPr>
@@ -253,7 +253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{C950E487-9BBE-47CD-837E-BFC7232D63DC}">
+    <comment ref="D37" authorId="0" shapeId="0" xr:uid="{C950E487-9BBE-47CD-837E-BFC7232D63DC}">
       <text>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D36" authorId="0" shapeId="0" xr:uid="{CAEAB304-D48F-42EF-854C-6ADD0CDE7561}">
+    <comment ref="D38" authorId="0" shapeId="0" xr:uid="{CAEAB304-D48F-42EF-854C-6ADD0CDE7561}">
       <text>
         <r>
           <rPr>
@@ -305,7 +305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D37" authorId="0" shapeId="0" xr:uid="{25822FDF-1644-4F43-898F-A6C8A5398052}">
+    <comment ref="D39" authorId="0" shapeId="0" xr:uid="{25822FDF-1644-4F43-898F-A6C8A5398052}">
       <text>
         <r>
           <rPr>
@@ -358,7 +358,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="249">
   <si>
     <r>
       <rPr>
@@ -427,81 +427,57 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>数据库集群检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <t>其他项检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>重要</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻微</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机系统分析</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Issue list</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>No.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题描述及建议</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题类别</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机系统分析</t>
   </si>
   <si>
     <t>数据库实例分析</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他项检查</t>
+  </si>
+  <si>
+    <t>数据库安全检查</t>
   </si>
   <si>
     <t>数据库备份检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库安全检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>软件使用分析</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他项检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>重要</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>轻微</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机系统分析</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Issue list</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>No.</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题描述及建议</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题类别</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机系统分析</t>
-  </si>
-  <si>
-    <t>数据库实例分析</t>
-  </si>
-  <si>
-    <t>其他项检查</t>
-  </si>
-  <si>
-    <t>数据库安全检查</t>
-  </si>
-  <si>
-    <t>数据库备份检查</t>
   </si>
   <si>
     <t>检查项</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>DataGuard检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>结果</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -638,14 +614,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>集群状态</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASM使用率</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>并行度&gt;1的表</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -886,9 +854,6 @@
     <t>Dbresource</t>
   </si>
   <si>
-    <t>Dbsequence</t>
-  </si>
-  <si>
     <t>Db_seq_usage</t>
   </si>
   <si>
@@ -901,9 +866,6 @@
     <t>Db_expir_user</t>
   </si>
   <si>
-    <t>Db_password_verif</t>
-  </si>
-  <si>
     <t>Dbdbapriv</t>
   </si>
   <si>
@@ -943,12 +905,6 @@
     <t>Dbdgerrcheck</t>
   </si>
   <si>
-    <t>Dbcrscheck</t>
-  </si>
-  <si>
-    <t>Dbasmusage</t>
-  </si>
-  <si>
     <t>NodeID</t>
   </si>
   <si>
@@ -1001,9 +957,6 @@
   </si>
   <si>
     <t>Instefficiency</t>
-  </si>
-  <si>
-    <t>Db_cursormem</t>
   </si>
   <si>
     <t>Topevent</t>
@@ -1235,6 +1188,102 @@
   </si>
   <si>
     <t>INX_PARALLEL</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dbsequence</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Db_password_verif</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crs_stat</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群资源状态</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCR状态</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCR备份检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASM磁盘组使用率</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASM磁盘偏移检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Asm_offset</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Asm_usage</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ocr_bak_check</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ocr_info</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crs_stat2</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群资源状态检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库集群</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataGuard</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库备份</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库安全</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机系统</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库分析</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件使用</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>实例分析</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库性能</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cursor_share_mem</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -2836,7 +2885,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>HealthReport!$L$25</c:f>
+              <c:f>HealthReport!$L$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -2845,7 +2894,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HealthReport!$L$26</c:f>
+              <c:f>HealthReport!$L$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3218,31 +3267,37 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>HealthReport!$C$15:$C$22</c:f>
+              <c:f>HealthReport!$C$15:$C$24</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>主机系统分析</c:v>
+                  <c:v>主机系统</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>数据库实例分析</c:v>
+                  <c:v>数据库分析</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>数据库集群检查</c:v>
+                  <c:v>实例分析</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>DataGuard检查</c:v>
+                  <c:v>数据库性能</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>数据库备份检查</c:v>
+                  <c:v>数据库集群</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>数据库安全检查</c:v>
+                  <c:v>DataGuard</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>软件使用分析</c:v>
+                  <c:v>数据库备份</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>数据库安全</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>软件使用</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>其他项检查</c:v>
                 </c:pt>
               </c:strCache>
@@ -3250,10 +3305,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HealthReport!$D$15:$D$22</c:f>
+              <c:f>HealthReport!$D$15:$D$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3276,6 +3331,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -3335,31 +3396,37 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>HealthReport!$C$15:$C$22</c:f>
+              <c:f>HealthReport!$C$15:$C$24</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>主机系统分析</c:v>
+                  <c:v>主机系统</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>数据库实例分析</c:v>
+                  <c:v>数据库分析</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>数据库集群检查</c:v>
+                  <c:v>实例分析</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>DataGuard检查</c:v>
+                  <c:v>数据库性能</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>数据库备份检查</c:v>
+                  <c:v>数据库集群</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>数据库安全检查</c:v>
+                  <c:v>DataGuard</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>软件使用分析</c:v>
+                  <c:v>数据库备份</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>数据库安全</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>软件使用</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>其他项检查</c:v>
                 </c:pt>
               </c:strCache>
@@ -3367,10 +3434,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HealthReport!$E$15:$E$22</c:f>
+              <c:f>HealthReport!$E$15:$E$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3393,6 +3460,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -3447,31 +3520,37 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>HealthReport!$C$15:$C$22</c:f>
+              <c:f>HealthReport!$C$15:$C$24</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>主机系统分析</c:v>
+                  <c:v>主机系统</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>数据库实例分析</c:v>
+                  <c:v>数据库分析</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>数据库集群检查</c:v>
+                  <c:v>实例分析</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>DataGuard检查</c:v>
+                  <c:v>数据库性能</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>数据库备份检查</c:v>
+                  <c:v>数据库集群</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>数据库安全检查</c:v>
+                  <c:v>DataGuard</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>软件使用分析</c:v>
+                  <c:v>数据库备份</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>数据库安全</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>软件使用</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>其他项检查</c:v>
                 </c:pt>
               </c:strCache>
@@ -3479,10 +3558,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HealthReport!$F$15:$F$22</c:f>
+              <c:f>HealthReport!$F$15:$F$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3505,6 +3584,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4887,7 +4972,7 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>579258</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>159768</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5147,7 +5232,7 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:P52"/>
+  <dimension ref="B1:P54"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -5170,7 +5255,7 @@
       <c r="D1" s="24"/>
       <c r="E1" s="24"/>
       <c r="F1" s="27" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G1" s="27"/>
       <c r="H1" s="25"/>
@@ -5216,7 +5301,7 @@
       </c>
       <c r="D4" s="49"/>
       <c r="E4" s="101" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="F4" s="101"/>
       <c r="G4" s="21"/>
@@ -5233,11 +5318,11 @@
     <row r="5" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14"/>
       <c r="C5" s="50" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D5" s="51"/>
       <c r="E5" s="102" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="F5" s="102"/>
       <c r="G5" s="21"/>
@@ -5246,7 +5331,7 @@
       </c>
       <c r="I5" s="50"/>
       <c r="J5" s="96" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="K5" s="96"/>
       <c r="L5" s="8"/>
@@ -5254,11 +5339,11 @@
     <row r="6" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="14"/>
       <c r="C6" s="50" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="96" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="F6" s="96"/>
       <c r="G6" s="21"/>
@@ -5275,16 +5360,16 @@
     <row r="7" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="14"/>
       <c r="C7" s="50" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="96" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="F7" s="96"/>
       <c r="G7" s="21"/>
       <c r="H7" s="50" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I7" s="50"/>
       <c r="J7" s="96" t="s">
@@ -5300,16 +5385,16 @@
     <row r="8" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="14"/>
       <c r="C8" s="50" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D8" s="50"/>
       <c r="E8" s="99" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="F8" s="96"/>
       <c r="G8" s="22"/>
       <c r="H8" s="50" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I8" s="50"/>
       <c r="J8" s="96" t="s">
@@ -5325,7 +5410,7 @@
       </c>
       <c r="D9" s="50"/>
       <c r="E9" s="96" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="F9" s="96"/>
       <c r="G9" s="22"/>
@@ -5342,16 +5427,16 @@
     <row r="10" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="14"/>
       <c r="C10" s="50" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D10" s="50"/>
       <c r="E10" s="96" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F10" s="96"/>
       <c r="G10" s="22"/>
       <c r="H10" s="52" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="I10" s="50"/>
       <c r="J10" s="96" t="s">
@@ -5396,7 +5481,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="8"/>
       <c r="H13" s="5" t="str">
-        <f>"Health status ("&amp;COUNTIFS(HealthReport!$L$27:$L$39, "&gt;0")&amp;" of "&amp;COUNTIFS(HealthReport!$H$27:$H$39, "&gt;0")&amp;")"</f>
+        <f>"Health status ("&amp;COUNTIFS(HealthReport!$L$29:$L$41, "&gt;0")&amp;" of "&amp;COUNTIFS(HealthReport!$H$29:$H$41, "&gt;0")&amp;")"</f>
         <v>Health status (0 of 0)</v>
       </c>
       <c r="I13" s="8"/>
@@ -5408,13 +5493,13 @@
       <c r="B14" s="15"/>
       <c r="C14" s="8"/>
       <c r="D14" s="20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
@@ -5426,7 +5511,7 @@
     <row r="15" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="15"/>
       <c r="C15" s="19" t="s">
-        <v>25</v>
+        <v>243</v>
       </c>
       <c r="D15" s="6">
         <v>0</v>
@@ -5447,7 +5532,7 @@
     <row r="16" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="15"/>
       <c r="C16" s="19" t="s">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="D16" s="6">
         <v>0</v>
@@ -5468,7 +5553,7 @@
     <row r="17" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="15"/>
       <c r="C17" s="19" t="s">
-        <v>17</v>
+        <v>246</v>
       </c>
       <c r="D17" s="6">
         <v>0</v>
@@ -5481,7 +5566,7 @@
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="5"/>
+      <c r="I17" s="8"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
@@ -5489,7 +5574,7 @@
     <row r="18" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15"/>
       <c r="C18" s="19" t="s">
-        <v>36</v>
+        <v>247</v>
       </c>
       <c r="D18" s="6">
         <v>0</v>
@@ -5510,7 +5595,7 @@
     <row r="19" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
       <c r="C19" s="19" t="s">
-        <v>19</v>
+        <v>239</v>
       </c>
       <c r="D19" s="6">
         <v>0</v>
@@ -5523,7 +5608,7 @@
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
@@ -5531,7 +5616,7 @@
     <row r="20" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="15"/>
       <c r="C20" s="19" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="D20" s="6">
         <v>0</v>
@@ -5542,7 +5627,7 @@
       <c r="F20" s="6">
         <v>0</v>
       </c>
-      <c r="G20" s="4"/>
+      <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
@@ -5552,7 +5637,7 @@
     <row r="21" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="15"/>
       <c r="C21" s="19" t="s">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="D21" s="6">
         <v>0</v>
@@ -5563,7 +5648,7 @@
       <c r="F21" s="6">
         <v>0</v>
       </c>
-      <c r="G21" s="4"/>
+      <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
@@ -5573,7 +5658,7 @@
     <row r="22" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="15"/>
       <c r="C22" s="19" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="D22" s="6">
         <v>0</v>
@@ -5591,12 +5676,20 @@
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
     </row>
-    <row r="23" spans="2:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="15"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="C23" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
       <c r="G23" s="4"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5604,12 +5697,20 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
     </row>
-    <row r="24" spans="2:12" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="15"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
+      <c r="C24" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
       <c r="G24" s="4"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -5617,112 +5718,84 @@
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
     </row>
-    <row r="25" spans="2:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="16"/>
-      <c r="C25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-    </row>
-    <row r="26" spans="2:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="73" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="69" t="s">
-        <v>46</v>
-      </c>
-      <c r="H26" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="47">
-        <f>SUM(HealthReport!$F$27:$F$39)/130</f>
+    <row r="25" spans="2:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="15"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="2:12" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="15"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+    </row>
+    <row r="27" spans="2:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+    </row>
+    <row r="28" spans="2:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="47">
+        <f>SUM(HealthReport!$F$29:$F$41)/130</f>
         <v>0.52307692307692311</v>
       </c>
     </row>
-    <row r="27" spans="2:12" ht="38.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="34">
+    <row r="29" spans="2:12" ht="38.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="34">
         <v>1</v>
       </c>
-      <c r="C27" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="37"/>
-      <c r="F27" s="38">
-        <v>10</v>
-      </c>
-      <c r="G27" s="70" t="str" cm="1">
-        <f t="array" ref="G27">_xlfn.IFS(HealthReport!$F27&gt;=10,"PASS",HealthReport!$F27=8,"轻微",HealthReport!$F27=5,"普通",HealthReport!$F27=0,"重要")</f>
-        <v>PASS</v>
-      </c>
-      <c r="H27" s="98"/>
-      <c r="I27" s="98"/>
-      <c r="J27" s="98"/>
-      <c r="K27" s="98"/>
-      <c r="L27" s="75" t="str">
-        <f>HYPERLINK("#OS!B5","Detail")</f>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="39">
-        <v>2</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="40"/>
-      <c r="F28" s="42">
-        <v>10</v>
-      </c>
-      <c r="G28" s="71" t="str" cm="1">
-        <f t="array" ref="G28">_xlfn.IFS(HealthReport!$F28&gt;=10,"PASS",HealthReport!$F28=8,"轻微",HealthReport!$F28=5,"普通",HealthReport!$F28=0,"重要")</f>
-        <v>PASS</v>
-      </c>
-      <c r="H28" s="93"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="76" t="str">
-        <f>HYPERLINK("#OS!B5","Detail")</f>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="34">
-        <v>3</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>48</v>
+      <c r="C29" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>41</v>
       </c>
       <c r="E29" s="37"/>
       <c r="F29" s="38">
@@ -5732,10 +5805,10 @@
         <f t="array" ref="G29">_xlfn.IFS(HealthReport!$F29&gt;=10,"PASS",HealthReport!$F29=8,"轻微",HealthReport!$F29=5,"普通",HealthReport!$F29=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H29" s="94"/>
-      <c r="I29" s="94"/>
-      <c r="J29" s="94"/>
-      <c r="K29" s="94"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="98"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="98"/>
       <c r="L29" s="75" t="str">
         <f>HYPERLINK("#OS!B5","Detail")</f>
         <v>Detail</v>
@@ -5743,21 +5816,21 @@
     </row>
     <row r="30" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E30" s="40"/>
       <c r="F30" s="42">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G30" s="71" t="str" cm="1">
         <f t="array" ref="G30">_xlfn.IFS(HealthReport!$F30&gt;=10,"PASS",HealthReport!$F30=8,"轻微",HealthReport!$F30=5,"普通",HealthReport!$F30=0,"重要")</f>
-        <v>普通</v>
+        <v>PASS</v>
       </c>
       <c r="H30" s="93"/>
       <c r="I30" s="93"/>
@@ -5770,13 +5843,13 @@
     </row>
     <row r="31" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E31" s="37"/>
       <c r="F31" s="38">
@@ -5791,81 +5864,81 @@
       <c r="J31" s="94"/>
       <c r="K31" s="94"/>
       <c r="L31" s="75" t="str">
-        <f t="shared" ref="L31:L39" si="0">HYPERLINK("#OS!A1","Detail")</f>
+        <f>HYPERLINK("#OS!B5","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E32" s="40"/>
       <c r="F32" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G32" s="71" t="str" cm="1">
         <f t="array" ref="G32">_xlfn.IFS(HealthReport!$F32&gt;=10,"PASS",HealthReport!$F32=8,"轻微",HealthReport!$F32=5,"普通",HealthReport!$F32=0,"重要")</f>
-        <v>PASS</v>
+        <v>普通</v>
       </c>
       <c r="H32" s="93"/>
       <c r="I32" s="93"/>
       <c r="J32" s="93"/>
       <c r="K32" s="93"/>
       <c r="L32" s="76" t="str">
-        <f t="shared" si="0"/>
+        <f>HYPERLINK("#OS!B5","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
     <row r="33" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E33" s="37"/>
       <c r="F33" s="38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G33" s="70" t="str" cm="1">
         <f t="array" ref="G33">_xlfn.IFS(HealthReport!$F33&gt;=10,"PASS",HealthReport!$F33=8,"轻微",HealthReport!$F33=5,"普通",HealthReport!$F33=0,"重要")</f>
-        <v>轻微</v>
+        <v>PASS</v>
       </c>
       <c r="H33" s="94"/>
       <c r="I33" s="94"/>
       <c r="J33" s="94"/>
       <c r="K33" s="94"/>
       <c r="L33" s="75" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L33:L41" si="0">HYPERLINK("#OS!A1","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
     <row r="34" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E34" s="40"/>
       <c r="F34" s="42">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G34" s="71" t="str" cm="1">
         <f t="array" ref="G34">_xlfn.IFS(HealthReport!$F34&gt;=10,"PASS",HealthReport!$F34=8,"轻微",HealthReport!$F34=5,"普通",HealthReport!$F34=0,"重要")</f>
-        <v>普通</v>
+        <v>PASS</v>
       </c>
       <c r="H34" s="93"/>
       <c r="I34" s="93"/>
@@ -5878,21 +5951,21 @@
     </row>
     <row r="35" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E35" s="37"/>
       <c r="F35" s="38">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G35" s="70" t="str" cm="1">
         <f t="array" ref="G35">_xlfn.IFS(HealthReport!$F35&gt;=10,"PASS",HealthReport!$F35=8,"轻微",HealthReport!$F35=5,"普通",HealthReport!$F35=0,"重要")</f>
-        <v>重要</v>
+        <v>轻微</v>
       </c>
       <c r="H35" s="94"/>
       <c r="I35" s="94"/>
@@ -5905,21 +5978,21 @@
     </row>
     <row r="36" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E36" s="40"/>
       <c r="F36" s="42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G36" s="71" t="str" cm="1">
         <f t="array" ref="G36">_xlfn.IFS(HealthReport!$F36&gt;=10,"PASS",HealthReport!$F36=8,"轻微",HealthReport!$F36=5,"普通",HealthReport!$F36=0,"重要")</f>
-        <v>重要</v>
+        <v>普通</v>
       </c>
       <c r="H36" s="93"/>
       <c r="I36" s="93"/>
@@ -5932,13 +6005,13 @@
     </row>
     <row r="37" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="34">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E37" s="37"/>
       <c r="F37" s="38">
@@ -5959,12 +6032,14 @@
     </row>
     <row r="38" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="39">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C38" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="41"/>
+        <v>26</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>38</v>
+      </c>
       <c r="E38" s="40"/>
       <c r="F38" s="42">
         <v>0</v>
@@ -5983,57 +6058,83 @@
       </c>
     </row>
     <row r="39" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="17">
-        <v>13</v>
-      </c>
-      <c r="C39" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="43"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="45">
+      <c r="B39" s="34">
+        <v>11</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="37"/>
+      <c r="F39" s="38">
         <v>0</v>
       </c>
-      <c r="G39" s="72" t="str" cm="1">
+      <c r="G39" s="70" t="str" cm="1">
         <f t="array" ref="G39">_xlfn.IFS(HealthReport!$F39&gt;=10,"PASS",HealthReport!$F39=8,"轻微",HealthReport!$F39=5,"普通",HealthReport!$F39=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H39" s="94" t="s">
-        <v>187</v>
-      </c>
+      <c r="H39" s="94"/>
       <c r="I39" s="94"/>
       <c r="J39" s="94"/>
       <c r="K39" s="94"/>
-      <c r="L39" s="77" t="str">
+      <c r="L39" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="39"/>
-      <c r="C40" s="40"/>
+      <c r="B40" s="39">
+        <v>12</v>
+      </c>
+      <c r="C40" s="40" t="s">
+        <v>28</v>
+      </c>
       <c r="D40" s="41"/>
       <c r="E40" s="40"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="71"/>
+      <c r="F40" s="42">
+        <v>0</v>
+      </c>
+      <c r="G40" s="71" t="str" cm="1">
+        <f t="array" ref="G40">_xlfn.IFS(HealthReport!$F40&gt;=10,"PASS",HealthReport!$F40=8,"轻微",HealthReport!$F40=5,"普通",HealthReport!$F40=0,"重要")</f>
+        <v>重要</v>
+      </c>
       <c r="H40" s="93"/>
       <c r="I40" s="93"/>
       <c r="J40" s="93"/>
       <c r="K40" s="93"/>
-      <c r="L40" s="76"/>
+      <c r="L40" s="76" t="str">
+        <f t="shared" si="0"/>
+        <v>Detail</v>
+      </c>
     </row>
     <row r="41" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="17"/>
-      <c r="C41" s="44"/>
+      <c r="B41" s="17">
+        <v>13</v>
+      </c>
+      <c r="C41" s="44" t="s">
+        <v>27</v>
+      </c>
       <c r="D41" s="43"/>
       <c r="E41" s="44"/>
-      <c r="F41" s="45"/>
-      <c r="G41" s="72"/>
-      <c r="H41" s="94"/>
+      <c r="F41" s="45">
+        <v>0</v>
+      </c>
+      <c r="G41" s="72" t="str" cm="1">
+        <f t="array" ref="G41">_xlfn.IFS(HealthReport!$F41&gt;=10,"PASS",HealthReport!$F41=8,"轻微",HealthReport!$F41=5,"普通",HealthReport!$F41=0,"重要")</f>
+        <v>重要</v>
+      </c>
+      <c r="H41" s="94" t="s">
+        <v>174</v>
+      </c>
       <c r="I41" s="94"/>
       <c r="J41" s="94"/>
       <c r="K41" s="94"/>
-      <c r="L41" s="77"/>
+      <c r="L41" s="77" t="str">
+        <f t="shared" si="0"/>
+        <v>Detail</v>
+      </c>
     </row>
     <row r="42" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="39"/>
@@ -6062,19 +6163,19 @@
       <c r="L43" s="77"/>
     </row>
     <row r="44" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="74"/>
-      <c r="C44" s="74"/>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="74"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="71"/>
       <c r="H44" s="93"/>
       <c r="I44" s="93"/>
       <c r="J44" s="93"/>
       <c r="K44" s="93"/>
-      <c r="L44" s="78"/>
-    </row>
-    <row r="45" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L44" s="76"/>
+    </row>
+    <row r="45" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="17"/>
       <c r="C45" s="44"/>
       <c r="D45" s="43"/>
@@ -6087,18 +6188,18 @@
       <c r="K45" s="94"/>
       <c r="L45" s="77"/>
     </row>
-    <row r="46" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="39"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="40"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="71"/>
+    <row r="46" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="74"/>
       <c r="H46" s="93"/>
       <c r="I46" s="93"/>
       <c r="J46" s="93"/>
       <c r="K46" s="93"/>
-      <c r="L46" s="76"/>
+      <c r="L46" s="78"/>
     </row>
     <row r="47" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="17"/>
@@ -6114,17 +6215,17 @@
       <c r="L47" s="77"/>
     </row>
     <row r="48" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="74"/>
-      <c r="C48" s="74"/>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="74"/>
+      <c r="B48" s="39"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="71"/>
       <c r="H48" s="93"/>
       <c r="I48" s="93"/>
       <c r="J48" s="93"/>
       <c r="K48" s="93"/>
-      <c r="L48" s="78"/>
+      <c r="L48" s="76"/>
     </row>
     <row r="49" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="17"/>
@@ -6140,17 +6241,17 @@
       <c r="L49" s="77"/>
     </row>
     <row r="50" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="39"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="42"/>
-      <c r="G50" s="71"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="74"/>
       <c r="H50" s="93"/>
       <c r="I50" s="93"/>
       <c r="J50" s="93"/>
       <c r="K50" s="93"/>
-      <c r="L50" s="76"/>
+      <c r="L50" s="78"/>
     </row>
     <row r="51" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="17"/>
@@ -6166,35 +6267,61 @@
       <c r="L51" s="77"/>
     </row>
     <row r="52" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="74"/>
-      <c r="C52" s="74"/>
-      <c r="D52" s="74"/>
-      <c r="E52" s="74"/>
-      <c r="F52" s="74"/>
-      <c r="G52" s="74"/>
+      <c r="B52" s="39"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="71"/>
       <c r="H52" s="93"/>
       <c r="I52" s="93"/>
       <c r="J52" s="93"/>
       <c r="K52" s="93"/>
-      <c r="L52" s="78"/>
+      <c r="L52" s="76"/>
+    </row>
+    <row r="53" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="17"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="45"/>
+      <c r="G53" s="72"/>
+      <c r="H53" s="94"/>
+      <c r="I53" s="94"/>
+      <c r="J53" s="94"/>
+      <c r="K53" s="94"/>
+      <c r="L53" s="77"/>
+    </row>
+    <row r="54" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="74"/>
+      <c r="C54" s="74"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="93"/>
+      <c r="I54" s="93"/>
+      <c r="J54" s="93"/>
+      <c r="K54" s="93"/>
+      <c r="L54" s="78"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="42">
-    <mergeCell ref="H44:K44"/>
-    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H46:K46"/>
     <mergeCell ref="H43:K43"/>
-    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="H45:K45"/>
     <mergeCell ref="H34:K34"/>
     <mergeCell ref="H36:K36"/>
     <mergeCell ref="H38:K38"/>
     <mergeCell ref="H40:K40"/>
     <mergeCell ref="H42:K42"/>
-    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="H44:K44"/>
     <mergeCell ref="H33:K33"/>
     <mergeCell ref="H35:K35"/>
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="H39:K39"/>
+    <mergeCell ref="H41:K41"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="J9:K9"/>
@@ -6208,24 +6335,24 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="J11:K11"/>
-    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="H32:K32"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="H28:K28"/>
     <mergeCell ref="H29:K29"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="H31:K31"/>
     <mergeCell ref="H52:K52"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="H54:K54"/>
     <mergeCell ref="H47:K47"/>
     <mergeCell ref="H48:K48"/>
     <mergeCell ref="H49:K49"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="H51:K51"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="B13:B24">
+  <conditionalFormatting sqref="B13:B26">
     <cfRule type="notContainsBlanks" dxfId="7" priority="40">
       <formula>LEN(TRIM(B13))&gt;0</formula>
     </cfRule>
@@ -6235,12 +6362,12 @@
       <formula>LEN(TRIM(B14))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12:L12 J13:L17 H17 H18:L24">
+  <conditionalFormatting sqref="B12:L12 J13:L19 H19 H20:L26">
     <cfRule type="notContainsBlanks" dxfId="5" priority="54">
       <formula>LEN(TRIM(B12))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G11 G13:G19">
+  <conditionalFormatting sqref="G8:G11 G13:G21">
     <cfRule type="notContainsBlanks" dxfId="4" priority="55">
       <formula>LEN(TRIM(G8))&gt;0</formula>
     </cfRule>
@@ -6250,7 +6377,7 @@
       <formula>LEN(TRIM(H14))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16:I16">
+  <conditionalFormatting sqref="H16:I18">
     <cfRule type="notContainsBlanks" dxfId="2" priority="53">
       <formula>LEN(TRIM(H16))&gt;0</formula>
     </cfRule>
@@ -6268,19 +6395,19 @@
   <dataValidations xWindow="250" yWindow="706" count="13">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Title of this worksheet is in cells B1 through C1. Enter School Supplies in table starting in cell B8. Enter budget in cell C5" sqref="C1" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell C5. Shopping List Total in cell C6 and Remaining Cash in cell C7 are automatically calculated based on entries in Checklist table" sqref="H3:K3 E12:F14 C13:D14 C3:F3" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell at right" sqref="C4 C7 H4:I4 H7:I7 C15 C18" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in cell at right" sqref="C5 C8 H5:I5 H8:I8 C16 C19" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in this cell" sqref="J5 D16:F16 D19:F19 D8:E8 J8 D5:E5" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in this cell" sqref="J4 D15:F15 D18:F18 D7:E7 J7 D4:E4" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in cell at right" sqref="C6 C20:C24 H6:I6 C17 H10:I12 C9:C12" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in this cell" sqref="F12 D17:F17 J6 D20:F24 J12:K12 J10:J11 D6:E6 D9:E12" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells E5 through H7" sqref="P7 H12:I12 G8:G19 C12:F12 L4:L11 H18:I24 H17 H13 H14:I14 H16:I16 H15 J12:L24" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Shopping details in table below. Category list is automatically updated from Category table" sqref="C25" xr:uid="{00000000-0002-0000-0000-00000A000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell at right" sqref="C4 C7 H4:I4 H7:I7 C15 C20" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in cell at right" sqref="C5 C8 H5:I5 H8:I8 C16:C18 C21" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in this cell" sqref="J5 D16:F18 D21:F21 D8:E8 J8 D5:E5" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in this cell" sqref="J4 D15:F15 D20:F20 D7:E7 J7 D4:E4" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in cell at right" sqref="C6 C22:C26 H6:I6 C19 H10:I12 C9:C12" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in this cell" sqref="F12 D19:F19 J6 D22:F26 J12:K12 J10:J11 D6:E6 D9:E12" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells E5 through H7" sqref="P7 H12:I12 G8:G21 C12:F12 L4:L11 H20:I26 H19 H13 H14:I14 H16:I18 H15 J12:L26" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Shopping details in table below. Category list is automatically updated from Category table" sqref="C27" xr:uid="{00000000-0002-0000-0000-00000A000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells below" sqref="H13" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27:C39" xr:uid="{9A7EB216-EA1D-4A3D-B9E3-20B91A83DBC8}">
-      <formula1>$C$15:$C$22</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C29:C41" xr:uid="{9A7EB216-EA1D-4A3D-B9E3-20B91A83DBC8}">
+      <formula1>$C$15:$C$24</formula1>
     </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select Category from the list. Enter new categories in Category worksheet. Select CANCEL, then press ALT+DOWN ARROW for options, then DOWN ARROW and ENTER to make selection" sqref="D27:E39" xr:uid="{00000000-0002-0000-0000-000013000000}"/>
+    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select Category from the list. Enter new categories in Category worksheet. Select CANCEL, then press ALT+DOWN ARROW for options, then DOWN ARROW and ENTER to make selection" sqref="D29:E41" xr:uid="{00000000-0002-0000-0000-000013000000}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6310,7 +6437,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>B44:C44</xm:sqref>
+          <xm:sqref>B46:C46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="16" id="{0F123DC0-E9CB-494F-9537-5267D0443334}">
@@ -6329,7 +6456,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>B48:C48</xm:sqref>
+          <xm:sqref>B50:C50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="5" id="{C75CBC66-D7CA-4A28-8777-654881069477}">
@@ -6348,7 +6475,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>B52:C52</xm:sqref>
+          <xm:sqref>B54:C54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="26" id="{42B44E61-BD45-4B3B-A366-60DC3FA6E891}">
@@ -6367,7 +6494,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>D44</xm:sqref>
+          <xm:sqref>D46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="15" id="{14B6D97C-3FC8-4777-B197-85596580A20F}">
@@ -6386,7 +6513,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>D48</xm:sqref>
+          <xm:sqref>D50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="4" id="{2B77CF01-0B59-4A94-968C-F819B9BFC886}">
@@ -6405,7 +6532,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>D52</xm:sqref>
+          <xm:sqref>D54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="25" id="{9AE0B0A0-31AC-419A-8920-AF3FF686551C}">
@@ -6424,7 +6551,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>E44</xm:sqref>
+          <xm:sqref>E46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="14" id="{BAA9148E-4C74-4C1C-A14C-98B823C60A38}">
@@ -6443,7 +6570,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>E48</xm:sqref>
+          <xm:sqref>E50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="3" id="{A442FCE3-8944-4D53-8BFE-78C12683D968}">
@@ -6462,7 +6589,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>E52</xm:sqref>
+          <xm:sqref>E54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="38" id="{D7E11CA3-AE2E-4AE0-8760-69AFD47E19CB}">
@@ -6481,7 +6608,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="1"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>F27:F43</xm:sqref>
+          <xm:sqref>F29:F45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="24" id="{3D962523-5725-48F8-9A20-D1500F15E2BB}">
@@ -6500,7 +6627,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>F44</xm:sqref>
+          <xm:sqref>F46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="21" id="{385FA039-B741-4960-9F2A-71D6C39C50C7}">
@@ -6519,7 +6646,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="1"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>F45:F47</xm:sqref>
+          <xm:sqref>F47:F49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="13" id="{CCF709D9-2591-4DAA-9315-C7A0355D6EA8}">
@@ -6538,7 +6665,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>F48</xm:sqref>
+          <xm:sqref>F50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="10" id="{EE2C29C5-1120-417B-89C1-A4074EDF4D05}">
@@ -6557,7 +6684,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="1"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>F49:F51</xm:sqref>
+          <xm:sqref>F51:F53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="2" id="{382D81D0-7236-4E93-AC9C-80DF5A6DE10A}">
@@ -6576,7 +6703,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>F52</xm:sqref>
+          <xm:sqref>F54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="29" id="{EC29932F-78D6-4AC8-9D56-2F5F67B5688C}">
@@ -6595,7 +6722,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>G44</xm:sqref>
+          <xm:sqref>G46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="17" id="{DEE3C81E-B484-4A72-9E13-E137E9862E3F}">
@@ -6614,7 +6741,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>G48</xm:sqref>
+          <xm:sqref>G50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="6" id="{9D2BC978-9B76-40DC-BBE3-4FE422176FDC}">
@@ -6633,7 +6760,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>G52</xm:sqref>
+          <xm:sqref>G54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="163" id="{904FC827-5D32-400A-97DB-D891D8D2E589}">
@@ -6652,48 +6779,10 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>H27:H40</xm:sqref>
+          <xm:sqref>H29:H42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="33" id="{63B576F9-8DAA-41CF-AE73-5AB45F4F4032}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H41</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="31" id="{26C2D381-0C21-4A34-BF51-D0D70A2BBE5D}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H42</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="32" id="{6416AA23-656B-4E60-B17B-E9CCF66906E3}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6712,7 +6801,7 @@
           <xm:sqref>H43</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="23" id="{55F288BA-48B1-4F42-A62E-AAE73E9A550A}">
+          <x14:cfRule type="iconSet" priority="31" id="{26C2D381-0C21-4A34-BF51-D0D70A2BBE5D}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6731,7 +6820,7 @@
           <xm:sqref>H44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="20" id="{E30994DE-231B-4B68-996D-3E763907FA3C}">
+          <x14:cfRule type="iconSet" priority="32" id="{6416AA23-656B-4E60-B17B-E9CCF66906E3}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6750,7 +6839,7 @@
           <xm:sqref>H45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="18" id="{5729C3FD-9889-4497-A536-FFF0436A57F1}">
+          <x14:cfRule type="iconSet" priority="23" id="{55F288BA-48B1-4F42-A62E-AAE73E9A550A}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6769,7 +6858,7 @@
           <xm:sqref>H46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="19" id="{40AFAEA4-3FCA-4567-9EEA-1BB8BD606A55}">
+          <x14:cfRule type="iconSet" priority="20" id="{E30994DE-231B-4B68-996D-3E763907FA3C}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6788,7 +6877,7 @@
           <xm:sqref>H47</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{893EE127-E4CD-4D52-A058-33508E1A8A65}">
+          <x14:cfRule type="iconSet" priority="18" id="{5729C3FD-9889-4497-A536-FFF0436A57F1}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6807,7 +6896,7 @@
           <xm:sqref>H48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{E49E2337-1248-464F-93AA-524E7A88F776}">
+          <x14:cfRule type="iconSet" priority="19" id="{40AFAEA4-3FCA-4567-9EEA-1BB8BD606A55}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6826,7 +6915,7 @@
           <xm:sqref>H49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{D4D8A87E-191B-49BE-8020-6766AF5D5BF4}">
+          <x14:cfRule type="iconSet" priority="12" id="{893EE127-E4CD-4D52-A058-33508E1A8A65}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6845,7 +6934,7 @@
           <xm:sqref>H50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{58674D53-21A4-454B-A030-FB1AC98A28E7}">
+          <x14:cfRule type="iconSet" priority="9" id="{E49E2337-1248-464F-93AA-524E7A88F776}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6864,7 +6953,7 @@
           <xm:sqref>H51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{2B6F2A62-C5BD-445A-8744-A65F0CE63FC7}">
+          <x14:cfRule type="iconSet" priority="7" id="{D4D8A87E-191B-49BE-8020-6766AF5D5BF4}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6883,7 +6972,7 @@
           <xm:sqref>H52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="164" id="{D6CA9112-E31E-493B-AC44-8CFD7A9AFAFB}">
+          <x14:cfRule type="iconSet" priority="8" id="{58674D53-21A4-454B-A030-FB1AC98A28E7}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6899,7 +6988,45 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>L27:L43</xm:sqref>
+          <xm:sqref>H53</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{2B6F2A62-C5BD-445A-8744-A65F0CE63FC7}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H54</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="164" id="{D6CA9112-E31E-493B-AC44-8CFD7A9AFAFB}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L29:L45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="22" id="{807675E3-8123-408A-902D-C5F91F09F34C}">
@@ -6918,7 +7045,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>L45:L47</xm:sqref>
+          <xm:sqref>L47:L49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="11" id="{96A2AA7D-5F86-4DB5-9EFC-E3D5A371360F}">
@@ -6937,7 +7064,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>L49:L51</xm:sqref>
+          <xm:sqref>L51:L53</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -6960,70 +7087,70 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="83" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B1" s="85" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C1" s="79"/>
       <c r="D1" s="80"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="83" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C2" s="58"/>
       <c r="D2" s="61"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="83" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C3" s="58"/>
       <c r="D3" s="61"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="83" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="C4" s="58"/>
       <c r="D4" s="81"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="83" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C5" s="58"/>
       <c r="D5" s="61"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="83" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C6" s="58"/>
       <c r="D6" s="62"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="83" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C7" s="58"/>
       <c r="D7" s="61"/>
@@ -7034,230 +7161,230 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="83" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C8" s="58"/>
       <c r="D8" s="61"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="83" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="C9" s="82"/>
       <c r="D9" s="62"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="83" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C10" s="58"/>
       <c r="D10" s="62"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="83" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C11" s="58"/>
       <c r="D11" s="61"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="83" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B12" s="86" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="60"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="83" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C13" s="58"/>
       <c r="D13" s="81"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="83" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B14" s="86" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C14" s="58"/>
       <c r="D14" s="66"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="83" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C15" s="58"/>
       <c r="D15" s="61"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="83" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B16" s="86" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C16" s="58"/>
       <c r="D16" s="62"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="83" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B17" s="86" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C17" s="58"/>
       <c r="D17" s="61"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="83" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B18" s="86" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C18" s="58"/>
       <c r="D18" s="61"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="83" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="C19" s="82"/>
       <c r="D19" s="62"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="83" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B20" s="86" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C20" s="82"/>
       <c r="D20" s="62"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="83" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C21" s="58"/>
       <c r="D21" s="62"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="83" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C22" s="59"/>
       <c r="D22" s="66"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="83" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B23" s="86" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C23" s="82"/>
       <c r="D23" s="61"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="83" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B24" s="86" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C24" s="82"/>
       <c r="D24" s="62"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="83" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B25" s="86" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C25" s="82"/>
       <c r="D25" s="61"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="83" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B26" s="86" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C26" s="82"/>
       <c r="D26" s="61"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="83" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B27" s="86" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C27" s="82"/>
       <c r="D27" s="62"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="83" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B28" s="86" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C28" s="82"/>
       <c r="D28" s="62"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="83" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="B29" s="86" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C29" s="82"/>
       <c r="D29" s="62"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="83" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B30" s="86" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C30" s="61"/>
       <c r="D30" s="62"/>
@@ -7270,7 +7397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965D7FAC-338D-40AE-9A03-D56E1C0E6070}">
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5" style="84" customWidth="1"/>
@@ -7282,10 +7409,10 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="83" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B1" s="88" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C1" s="57"/>
       <c r="D1" s="60"/>
@@ -7293,20 +7420,20 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="83" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B2" s="85" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C2" s="58"/>
       <c r="D2" s="61"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="83" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C3" s="59"/>
       <c r="D3" s="62"/>
@@ -7314,110 +7441,110 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="83" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B4" s="85" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C4" s="59"/>
       <c r="D4" s="62"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="83" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B5" s="85" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C5" s="59"/>
       <c r="D5" s="62"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="83" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B6" s="85" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C6" s="59"/>
       <c r="D6" s="62"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="83" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B7" s="85" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C7" s="59"/>
       <c r="D7" s="62"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="83" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C8" s="59"/>
       <c r="D8" s="62"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="83" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="B9" s="85" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C9" s="59"/>
       <c r="D9" s="62"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="83" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="B10" s="85" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C10" s="59"/>
       <c r="D10" s="62"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="83" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C11" s="59"/>
       <c r="D11" s="62"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="83" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C12" s="59"/>
       <c r="D12" s="62"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="83" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C13" s="59"/>
       <c r="D13" s="62"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="83" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C14" s="59"/>
       <c r="D14" s="62"/>
@@ -7427,300 +7554,340 @@
         <v>9</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C15" s="59"/>
       <c r="D15" s="62"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="83" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C16" s="59"/>
       <c r="D16" s="62"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="83" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B17" s="85" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C17" s="59"/>
       <c r="D17" s="62"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="83" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B18" s="85" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C18" s="59"/>
       <c r="D18" s="62"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="83" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B19" s="85" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C19" s="59"/>
       <c r="D19" s="62"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="83" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B20" s="85" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C20" s="59"/>
       <c r="D20" s="62"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="83" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B21" s="85" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C21" s="59"/>
       <c r="D21" s="62"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="83" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B22" s="85" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="C22" s="59"/>
       <c r="D22" s="62"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="83" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B23" s="88" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C23" s="59"/>
       <c r="D23" s="62"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="83" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B24" s="88" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C24" s="59"/>
       <c r="D24" s="62"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="83" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B25" s="88" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C25" s="59"/>
       <c r="D25" s="62"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="83" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B26" s="88" t="s">
-        <v>137</v>
+        <v>225</v>
       </c>
       <c r="C26" s="59"/>
       <c r="D26" s="62"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="83" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B27" s="88" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C27" s="59"/>
       <c r="D27" s="62"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="83" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B28" s="88" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C28" s="59"/>
       <c r="D28" s="62"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="83" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B29" s="88" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C29" s="59"/>
       <c r="D29" s="62"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="83" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B30" s="88" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C30" s="59"/>
       <c r="D30" s="62"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="83" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B31" s="88" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
       <c r="C31" s="59"/>
       <c r="D31" s="62"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="83" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B32" s="88" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C32" s="59"/>
       <c r="D32" s="62"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="83" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B33" s="88" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C33" s="59"/>
       <c r="D33" s="62"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="83" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B34" s="88" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C34" s="59"/>
       <c r="D34" s="62"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="83" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B35" s="88" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C35" s="59"/>
       <c r="D35" s="62"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="83" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B36" s="88" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C36" s="59"/>
       <c r="D36" s="62"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="83" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B37" s="88" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="62"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="83" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B38" s="88" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="62"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="83" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B39" s="88" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C39" s="59"/>
       <c r="D39" s="62"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="83" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B40" s="88" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C40" s="59"/>
       <c r="D40" s="62"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="83" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B41" s="88" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C41" s="59"/>
       <c r="D41" s="62"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="83" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B42" s="88" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C42" s="59"/>
       <c r="D42" s="62"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="83" t="s">
-        <v>71</v>
+        <v>228</v>
       </c>
       <c r="B43" s="88" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="C43" s="59"/>
       <c r="D43" s="62"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="83" t="s">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="B44" s="88" t="s">
-        <v>157</v>
-      </c>
-      <c r="C44" s="63"/>
-      <c r="D44" s="64"/>
+        <v>237</v>
+      </c>
+      <c r="C44" s="57"/>
+      <c r="D44" s="60"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="83" t="s">
+        <v>229</v>
+      </c>
+      <c r="B45" s="88" t="s">
+        <v>236</v>
+      </c>
+      <c r="C45" s="63"/>
+      <c r="D45" s="64"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="83" t="s">
+        <v>230</v>
+      </c>
+      <c r="B46" s="88" t="s">
+        <v>235</v>
+      </c>
+      <c r="C46" s="59"/>
+      <c r="D46" s="62"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="83" t="s">
+        <v>231</v>
+      </c>
+      <c r="B47" s="88" t="s">
+        <v>234</v>
+      </c>
+      <c r="C47" s="57"/>
+      <c r="D47" s="60"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="83" t="s">
+        <v>232</v>
+      </c>
+      <c r="B48" s="88" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="63"/>
+      <c r="D48" s="64"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -7734,16 +7901,16 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.125" style="90" customWidth="1"/>
-    <col min="2" max="2" width="18.875" customWidth="1"/>
-    <col min="3" max="4" width="90.625" style="55" customWidth="1"/>
+    <col min="2" max="2" width="15.625" customWidth="1"/>
+    <col min="3" max="4" width="102.625" style="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="83" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C1" s="58"/>
       <c r="D1" s="61"/>
@@ -7774,70 +7941,70 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="83" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C2" s="65"/>
       <c r="D2" s="66"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="83" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C3" s="65"/>
       <c r="D3" s="66"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="83" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C4" s="58"/>
       <c r="D4" s="66"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="83" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C5" s="65"/>
       <c r="D5" s="66"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="83" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C6" s="65"/>
       <c r="D6" s="66"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="27" x14ac:dyDescent="0.25">
       <c r="A7" s="83" t="s">
-        <v>186</v>
+        <v>93</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="C7" s="65"/>
       <c r="D7" s="66"/>
     </row>
     <row r="8" spans="1:28" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="83" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C8" s="65"/>
       <c r="D8" s="66"/>
@@ -7867,82 +8034,82 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="83" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C9" s="65"/>
       <c r="D9" s="66"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="83" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C10" s="65"/>
       <c r="D10" s="66"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="83" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C11" s="65"/>
       <c r="D11" s="66"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="83" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C12" s="65" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D12" s="66"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="27" x14ac:dyDescent="0.25">
       <c r="A13" s="83" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="83" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C14" s="91"/>
       <c r="D14" s="92"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="83" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B15" s="54" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C15" s="67"/>
       <c r="D15" s="68"/>
     </row>
     <row r="16" spans="1:28" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="83" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B16" s="54" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C16" s="59"/>
       <c r="D16" s="62"/>
@@ -7972,10 +8139,10 @@
     </row>
     <row r="17" spans="1:27" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="83" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C17" s="59"/>
       <c r="D17" s="62"/>

--- a/HealthReport.xlsx
+++ b/HealthReport.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF45CFF-FB3D-4560-83D3-D2B13E7ED167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A01C3E3-2861-4BC3-9046-B9D16283A824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HealthReport" sheetId="1" r:id="rId1"/>
@@ -358,7 +358,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="248">
   <si>
     <r>
       <rPr>
@@ -610,10 +610,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>闪回区使用</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>并行度&gt;1的表</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -754,10 +750,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>Recovery区使用检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>错误口令登录锁定检查</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -766,10 +758,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>实例名</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -824,9 +812,6 @@
     <t>Logmode</t>
   </si>
   <si>
-    <t>Flashback</t>
-  </si>
-  <si>
     <t>Dbtblcount</t>
   </si>
   <si>
@@ -836,9 +821,6 @@
     <t>Dbtbsusage</t>
   </si>
   <si>
-    <t>Dbredocheck</t>
-  </si>
-  <si>
     <t>Tmpfile_size</t>
   </si>
   <si>
@@ -881,15 +863,6 @@
     <t>Db_nosys_in_system</t>
   </si>
   <si>
-    <t>Dbrecoverydest</t>
-  </si>
-  <si>
-    <t>Dbflashrecoveryuseage</t>
-  </si>
-  <si>
-    <t>Dbproductuserfailedlogin</t>
-  </si>
-  <si>
     <t>Dbvirscheck</t>
   </si>
   <si>
@@ -956,15 +929,9 @@
     <t>Loadprofile</t>
   </si>
   <si>
-    <t>Instefficiency</t>
-  </si>
-  <si>
     <t>Topevent</t>
   </si>
   <si>
-    <t>Topsqlbyelapstime</t>
-  </si>
-  <si>
     <t>Dbpsu</t>
   </si>
   <si>
@@ -975,9 +942,6 @@
   </si>
   <si>
     <t>Dbparameter</t>
-  </si>
-  <si>
-    <t>Db_parameter_file</t>
   </si>
   <si>
     <t>Dbredoswitch</t>
@@ -1284,6 +1248,46 @@
   </si>
   <si>
     <t>Cursor_share_mem</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flashback</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dbredocheck</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪回区使用检查</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪回区使用DETAIL</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recovery_usage</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recovery_detail</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Userfailedlogin</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Db_parameter_file</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instefficiency</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Topsql_by_ela</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -1972,7 +1976,7 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2006,9 +2010,6 @@
     <xf numFmtId="7" fontId="4" fillId="4" borderId="1" xfId="9" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2021,9 +2022,6 @@
     <xf numFmtId="9" fontId="1" fillId="4" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2056,18 +2054,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="17" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="19" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
@@ -2112,9 +2098,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="14" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="13" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2178,9 +2161,6 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="21" fillId="6" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2189,9 +2169,6 @@
     </xf>
     <xf numFmtId="37" fontId="21" fillId="6" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2238,11 +2215,29 @@
     <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2297,7 +2292,12 @@
     <cellStyle name="货币[0]" xfId="11" builtinId="7" customBuiltin="1"/>
     <cellStyle name="超链接" xfId="14" builtinId="8" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -2427,15 +2427,15 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultTableStyle="College Checklist" defaultPivotStyle="PivotStyleLight16">
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="College Checklist" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="12"/>
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
     </tableStyle>
     <tableStyle name="Shopping List" pivot="0" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="9"/>
-      <tableStyleElement type="headerRow" dxfId="8"/>
+      <tableStyleElement type="wholeTable" dxfId="10"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2887,7 +2887,7 @@
             <c:numRef>
               <c:f>HealthReport!$L$27</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
               </c:numCache>
             </c:numRef>
@@ -2973,7 +2973,7 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3394,6 +3394,61 @@
             </a:sp3d>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>HealthReport!$C$15:$C$24</c:f>
@@ -3439,7 +3494,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -5232,11 +5287,11 @@
     <tabColor theme="2" tint="-0.249977111117893"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:P54"/>
+  <dimension ref="B1:P62"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="2" width="5.25" style="18" customWidth="1"/>
+    <col min="2" max="2" width="5.25" style="16" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="6" width="12.625" customWidth="1"/>
     <col min="7" max="7" width="6.375" customWidth="1"/>
@@ -5248,25 +5303,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="23"/>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="27" t="s">
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
     </row>
     <row r="2" spans="2:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14"/>
-      <c r="C2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="11"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -5278,7 +5333,7 @@
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="14"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -5295,87 +5350,87 @@
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="14"/>
-      <c r="C4" s="48" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="101" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="101"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="53" t="s">
+      <c r="D4" s="42"/>
+      <c r="E4" s="98" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" s="98"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="53"/>
-      <c r="J4" s="100" t="s">
+      <c r="I4" s="46"/>
+      <c r="J4" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="100"/>
+      <c r="K4" s="97"/>
       <c r="L4" s="8"/>
     </row>
     <row r="5" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="14"/>
-      <c r="C5" s="50" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="102" t="s">
-        <v>202</v>
-      </c>
-      <c r="F5" s="102"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="50" t="s">
+      <c r="D5" s="44"/>
+      <c r="E5" s="99" t="s">
+        <v>191</v>
+      </c>
+      <c r="F5" s="99"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="50"/>
-      <c r="J5" s="96" t="s">
-        <v>210</v>
-      </c>
-      <c r="K5" s="96"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="K5" s="93"/>
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="14"/>
-      <c r="C6" s="50" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="96" t="s">
-        <v>203</v>
-      </c>
-      <c r="F6" s="96"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="50" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="93" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="93"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="50"/>
-      <c r="J6" s="96" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="96"/>
+      <c r="K6" s="93"/>
       <c r="L6" s="8"/>
     </row>
     <row r="7" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="14"/>
-      <c r="C7" s="50" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="96" t="s">
-        <v>204</v>
-      </c>
-      <c r="F7" s="96"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="50"/>
-      <c r="J7" s="96" t="s">
+      <c r="D7" s="45"/>
+      <c r="E7" s="93" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="93"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="43"/>
+      <c r="J7" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="96"/>
+      <c r="K7" s="93"/>
       <c r="L7" s="8"/>
       <c r="P7" s="1">
         <f>19.8/12</f>
@@ -5383,83 +5438,83 @@
       </c>
     </row>
     <row r="8" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="14"/>
-      <c r="C8" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="50"/>
-      <c r="E8" s="99" t="s">
-        <v>205</v>
-      </c>
-      <c r="F8" s="96"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="I8" s="50"/>
-      <c r="J8" s="96" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="43"/>
+      <c r="E8" s="96" t="s">
+        <v>194</v>
+      </c>
+      <c r="F8" s="93"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="43"/>
+      <c r="J8" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="96"/>
+      <c r="K8" s="93"/>
       <c r="L8" s="8"/>
     </row>
     <row r="9" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="14"/>
-      <c r="C9" s="50" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="96" t="s">
-        <v>206</v>
-      </c>
-      <c r="F9" s="96"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="50" t="s">
+      <c r="D9" s="43"/>
+      <c r="E9" s="93" t="s">
+        <v>195</v>
+      </c>
+      <c r="F9" s="93"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="50"/>
-      <c r="J9" s="96" t="s">
+      <c r="I9" s="43"/>
+      <c r="J9" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="96"/>
+      <c r="K9" s="93"/>
       <c r="L9" s="8"/>
     </row>
     <row r="10" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="14"/>
-      <c r="C10" s="50" t="s">
-        <v>207</v>
-      </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="96" t="s">
-        <v>209</v>
-      </c>
-      <c r="F10" s="96"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="52" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" s="50"/>
-      <c r="J10" s="96" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="43"/>
+      <c r="E10" s="93" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="93"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="I10" s="43"/>
+      <c r="J10" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="K10" s="96"/>
+      <c r="K10" s="93"/>
       <c r="L10" s="8"/>
     </row>
     <row r="11" spans="2:16" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="14"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="97"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="95"/>
-      <c r="K11" s="95"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="92"/>
       <c r="L11" s="8"/>
     </row>
     <row r="12" spans="2:16" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="9"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -5472,7 +5527,7 @@
       <c r="L12" s="8"/>
     </row>
     <row r="13" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="5" t="s">
         <v>16</v>
       </c>
@@ -5490,15 +5545,15 @@
       <c r="L13" s="8"/>
     </row>
     <row r="14" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="15"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G14" s="8"/>
@@ -5509,15 +5564,15 @@
       <c r="L14" s="8"/>
     </row>
     <row r="15" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
-      <c r="C15" s="19" t="s">
-        <v>243</v>
+      <c r="B15" s="14"/>
+      <c r="C15" s="17" t="s">
+        <v>232</v>
       </c>
       <c r="D15" s="6">
         <v>0</v>
       </c>
       <c r="E15" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6">
         <v>0</v>
@@ -5530,9 +5585,9 @@
       <c r="L15" s="8"/>
     </row>
     <row r="16" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="15"/>
-      <c r="C16" s="19" t="s">
-        <v>244</v>
+      <c r="B16" s="14"/>
+      <c r="C16" s="17" t="s">
+        <v>233</v>
       </c>
       <c r="D16" s="6">
         <v>0</v>
@@ -5551,9 +5606,9 @@
       <c r="L16" s="8"/>
     </row>
     <row r="17" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="15"/>
-      <c r="C17" s="19" t="s">
-        <v>246</v>
+      <c r="B17" s="14"/>
+      <c r="C17" s="17" t="s">
+        <v>235</v>
       </c>
       <c r="D17" s="6">
         <v>0</v>
@@ -5572,9 +5627,9 @@
       <c r="L17" s="8"/>
     </row>
     <row r="18" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="15"/>
-      <c r="C18" s="19" t="s">
-        <v>247</v>
+      <c r="B18" s="14"/>
+      <c r="C18" s="17" t="s">
+        <v>236</v>
       </c>
       <c r="D18" s="6">
         <v>0</v>
@@ -5593,9 +5648,9 @@
       <c r="L18" s="8"/>
     </row>
     <row r="19" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
-      <c r="C19" s="19" t="s">
-        <v>239</v>
+      <c r="B19" s="14"/>
+      <c r="C19" s="17" t="s">
+        <v>228</v>
       </c>
       <c r="D19" s="6">
         <v>0</v>
@@ -5614,9 +5669,9 @@
       <c r="L19" s="8"/>
     </row>
     <row r="20" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="15"/>
-      <c r="C20" s="19" t="s">
-        <v>240</v>
+      <c r="B20" s="14"/>
+      <c r="C20" s="17" t="s">
+        <v>229</v>
       </c>
       <c r="D20" s="6">
         <v>0</v>
@@ -5635,9 +5690,9 @@
       <c r="L20" s="8"/>
     </row>
     <row r="21" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="15"/>
-      <c r="C21" s="19" t="s">
-        <v>241</v>
+      <c r="B21" s="14"/>
+      <c r="C21" s="17" t="s">
+        <v>230</v>
       </c>
       <c r="D21" s="6">
         <v>0</v>
@@ -5656,9 +5711,9 @@
       <c r="L21" s="8"/>
     </row>
     <row r="22" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="15"/>
-      <c r="C22" s="19" t="s">
-        <v>242</v>
+      <c r="B22" s="14"/>
+      <c r="C22" s="17" t="s">
+        <v>231</v>
       </c>
       <c r="D22" s="6">
         <v>0</v>
@@ -5677,9 +5732,9 @@
       <c r="L22" s="8"/>
     </row>
     <row r="23" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="15"/>
-      <c r="C23" s="19" t="s">
-        <v>245</v>
+      <c r="B23" s="14"/>
+      <c r="C23" s="17" t="s">
+        <v>234</v>
       </c>
       <c r="D23" s="6">
         <v>0</v>
@@ -5698,8 +5753,8 @@
       <c r="L23" s="8"/>
     </row>
     <row r="24" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="15"/>
-      <c r="C24" s="19" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="17" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="6">
@@ -5719,8 +5774,8 @@
       <c r="L24" s="8"/>
     </row>
     <row r="25" spans="2:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="15"/>
-      <c r="C25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="12"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -5732,7 +5787,7 @@
       <c r="L25" s="8"/>
     </row>
     <row r="26" spans="2:12" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="15"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="9"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
@@ -5745,569 +5800,673 @@
       <c r="L26" s="8"/>
     </row>
     <row r="27" spans="2:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="16"/>
+      <c r="B27" s="14"/>
       <c r="C27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
     </row>
     <row r="28" spans="2:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="73" t="s">
+      <c r="D28" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28" t="s">
+      <c r="E28" s="83"/>
+      <c r="F28" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="G28" s="69" t="s">
+      <c r="G28" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="30" t="s">
+      <c r="H28" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="47">
+      <c r="I28" s="82"/>
+      <c r="J28" s="82"/>
+      <c r="K28" s="87"/>
+      <c r="L28" s="88">
         <f>SUM(HealthReport!$F$29:$F$41)/130</f>
         <v>0.52307692307692311</v>
       </c>
     </row>
     <row r="29" spans="2:12" ht="38.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="34">
+      <c r="B29" s="28">
         <v>1</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="38">
+      <c r="E29" s="31"/>
+      <c r="F29" s="32">
         <v>10</v>
       </c>
-      <c r="G29" s="70" t="str" cm="1">
+      <c r="G29" s="62" t="str" cm="1">
         <f t="array" ref="G29">_xlfn.IFS(HealthReport!$F29&gt;=10,"PASS",HealthReport!$F29=8,"轻微",HealthReport!$F29=5,"普通",HealthReport!$F29=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H29" s="98"/>
-      <c r="I29" s="98"/>
-      <c r="J29" s="98"/>
-      <c r="K29" s="98"/>
-      <c r="L29" s="75" t="str">
+      <c r="H29" s="95"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="66" t="str">
         <f>HYPERLINK("#OS!B5","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
     <row r="30" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="39">
+      <c r="B30" s="33">
         <v>2</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="41" t="s">
+      <c r="D30" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="40"/>
-      <c r="F30" s="42">
+      <c r="E30" s="34"/>
+      <c r="F30" s="36">
         <v>10</v>
       </c>
-      <c r="G30" s="71" t="str" cm="1">
+      <c r="G30" s="63" t="str" cm="1">
         <f t="array" ref="G30">_xlfn.IFS(HealthReport!$F30&gt;=10,"PASS",HealthReport!$F30=8,"轻微",HealthReport!$F30=5,"普通",HealthReport!$F30=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H30" s="93"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="93"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="76" t="str">
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="67" t="str">
         <f>HYPERLINK("#OS!B5","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
     <row r="31" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="34">
+      <c r="B31" s="28">
         <v>3</v>
       </c>
-      <c r="C31" s="37" t="s">
+      <c r="C31" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="43" t="s">
+      <c r="D31" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="37"/>
-      <c r="F31" s="38">
+      <c r="E31" s="31"/>
+      <c r="F31" s="32">
         <v>10</v>
       </c>
-      <c r="G31" s="70" t="str" cm="1">
+      <c r="G31" s="62" t="str" cm="1">
         <f t="array" ref="G31">_xlfn.IFS(HealthReport!$F31&gt;=10,"PASS",HealthReport!$F31=8,"轻微",HealthReport!$F31=5,"普通",HealthReport!$F31=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H31" s="94"/>
-      <c r="I31" s="94"/>
-      <c r="J31" s="94"/>
-      <c r="K31" s="94"/>
-      <c r="L31" s="75" t="str">
+      <c r="H31" s="91"/>
+      <c r="I31" s="91"/>
+      <c r="J31" s="91"/>
+      <c r="K31" s="91"/>
+      <c r="L31" s="66" t="str">
         <f>HYPERLINK("#OS!B5","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="39">
+      <c r="B32" s="33">
         <v>4</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="41" t="s">
+      <c r="D32" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="40"/>
-      <c r="F32" s="42">
+      <c r="E32" s="34"/>
+      <c r="F32" s="36">
         <v>5</v>
       </c>
-      <c r="G32" s="71" t="str" cm="1">
+      <c r="G32" s="63" t="str" cm="1">
         <f t="array" ref="G32">_xlfn.IFS(HealthReport!$F32&gt;=10,"PASS",HealthReport!$F32=8,"轻微",HealthReport!$F32=5,"普通",HealthReport!$F32=0,"重要")</f>
         <v>普通</v>
       </c>
-      <c r="H32" s="93"/>
-      <c r="I32" s="93"/>
-      <c r="J32" s="93"/>
-      <c r="K32" s="93"/>
-      <c r="L32" s="76" t="str">
+      <c r="H32" s="90"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="67" t="str">
         <f>HYPERLINK("#OS!B5","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
     <row r="33" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="34">
+      <c r="B33" s="28">
         <v>5</v>
       </c>
-      <c r="C33" s="37" t="s">
+      <c r="C33" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="43" t="s">
+      <c r="D33" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="37"/>
-      <c r="F33" s="38">
+      <c r="E33" s="31"/>
+      <c r="F33" s="32">
         <v>10</v>
       </c>
-      <c r="G33" s="70" t="str" cm="1">
+      <c r="G33" s="62" t="str" cm="1">
         <f t="array" ref="G33">_xlfn.IFS(HealthReport!$F33&gt;=10,"PASS",HealthReport!$F33=8,"轻微",HealthReport!$F33=5,"普通",HealthReport!$F33=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H33" s="94"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="94"/>
-      <c r="K33" s="94"/>
-      <c r="L33" s="75" t="str">
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="66" t="str">
         <f t="shared" ref="L33:L41" si="0">HYPERLINK("#OS!A1","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
     <row r="34" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="39">
+      <c r="B34" s="33">
         <v>6</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="C34" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="41" t="s">
+      <c r="D34" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="42">
+      <c r="E34" s="34"/>
+      <c r="F34" s="36">
         <v>10</v>
       </c>
-      <c r="G34" s="71" t="str" cm="1">
+      <c r="G34" s="63" t="str" cm="1">
         <f t="array" ref="G34">_xlfn.IFS(HealthReport!$F34&gt;=10,"PASS",HealthReport!$F34=8,"轻微",HealthReport!$F34=5,"普通",HealthReport!$F34=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H34" s="93"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="93"/>
-      <c r="K34" s="93"/>
-      <c r="L34" s="76" t="str">
+      <c r="H34" s="90"/>
+      <c r="I34" s="90"/>
+      <c r="J34" s="90"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="67" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="34">
+      <c r="B35" s="28">
         <v>7</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="43" t="s">
+      <c r="D35" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="37"/>
-      <c r="F35" s="38">
+      <c r="E35" s="31"/>
+      <c r="F35" s="32">
         <v>8</v>
       </c>
-      <c r="G35" s="70" t="str" cm="1">
+      <c r="G35" s="62" t="str" cm="1">
         <f t="array" ref="G35">_xlfn.IFS(HealthReport!$F35&gt;=10,"PASS",HealthReport!$F35=8,"轻微",HealthReport!$F35=5,"普通",HealthReport!$F35=0,"重要")</f>
         <v>轻微</v>
       </c>
-      <c r="H35" s="94"/>
-      <c r="I35" s="94"/>
-      <c r="J35" s="94"/>
-      <c r="K35" s="94"/>
-      <c r="L35" s="75" t="str">
+      <c r="H35" s="91"/>
+      <c r="I35" s="91"/>
+      <c r="J35" s="91"/>
+      <c r="K35" s="91"/>
+      <c r="L35" s="66" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="39">
+      <c r="B36" s="33">
         <v>8</v>
       </c>
-      <c r="C36" s="40" t="s">
+      <c r="C36" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="41" t="s">
+      <c r="D36" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="40"/>
-      <c r="F36" s="42">
+      <c r="E36" s="34"/>
+      <c r="F36" s="36">
         <v>5</v>
       </c>
-      <c r="G36" s="71" t="str" cm="1">
+      <c r="G36" s="63" t="str" cm="1">
         <f t="array" ref="G36">_xlfn.IFS(HealthReport!$F36&gt;=10,"PASS",HealthReport!$F36=8,"轻微",HealthReport!$F36=5,"普通",HealthReport!$F36=0,"重要")</f>
         <v>普通</v>
       </c>
-      <c r="H36" s="93"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="93"/>
-      <c r="K36" s="93"/>
-      <c r="L36" s="76" t="str">
+      <c r="H36" s="90"/>
+      <c r="I36" s="90"/>
+      <c r="J36" s="90"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="67" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="34">
+      <c r="B37" s="28">
         <v>9</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="43" t="s">
+      <c r="D37" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="37"/>
-      <c r="F37" s="38">
+      <c r="E37" s="31"/>
+      <c r="F37" s="32">
         <v>0</v>
       </c>
-      <c r="G37" s="70" t="str" cm="1">
+      <c r="G37" s="62" t="str" cm="1">
         <f t="array" ref="G37">_xlfn.IFS(HealthReport!$F37&gt;=10,"PASS",HealthReport!$F37=8,"轻微",HealthReport!$F37=5,"普通",HealthReport!$F37=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H37" s="94"/>
-      <c r="I37" s="94"/>
-      <c r="J37" s="94"/>
-      <c r="K37" s="94"/>
-      <c r="L37" s="75" t="str">
+      <c r="H37" s="91"/>
+      <c r="I37" s="91"/>
+      <c r="J37" s="91"/>
+      <c r="K37" s="91"/>
+      <c r="L37" s="66" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="39">
+      <c r="B38" s="33">
         <v>10</v>
       </c>
-      <c r="C38" s="40" t="s">
+      <c r="C38" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="41" t="s">
+      <c r="D38" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="E38" s="40"/>
-      <c r="F38" s="42">
+      <c r="E38" s="34"/>
+      <c r="F38" s="36">
         <v>0</v>
       </c>
-      <c r="G38" s="71" t="str" cm="1">
+      <c r="G38" s="63" t="str" cm="1">
         <f t="array" ref="G38">_xlfn.IFS(HealthReport!$F38&gt;=10,"PASS",HealthReport!$F38=8,"轻微",HealthReport!$F38=5,"普通",HealthReport!$F38=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H38" s="93"/>
-      <c r="I38" s="93"/>
-      <c r="J38" s="93"/>
-      <c r="K38" s="93"/>
-      <c r="L38" s="76" t="str">
+      <c r="H38" s="90"/>
+      <c r="I38" s="90"/>
+      <c r="J38" s="90"/>
+      <c r="K38" s="90"/>
+      <c r="L38" s="67" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="34">
+      <c r="B39" s="28">
         <v>11</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="43" t="s">
+      <c r="D39" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="E39" s="37"/>
-      <c r="F39" s="38">
+      <c r="E39" s="31"/>
+      <c r="F39" s="32">
         <v>0</v>
       </c>
-      <c r="G39" s="70" t="str" cm="1">
+      <c r="G39" s="62" t="str" cm="1">
         <f t="array" ref="G39">_xlfn.IFS(HealthReport!$F39&gt;=10,"PASS",HealthReport!$F39=8,"轻微",HealthReport!$F39=5,"普通",HealthReport!$F39=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H39" s="94"/>
-      <c r="I39" s="94"/>
-      <c r="J39" s="94"/>
-      <c r="K39" s="94"/>
-      <c r="L39" s="75" t="str">
+      <c r="H39" s="91"/>
+      <c r="I39" s="91"/>
+      <c r="J39" s="91"/>
+      <c r="K39" s="91"/>
+      <c r="L39" s="66" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="39">
+      <c r="B40" s="33">
         <v>12</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="D40" s="41"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="42">
+      <c r="D40" s="35"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="36">
         <v>0</v>
       </c>
-      <c r="G40" s="71" t="str" cm="1">
+      <c r="G40" s="63" t="str" cm="1">
         <f t="array" ref="G40">_xlfn.IFS(HealthReport!$F40&gt;=10,"PASS",HealthReport!$F40=8,"轻微",HealthReport!$F40=5,"普通",HealthReport!$F40=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H40" s="93"/>
-      <c r="I40" s="93"/>
-      <c r="J40" s="93"/>
-      <c r="K40" s="93"/>
-      <c r="L40" s="76" t="str">
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="67" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="17">
+      <c r="B41" s="15">
         <v>13</v>
       </c>
-      <c r="C41" s="44" t="s">
+      <c r="C41" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="43"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="45">
+      <c r="D41" s="37"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="39">
         <v>0</v>
       </c>
-      <c r="G41" s="72" t="str" cm="1">
+      <c r="G41" s="64" t="str" cm="1">
         <f t="array" ref="G41">_xlfn.IFS(HealthReport!$F41&gt;=10,"PASS",HealthReport!$F41=8,"轻微",HealthReport!$F41=5,"普通",HealthReport!$F41=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H41" s="94" t="s">
-        <v>174</v>
-      </c>
-      <c r="I41" s="94"/>
-      <c r="J41" s="94"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="77" t="str">
+      <c r="H41" s="91" t="s">
+        <v>163</v>
+      </c>
+      <c r="I41" s="91"/>
+      <c r="J41" s="91"/>
+      <c r="K41" s="91"/>
+      <c r="L41" s="68" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
     </row>
     <row r="42" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="39"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="93"/>
-      <c r="I42" s="93"/>
-      <c r="J42" s="93"/>
-      <c r="K42" s="93"/>
-      <c r="L42" s="76"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="90"/>
+      <c r="I42" s="90"/>
+      <c r="J42" s="90"/>
+      <c r="K42" s="90"/>
+      <c r="L42" s="67"/>
     </row>
     <row r="43" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="17"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="45"/>
-      <c r="G43" s="72"/>
-      <c r="H43" s="94"/>
-      <c r="I43" s="94"/>
-      <c r="J43" s="94"/>
-      <c r="K43" s="94"/>
-      <c r="L43" s="77"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="64"/>
+      <c r="H43" s="91"/>
+      <c r="I43" s="91"/>
+      <c r="J43" s="91"/>
+      <c r="K43" s="91"/>
+      <c r="L43" s="68"/>
     </row>
     <row r="44" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="39"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="71"/>
-      <c r="H44" s="93"/>
-      <c r="I44" s="93"/>
-      <c r="J44" s="93"/>
-      <c r="K44" s="93"/>
-      <c r="L44" s="76"/>
+      <c r="B44" s="33"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="90"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="90"/>
+      <c r="K44" s="90"/>
+      <c r="L44" s="67"/>
     </row>
     <row r="45" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="17"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="72"/>
-      <c r="H45" s="94"/>
-      <c r="I45" s="94"/>
-      <c r="J45" s="94"/>
-      <c r="K45" s="94"/>
-      <c r="L45" s="77"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="64"/>
+      <c r="H45" s="91"/>
+      <c r="I45" s="91"/>
+      <c r="J45" s="91"/>
+      <c r="K45" s="91"/>
+      <c r="L45" s="68"/>
     </row>
     <row r="46" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="74"/>
-      <c r="C46" s="74"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="74"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="74"/>
-      <c r="H46" s="93"/>
-      <c r="I46" s="93"/>
-      <c r="J46" s="93"/>
-      <c r="K46" s="93"/>
-      <c r="L46" s="78"/>
+      <c r="B46" s="65"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="65"/>
+      <c r="H46" s="90"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="90"/>
+      <c r="K46" s="90"/>
+      <c r="L46" s="69"/>
     </row>
     <row r="47" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="17"/>
-      <c r="C47" s="44"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="72"/>
-      <c r="H47" s="94"/>
-      <c r="I47" s="94"/>
-      <c r="J47" s="94"/>
-      <c r="K47" s="94"/>
-      <c r="L47" s="77"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="91"/>
+      <c r="I47" s="91"/>
+      <c r="J47" s="91"/>
+      <c r="K47" s="91"/>
+      <c r="L47" s="68"/>
     </row>
     <row r="48" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="39"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="40"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="71"/>
-      <c r="H48" s="93"/>
-      <c r="I48" s="93"/>
-      <c r="J48" s="93"/>
-      <c r="K48" s="93"/>
-      <c r="L48" s="76"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="90"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="90"/>
+      <c r="K48" s="90"/>
+      <c r="L48" s="67"/>
     </row>
     <row r="49" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="17"/>
-      <c r="C49" s="44"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="44"/>
-      <c r="F49" s="45"/>
-      <c r="G49" s="72"/>
-      <c r="H49" s="94"/>
-      <c r="I49" s="94"/>
-      <c r="J49" s="94"/>
-      <c r="K49" s="94"/>
-      <c r="L49" s="77"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="64"/>
+      <c r="H49" s="91"/>
+      <c r="I49" s="91"/>
+      <c r="J49" s="91"/>
+      <c r="K49" s="91"/>
+      <c r="L49" s="68"/>
     </row>
     <row r="50" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="74"/>
-      <c r="C50" s="74"/>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="74"/>
-      <c r="H50" s="93"/>
-      <c r="I50" s="93"/>
-      <c r="J50" s="93"/>
-      <c r="K50" s="93"/>
-      <c r="L50" s="78"/>
+      <c r="B50" s="65"/>
+      <c r="C50" s="65"/>
+      <c r="D50" s="65"/>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
+      <c r="H50" s="90"/>
+      <c r="I50" s="90"/>
+      <c r="J50" s="90"/>
+      <c r="K50" s="90"/>
+      <c r="L50" s="69"/>
     </row>
     <row r="51" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="17"/>
-      <c r="C51" s="44"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="44"/>
-      <c r="F51" s="45"/>
-      <c r="G51" s="72"/>
-      <c r="H51" s="94"/>
-      <c r="I51" s="94"/>
-      <c r="J51" s="94"/>
-      <c r="K51" s="94"/>
-      <c r="L51" s="77"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="64"/>
+      <c r="H51" s="91"/>
+      <c r="I51" s="91"/>
+      <c r="J51" s="91"/>
+      <c r="K51" s="91"/>
+      <c r="L51" s="68"/>
     </row>
     <row r="52" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="39"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="40"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="71"/>
-      <c r="H52" s="93"/>
-      <c r="I52" s="93"/>
-      <c r="J52" s="93"/>
-      <c r="K52" s="93"/>
-      <c r="L52" s="76"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="90"/>
+      <c r="I52" s="90"/>
+      <c r="J52" s="90"/>
+      <c r="K52" s="90"/>
+      <c r="L52" s="67"/>
     </row>
     <row r="53" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="17"/>
-      <c r="C53" s="44"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="72"/>
-      <c r="H53" s="94"/>
-      <c r="I53" s="94"/>
-      <c r="J53" s="94"/>
-      <c r="K53" s="94"/>
-      <c r="L53" s="77"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="64"/>
+      <c r="H53" s="91"/>
+      <c r="I53" s="91"/>
+      <c r="J53" s="91"/>
+      <c r="K53" s="91"/>
+      <c r="L53" s="68"/>
     </row>
     <row r="54" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="74"/>
-      <c r="C54" s="74"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="93"/>
-      <c r="I54" s="93"/>
-      <c r="J54" s="93"/>
-      <c r="K54" s="93"/>
-      <c r="L54" s="78"/>
+      <c r="B54" s="65"/>
+      <c r="C54" s="65"/>
+      <c r="D54" s="65"/>
+      <c r="E54" s="65"/>
+      <c r="F54" s="65"/>
+      <c r="G54" s="65"/>
+      <c r="H54" s="90"/>
+      <c r="I54" s="90"/>
+      <c r="J54" s="90"/>
+      <c r="K54" s="90"/>
+      <c r="L54" s="69"/>
+    </row>
+    <row r="55" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="15"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="91"/>
+      <c r="I55" s="91"/>
+      <c r="J55" s="91"/>
+      <c r="K55" s="91"/>
+      <c r="L55" s="68"/>
+    </row>
+    <row r="56" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="33"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="90"/>
+      <c r="I56" s="90"/>
+      <c r="J56" s="90"/>
+      <c r="K56" s="90"/>
+      <c r="L56" s="67"/>
+    </row>
+    <row r="57" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="15"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="39"/>
+      <c r="G57" s="64"/>
+      <c r="H57" s="91"/>
+      <c r="I57" s="91"/>
+      <c r="J57" s="91"/>
+      <c r="K57" s="91"/>
+      <c r="L57" s="68"/>
+    </row>
+    <row r="58" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="65"/>
+      <c r="C58" s="65"/>
+      <c r="D58" s="65"/>
+      <c r="E58" s="65"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="65"/>
+      <c r="H58" s="90"/>
+      <c r="I58" s="90"/>
+      <c r="J58" s="90"/>
+      <c r="K58" s="90"/>
+      <c r="L58" s="69"/>
+    </row>
+    <row r="59" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="15"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="64"/>
+      <c r="H59" s="91"/>
+      <c r="I59" s="91"/>
+      <c r="J59" s="91"/>
+      <c r="K59" s="91"/>
+      <c r="L59" s="68"/>
+    </row>
+    <row r="60" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="33"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="63"/>
+      <c r="H60" s="90"/>
+      <c r="I60" s="90"/>
+      <c r="J60" s="90"/>
+      <c r="K60" s="90"/>
+      <c r="L60" s="67"/>
+    </row>
+    <row r="61" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="15"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="64"/>
+      <c r="H61" s="91"/>
+      <c r="I61" s="91"/>
+      <c r="J61" s="91"/>
+      <c r="K61" s="91"/>
+      <c r="L61" s="68"/>
+    </row>
+    <row r="62" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="65"/>
+      <c r="C62" s="65"/>
+      <c r="D62" s="65"/>
+      <c r="E62" s="65"/>
+      <c r="F62" s="65"/>
+      <c r="G62" s="65"/>
+      <c r="H62" s="90"/>
+      <c r="I62" s="90"/>
+      <c r="J62" s="90"/>
+      <c r="K62" s="90"/>
+      <c r="L62" s="69"/>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="42">
+  <mergeCells count="50">
     <mergeCell ref="H46:K46"/>
     <mergeCell ref="H43:K43"/>
     <mergeCell ref="H45:K45"/>
@@ -6350,58 +6509,70 @@
     <mergeCell ref="H49:K49"/>
     <mergeCell ref="H50:K50"/>
     <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H60:K60"/>
+    <mergeCell ref="H61:K61"/>
+    <mergeCell ref="H62:K62"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="H56:K56"/>
+    <mergeCell ref="H57:K57"/>
+    <mergeCell ref="H58:K58"/>
+    <mergeCell ref="H59:K59"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="B13:B26">
-    <cfRule type="notContainsBlanks" dxfId="7" priority="40">
+  <conditionalFormatting sqref="B13:B27">
+    <cfRule type="notContainsBlanks" dxfId="8" priority="63">
       <formula>LEN(TRIM(B13))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:C14">
-    <cfRule type="notContainsBlanks" dxfId="6" priority="41">
+    <cfRule type="notContainsBlanks" dxfId="7" priority="64">
       <formula>LEN(TRIM(B14))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:L12 J13:L19 H19 H20:L26">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="54">
+    <cfRule type="notContainsBlanks" dxfId="6" priority="77">
       <formula>LEN(TRIM(B12))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D27:L27">
+    <cfRule type="notContainsBlanks" dxfId="5" priority="1">
+      <formula>LEN(TRIM(D27))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G8:G11 G13:G21">
-    <cfRule type="notContainsBlanks" dxfId="4" priority="55">
+    <cfRule type="notContainsBlanks" dxfId="4" priority="78">
       <formula>LEN(TRIM(G8))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:H15">
-    <cfRule type="notContainsBlanks" dxfId="3" priority="47">
+    <cfRule type="notContainsBlanks" dxfId="3" priority="70">
       <formula>LEN(TRIM(H14))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:I18">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="53">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="76">
       <formula>LEN(TRIM(H16))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I15">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="44">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="67">
       <formula>LEN(TRIM(I13))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L11 P7">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="56">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="79">
       <formula>LEN(TRIM(L4))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="250" yWindow="706" count="13">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Title of this worksheet is in cells B1 through C1. Enter School Supplies in table starting in cell B8. Enter budget in cell C5" sqref="C1" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell C5. Shopping List Total in cell C6 and Remaining Cash in cell C7 are automatically calculated based on entries in Checklist table" sqref="H3:K3 E12:F14 C13:D14 C3:F3" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell at right" sqref="C4 C7 H4:I4 H7:I7 C15 C20" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in cell at right" sqref="C5 C8 H5:I5 H8:I8 C16:C18 C21" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in this cell" sqref="J5 D16:F18 D21:F21 D8:E8 J8 D5:E5" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in this cell" sqref="J4 D15:F15 D20:F20 D7:E7 J7 D4:E4" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in cell at right" sqref="C6 C22:C26 H6:I6 C19 H10:I12 C9:C12" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in this cell" sqref="F12 D19:F19 J6 D22:F26 J12:K12 J10:J11 D6:E6 D9:E12" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells E5 through H7" sqref="P7 H12:I12 G8:G21 C12:F12 L4:L11 H20:I26 H19 H13 H14:I14 H16:I18 H15 J12:L26" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
+  <dataValidations xWindow="250" yWindow="706" count="12">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell C5. Shopping List Total in cell C6 and Remaining Cash in cell C7 are automatically calculated based on entries in Checklist table" sqref="C13:D14 E12:F14" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell at right" sqref="C15 C20" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in cell at right" sqref="C16:C18 C21" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in this cell" sqref="D21:F21 D16:F18" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in this cell" sqref="D20:F20 D15:F15" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in cell at right" sqref="C12 C22:C26 H12:I12 C19" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in this cell" sqref="F12 D19:F19 D12:E12 D22:F26 J12:K12" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells E5 through H7" sqref="P7 H12:I12 J12:L26 C12:F12 L4:L11 H20:I26 H19 H13 H14:I14 H16:I18 H15 G12:G21" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Shopping details in table below. Category list is automatically updated from Category table" sqref="C27" xr:uid="{00000000-0002-0000-0000-00000A000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells below" sqref="H13" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C29:C41" xr:uid="{9A7EB216-EA1D-4A3D-B9E3-20B91A83DBC8}">
@@ -6421,7 +6592,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="27" id="{3AD485F5-512A-4830-BA74-F6B14C2FEF34}">
+          <x14:cfRule type="iconSet" priority="50" id="{3AD485F5-512A-4830-BA74-F6B14C2FEF34}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6440,7 +6611,7 @@
           <xm:sqref>B46:C46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="16" id="{0F123DC0-E9CB-494F-9537-5267D0443334}">
+          <x14:cfRule type="iconSet" priority="39" id="{0F123DC0-E9CB-494F-9537-5267D0443334}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6459,7 +6630,7 @@
           <xm:sqref>B50:C50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{C75CBC66-D7CA-4A28-8777-654881069477}">
+          <x14:cfRule type="iconSet" priority="28" id="{C75CBC66-D7CA-4A28-8777-654881069477}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6478,7 +6649,45 @@
           <xm:sqref>B54:C54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="26" id="{42B44E61-BD45-4B3B-A366-60DC3FA6E891}">
+          <x14:cfRule type="iconSet" priority="17" id="{88ED8CEC-2FA2-43DA-8ADA-0BDBE1D94E7F}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>B58:C58</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="6" id="{18D66B4D-9470-4F8E-B72C-CD2C03C24492}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>B62:C62</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="49" id="{42B44E61-BD45-4B3B-A366-60DC3FA6E891}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6497,7 +6706,7 @@
           <xm:sqref>D46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{14B6D97C-3FC8-4777-B197-85596580A20F}">
+          <x14:cfRule type="iconSet" priority="38" id="{14B6D97C-3FC8-4777-B197-85596580A20F}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6516,7 +6725,7 @@
           <xm:sqref>D50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{2B77CF01-0B59-4A94-968C-F819B9BFC886}">
+          <x14:cfRule type="iconSet" priority="27" id="{2B77CF01-0B59-4A94-968C-F819B9BFC886}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6535,7 +6744,45 @@
           <xm:sqref>D54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="25" id="{9AE0B0A0-31AC-419A-8920-AF3FF686551C}">
+          <x14:cfRule type="iconSet" priority="16" id="{6A110090-049C-450A-84FF-B5C33643E19C}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D58</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="5" id="{23025D6F-F171-4B0A-A495-741EF450595B}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D62</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="48" id="{9AE0B0A0-31AC-419A-8920-AF3FF686551C}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6554,7 +6801,7 @@
           <xm:sqref>E46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="14" id="{BAA9148E-4C74-4C1C-A14C-98B823C60A38}">
+          <x14:cfRule type="iconSet" priority="37" id="{BAA9148E-4C74-4C1C-A14C-98B823C60A38}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6573,7 +6820,7 @@
           <xm:sqref>E50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{A442FCE3-8944-4D53-8BFE-78C12683D968}">
+          <x14:cfRule type="iconSet" priority="26" id="{A442FCE3-8944-4D53-8BFE-78C12683D968}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6592,7 +6839,45 @@
           <xm:sqref>E54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="38" id="{D7E11CA3-AE2E-4AE0-8760-69AFD47E19CB}">
+          <x14:cfRule type="iconSet" priority="15" id="{085671F5-C388-48EA-B946-69A906653317}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>E58</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="4" id="{1CCBB599-0F02-4566-B4CA-822394CA31B8}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>E62</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="61" id="{D7E11CA3-AE2E-4AE0-8760-69AFD47E19CB}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6611,7 +6896,7 @@
           <xm:sqref>F29:F45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="24" id="{3D962523-5725-48F8-9A20-D1500F15E2BB}">
+          <x14:cfRule type="iconSet" priority="47" id="{3D962523-5725-48F8-9A20-D1500F15E2BB}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6630,7 +6915,7 @@
           <xm:sqref>F46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="21" id="{385FA039-B741-4960-9F2A-71D6C39C50C7}">
+          <x14:cfRule type="iconSet" priority="44" id="{385FA039-B741-4960-9F2A-71D6C39C50C7}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6649,7 +6934,7 @@
           <xm:sqref>F47:F49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{CCF709D9-2591-4DAA-9315-C7A0355D6EA8}">
+          <x14:cfRule type="iconSet" priority="36" id="{CCF709D9-2591-4DAA-9315-C7A0355D6EA8}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6668,7 +6953,7 @@
           <xm:sqref>F50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{EE2C29C5-1120-417B-89C1-A4074EDF4D05}">
+          <x14:cfRule type="iconSet" priority="33" id="{EE2C29C5-1120-417B-89C1-A4074EDF4D05}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6687,7 +6972,7 @@
           <xm:sqref>F51:F53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{382D81D0-7236-4E93-AC9C-80DF5A6DE10A}">
+          <x14:cfRule type="iconSet" priority="25" id="{382D81D0-7236-4E93-AC9C-80DF5A6DE10A}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6706,7 +6991,83 @@
           <xm:sqref>F54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="29" id="{EC29932F-78D6-4AC8-9D56-2F5F67B5688C}">
+          <x14:cfRule type="iconSet" priority="22" id="{2E2DF39E-FCE4-494D-9ED5-2A48DAC77F81}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>5</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>8</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Flags" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F55:F57</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="14" id="{88EB00A5-156B-492D-85CB-0C5859CC38ED}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F58</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="11" id="{330F031B-0D20-423C-A87C-02662C42927C}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>5</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>8</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Flags" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F59:F61</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="3" id="{2F58AE20-A011-429D-A34F-429BFA1C9011}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F62</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="52" id="{EC29932F-78D6-4AC8-9D56-2F5F67B5688C}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6725,7 +7086,7 @@
           <xm:sqref>G46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="17" id="{DEE3C81E-B484-4A72-9E13-E137E9862E3F}">
+          <x14:cfRule type="iconSet" priority="40" id="{DEE3C81E-B484-4A72-9E13-E137E9862E3F}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6744,7 +7105,7 @@
           <xm:sqref>G50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{9D2BC978-9B76-40DC-BBE3-4FE422176FDC}">
+          <x14:cfRule type="iconSet" priority="29" id="{9D2BC978-9B76-40DC-BBE3-4FE422176FDC}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6763,7 +7124,45 @@
           <xm:sqref>G54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="163" id="{904FC827-5D32-400A-97DB-D891D8D2E589}">
+          <x14:cfRule type="iconSet" priority="18" id="{2280D9D6-E10D-49C5-818E-A0E3B04DBFB6}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>G58</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="7" id="{64445DF7-6492-4705-84DA-BB6A157D4154}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>G62</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="186" id="{904FC827-5D32-400A-97DB-D891D8D2E589}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6782,7 +7181,7 @@
           <xm:sqref>H29:H42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="33" id="{63B576F9-8DAA-41CF-AE73-5AB45F4F4032}">
+          <x14:cfRule type="iconSet" priority="56" id="{63B576F9-8DAA-41CF-AE73-5AB45F4F4032}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6801,7 +7200,7 @@
           <xm:sqref>H43</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="31" id="{26C2D381-0C21-4A34-BF51-D0D70A2BBE5D}">
+          <x14:cfRule type="iconSet" priority="54" id="{26C2D381-0C21-4A34-BF51-D0D70A2BBE5D}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6820,7 +7219,7 @@
           <xm:sqref>H44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="32" id="{6416AA23-656B-4E60-B17B-E9CCF66906E3}">
+          <x14:cfRule type="iconSet" priority="55" id="{6416AA23-656B-4E60-B17B-E9CCF66906E3}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6839,7 +7238,7 @@
           <xm:sqref>H45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="23" id="{55F288BA-48B1-4F42-A62E-AAE73E9A550A}">
+          <x14:cfRule type="iconSet" priority="46" id="{55F288BA-48B1-4F42-A62E-AAE73E9A550A}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6858,7 +7257,7 @@
           <xm:sqref>H46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="20" id="{E30994DE-231B-4B68-996D-3E763907FA3C}">
+          <x14:cfRule type="iconSet" priority="43" id="{E30994DE-231B-4B68-996D-3E763907FA3C}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6877,7 +7276,7 @@
           <xm:sqref>H47</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="18" id="{5729C3FD-9889-4497-A536-FFF0436A57F1}">
+          <x14:cfRule type="iconSet" priority="41" id="{5729C3FD-9889-4497-A536-FFF0436A57F1}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6896,7 +7295,7 @@
           <xm:sqref>H48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="19" id="{40AFAEA4-3FCA-4567-9EEA-1BB8BD606A55}">
+          <x14:cfRule type="iconSet" priority="42" id="{40AFAEA4-3FCA-4567-9EEA-1BB8BD606A55}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6915,7 +7314,7 @@
           <xm:sqref>H49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{893EE127-E4CD-4D52-A058-33508E1A8A65}">
+          <x14:cfRule type="iconSet" priority="35" id="{893EE127-E4CD-4D52-A058-33508E1A8A65}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6934,7 +7333,7 @@
           <xm:sqref>H50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{E49E2337-1248-464F-93AA-524E7A88F776}">
+          <x14:cfRule type="iconSet" priority="32" id="{E49E2337-1248-464F-93AA-524E7A88F776}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6953,7 +7352,7 @@
           <xm:sqref>H51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{D4D8A87E-191B-49BE-8020-6766AF5D5BF4}">
+          <x14:cfRule type="iconSet" priority="30" id="{D4D8A87E-191B-49BE-8020-6766AF5D5BF4}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6972,7 +7371,7 @@
           <xm:sqref>H52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{58674D53-21A4-454B-A030-FB1AC98A28E7}">
+          <x14:cfRule type="iconSet" priority="31" id="{58674D53-21A4-454B-A030-FB1AC98A28E7}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -6991,7 +7390,7 @@
           <xm:sqref>H53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{2B6F2A62-C5BD-445A-8744-A65F0CE63FC7}">
+          <x14:cfRule type="iconSet" priority="24" id="{2B6F2A62-C5BD-445A-8744-A65F0CE63FC7}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -7010,7 +7409,159 @@
           <xm:sqref>H54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="164" id="{D6CA9112-E31E-493B-AC44-8CFD7A9AFAFB}">
+          <x14:cfRule type="iconSet" priority="21" id="{87964D9C-BBDE-4055-86C3-0325D9EE2A04}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H55</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="19" id="{78D85B58-EB6F-4BF5-A949-D6B9FB21DEC9}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H56</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="20" id="{4D437682-03CE-4E4E-AC65-5D0E0945D807}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H57</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="13" id="{231BF1BC-B7AB-433E-9409-D98755AF356D}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H58</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="10" id="{968DE5F6-A421-4C85-9FFB-E701ABD18091}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H59</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="8" id="{54B927FA-810D-48A4-A7FB-8B3F8831820E}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H60</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="9" id="{1FAD6668-9FA5-4FB1-A02D-65F6CC919842}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H61</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{7DFFAE32-F89E-40E5-BBB3-D2764C6A85A7}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H62</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="187" id="{D6CA9112-E31E-493B-AC44-8CFD7A9AFAFB}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -7029,7 +7580,7 @@
           <xm:sqref>L29:L45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="22" id="{807675E3-8123-408A-902D-C5F91F09F34C}">
+          <x14:cfRule type="iconSet" priority="45" id="{807675E3-8123-408A-902D-C5F91F09F34C}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -7048,7 +7599,7 @@
           <xm:sqref>L47:L49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{96A2AA7D-5F86-4DB5-9EFC-E3D5A371360F}">
+          <x14:cfRule type="iconSet" priority="34" id="{96A2AA7D-5F86-4DB5-9EFC-E3D5A371360F}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -7065,6 +7616,44 @@
             </x14:iconSet>
           </x14:cfRule>
           <xm:sqref>L51:L53</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="23" id="{8828D4DD-5476-49CF-88AD-0D99C48FF04B}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L55:L57</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="12" id="{1799AB56-073C-44A9-976B-79E653DC5E00}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L59:L61</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -7077,317 +7666,317 @@
   <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.125" style="84" customWidth="1"/>
-    <col min="2" max="2" width="18.375" style="87" customWidth="1"/>
-    <col min="3" max="4" width="90.625" style="56" customWidth="1"/>
-    <col min="5" max="5" width="9" style="32" customWidth="1"/>
-    <col min="6" max="28" width="70" style="32" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="33"/>
+    <col min="1" max="1" width="19.125" style="75" customWidth="1"/>
+    <col min="2" max="2" width="18.375" style="78" customWidth="1"/>
+    <col min="3" max="4" width="90.625" style="49" customWidth="1"/>
+    <col min="5" max="5" width="9" style="26" customWidth="1"/>
+    <col min="6" max="28" width="70" style="26" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="85" t="s">
-        <v>146</v>
-      </c>
-      <c r="C1" s="79"/>
-      <c r="D1" s="80"/>
+      <c r="A1" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="70"/>
+      <c r="D1" s="71"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="86" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="61"/>
+      <c r="B2" s="77" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="54"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="86" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="61"/>
+      <c r="B3" s="77" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="54"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
-        <v>208</v>
-      </c>
-      <c r="B4" s="86" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="81"/>
+      <c r="A4" s="74" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="77" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="72"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="86" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="61"/>
+      <c r="B5" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="51"/>
+      <c r="D5" s="54"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="83" t="s">
-        <v>175</v>
-      </c>
-      <c r="B6" s="86" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="62"/>
+      <c r="A6" s="74" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="77" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="51"/>
+      <c r="D6" s="55"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="86" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="46" t="str">
+      <c r="A7" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="77" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="51"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="40" t="str">
         <f>HYPERLINK("#HealthReport!B30","Retrun")</f>
         <v>Retrun</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="86" t="s">
-        <v>153</v>
-      </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="61"/>
+      <c r="B8" s="77" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="54"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="83" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="86" t="s">
+      <c r="A9" s="74" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="73"/>
+      <c r="D9" s="55"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="74" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="77" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="51"/>
+      <c r="D10" s="55"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="51"/>
+      <c r="D11" s="54"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="74" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="51"/>
+      <c r="D12" s="53"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="77" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="51"/>
+      <c r="D13" s="72"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="77" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" s="51"/>
+      <c r="D14" s="59"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="74" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="77" t="s">
+        <v>167</v>
+      </c>
+      <c r="C15" s="51"/>
+      <c r="D15" s="54"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="74" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="77" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="51"/>
+      <c r="D16" s="55"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="77" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" s="51"/>
+      <c r="D17" s="54"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="51"/>
+      <c r="D18" s="54"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="74" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="73"/>
+      <c r="D19" s="55"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="74" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" s="73"/>
+      <c r="D20" s="55"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="74" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="77" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" s="51"/>
+      <c r="D21" s="55"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="77" t="s">
+        <v>184</v>
+      </c>
+      <c r="C22" s="52"/>
+      <c r="D22" s="59"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="73"/>
+      <c r="D23" s="54"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="74" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" s="77" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="73"/>
+      <c r="D24" s="55"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="74" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" s="73"/>
+      <c r="D25" s="54"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="74" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="73"/>
+      <c r="D26" s="54"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="77" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="73"/>
+      <c r="D27" s="55"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="74" t="s">
+        <v>186</v>
+      </c>
+      <c r="B28" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="73"/>
+      <c r="D28" s="55"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="74" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="82"/>
-      <c r="D9" s="62"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="83" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="86" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="62"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="86" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="61"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="83" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="86" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="60"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="86" t="s">
-        <v>158</v>
-      </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="81"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="86" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="66"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="83" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="86" t="s">
+      <c r="B29" s="77" t="s">
         <v>178</v>
       </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="61"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="86" t="s">
-        <v>179</v>
-      </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="62"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="83" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="86" t="s">
-        <v>190</v>
-      </c>
-      <c r="C17" s="58"/>
-      <c r="D17" s="61"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="86" t="s">
-        <v>191</v>
-      </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="61"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="83" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="86" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" s="82"/>
-      <c r="D19" s="62"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="83" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="86" t="s">
-        <v>193</v>
-      </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="62"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="83" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="86" t="s">
-        <v>194</v>
-      </c>
-      <c r="C21" s="58"/>
-      <c r="D21" s="62"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="83" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="86" t="s">
-        <v>195</v>
-      </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="66"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="83" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="86" t="s">
-        <v>157</v>
-      </c>
-      <c r="C23" s="82"/>
-      <c r="D23" s="61"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="83" t="s">
-        <v>180</v>
-      </c>
-      <c r="B24" s="86" t="s">
-        <v>181</v>
-      </c>
-      <c r="C24" s="82"/>
-      <c r="D24" s="62"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="83" t="s">
-        <v>182</v>
-      </c>
-      <c r="B25" s="86" t="s">
-        <v>183</v>
-      </c>
-      <c r="C25" s="82"/>
-      <c r="D25" s="61"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="83" t="s">
-        <v>184</v>
-      </c>
-      <c r="B26" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="C26" s="82"/>
-      <c r="D26" s="61"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="83" t="s">
-        <v>196</v>
-      </c>
-      <c r="B27" s="86" t="s">
-        <v>186</v>
-      </c>
-      <c r="C27" s="82"/>
-      <c r="D27" s="62"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="83" t="s">
-        <v>197</v>
-      </c>
-      <c r="B28" s="86" t="s">
+      <c r="C29" s="73"/>
+      <c r="D29" s="55"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="74" t="s">
         <v>188</v>
       </c>
-      <c r="C28" s="82"/>
-      <c r="D28" s="62"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="83" t="s">
-        <v>198</v>
-      </c>
-      <c r="B29" s="86" t="s">
+      <c r="B30" s="77" t="s">
         <v>189</v>
       </c>
-      <c r="C29" s="82"/>
-      <c r="D29" s="62"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="83" t="s">
-        <v>199</v>
-      </c>
-      <c r="B30" s="86" t="s">
-        <v>200</v>
-      </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="62"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="55"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -7397,497 +7986,467 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965D7FAC-338D-40AE-9A03-D56E1C0E6070}">
-  <dimension ref="A1:AB48"/>
+  <dimension ref="A1:AB45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="84" customWidth="1"/>
-    <col min="2" max="2" width="20" style="89" customWidth="1"/>
-    <col min="3" max="4" width="90.625" style="56" customWidth="1"/>
-    <col min="5" max="27" width="87.5" style="32" customWidth="1"/>
-    <col min="28" max="16384" width="9" style="33"/>
+    <col min="1" max="1" width="25.5" style="75" customWidth="1"/>
+    <col min="2" max="2" width="20" style="80" customWidth="1"/>
+    <col min="3" max="4" width="90.625" style="49" customWidth="1"/>
+    <col min="5" max="27" width="87.5" style="26" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="50"/>
+      <c r="D1" s="53"/>
+      <c r="AB1" s="26"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="76" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="54"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="55"/>
+      <c r="AB3" s="26"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="74" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="76" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="88" t="s">
-        <v>146</v>
-      </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="60"/>
-      <c r="AB1" s="32"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="85" t="s">
+      <c r="C4" s="52"/>
+      <c r="D4" s="55"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="76" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="61"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="86" t="s">
+      <c r="C5" s="52"/>
+      <c r="D5" s="55"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="76" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="62"/>
-      <c r="AB3" s="32"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
+      <c r="C6" s="52"/>
+      <c r="D6" s="55"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B7" s="76" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="62"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="C7" s="52"/>
+      <c r="D7" s="55"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="74" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="76" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="52"/>
+      <c r="D8" s="55"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="74" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="55"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="76" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="55"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="55"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="76" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="55"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="74" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="76" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="52"/>
+      <c r="D13" s="55"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="76" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="52"/>
+      <c r="D14" s="55"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="76" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="52"/>
+      <c r="D15" s="55"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="76" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="55"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="55"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="74" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="76" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="52"/>
+      <c r="D18" s="55"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="52"/>
+      <c r="D19" s="55"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="74" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="76" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="52"/>
+      <c r="D20" s="55"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="52"/>
+      <c r="D21" s="55"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="79" t="s">
+        <v>213</v>
+      </c>
+      <c r="C22" s="52"/>
+      <c r="D22" s="55"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="79" t="s">
+        <v>211</v>
+      </c>
+      <c r="C23" s="52"/>
+      <c r="D23" s="55"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="79" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" s="52"/>
+      <c r="D24" s="55"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="79" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="52"/>
+      <c r="D25" s="55"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="74" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="79" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="52"/>
+      <c r="D26" s="55"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="85" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="62"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="83" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="62"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="85" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="59"/>
-      <c r="D7" s="62"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="85" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="62"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="83" t="s">
+      <c r="B27" s="79" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="52"/>
+      <c r="D27" s="55"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="74" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="79" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="52"/>
+      <c r="D28" s="55"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="79" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="52"/>
+      <c r="D29" s="55"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="79" t="s">
+        <v>215</v>
+      </c>
+      <c r="C30" s="52"/>
+      <c r="D30" s="55"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="79" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" s="52"/>
+      <c r="D31" s="55"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="79" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="52"/>
+      <c r="D32" s="55"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="52"/>
+      <c r="D33" s="55"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="79" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="52"/>
+      <c r="D34" s="55"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="79" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="52"/>
+      <c r="D35" s="55"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="79" t="s">
+        <v>244</v>
+      </c>
+      <c r="C36" s="52"/>
+      <c r="D36" s="55"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" s="52"/>
+      <c r="D37" s="55"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="52"/>
+      <c r="D38" s="55"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="52"/>
+      <c r="D39" s="55"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="74" t="s">
+        <v>217</v>
+      </c>
+      <c r="B40" s="79" t="s">
         <v>216</v>
       </c>
-      <c r="B9" s="85" t="s">
-        <v>212</v>
-      </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="62"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="83" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>213</v>
-      </c>
-      <c r="C10" s="59"/>
-      <c r="D10" s="62"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="85" t="s">
-        <v>214</v>
-      </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="62"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="83" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="85" t="s">
-        <v>215</v>
-      </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="62"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="83" t="s">
+      <c r="C40" s="52"/>
+      <c r="D40" s="55"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="74" t="s">
+        <v>227</v>
+      </c>
+      <c r="B41" s="79" t="s">
+        <v>226</v>
+      </c>
+      <c r="C41" s="50"/>
+      <c r="D41" s="53"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="B13" s="85" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="62"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="85" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="62"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="83" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="85" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="59"/>
-      <c r="D15" s="62"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="83" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="59"/>
-      <c r="D16" s="62"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="83" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" s="85" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="62"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" s="85" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="62"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="83" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="85" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="62"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="83" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="85" t="s">
+      <c r="B42" s="79" t="s">
+        <v>225</v>
+      </c>
+      <c r="C42" s="56"/>
+      <c r="D42" s="57"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" s="79" t="s">
+        <v>224</v>
+      </c>
+      <c r="C43" s="52"/>
+      <c r="D43" s="55"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="74" t="s">
         <v>220</v>
       </c>
-      <c r="C20" s="59"/>
-      <c r="D20" s="62"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="83" t="s">
-        <v>81</v>
-      </c>
-      <c r="B21" s="85" t="s">
-        <v>127</v>
-      </c>
-      <c r="C21" s="59"/>
-      <c r="D21" s="62"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="85" t="s">
+      <c r="B44" s="79" t="s">
+        <v>223</v>
+      </c>
+      <c r="C44" s="50"/>
+      <c r="D44" s="53"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="74" t="s">
         <v>221</v>
       </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="62"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="83" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="88" t="s">
-        <v>224</v>
-      </c>
-      <c r="C23" s="59"/>
-      <c r="D23" s="62"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="83" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="88" t="s">
+      <c r="B45" s="79" t="s">
         <v>222</v>
       </c>
-      <c r="C24" s="59"/>
-      <c r="D24" s="62"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="83" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="C25" s="59"/>
-      <c r="D25" s="62"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="88" t="s">
-        <v>225</v>
-      </c>
-      <c r="C26" s="59"/>
-      <c r="D26" s="62"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="B27" s="88" t="s">
-        <v>129</v>
-      </c>
-      <c r="C27" s="59"/>
-      <c r="D27" s="62"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="83" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" s="88" t="s">
-        <v>130</v>
-      </c>
-      <c r="C28" s="59"/>
-      <c r="D28" s="62"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="83" t="s">
-        <v>90</v>
-      </c>
-      <c r="B29" s="88" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="59"/>
-      <c r="D29" s="62"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="83" t="s">
-        <v>94</v>
-      </c>
-      <c r="B30" s="88" t="s">
-        <v>132</v>
-      </c>
-      <c r="C30" s="59"/>
-      <c r="D30" s="62"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="83" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="88" t="s">
-        <v>226</v>
-      </c>
-      <c r="C31" s="59"/>
-      <c r="D31" s="62"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="83" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="88" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="59"/>
-      <c r="D32" s="62"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="83" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="88" t="s">
-        <v>134</v>
-      </c>
-      <c r="C33" s="59"/>
-      <c r="D33" s="62"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="88" t="s">
-        <v>135</v>
-      </c>
-      <c r="C34" s="59"/>
-      <c r="D34" s="62"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="83" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="88" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" s="59"/>
-      <c r="D35" s="62"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="83" t="s">
-        <v>99</v>
-      </c>
-      <c r="B36" s="88" t="s">
-        <v>137</v>
-      </c>
-      <c r="C36" s="59"/>
-      <c r="D36" s="62"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="83" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" s="88" t="s">
-        <v>138</v>
-      </c>
-      <c r="C37" s="59"/>
-      <c r="D37" s="62"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="B38" s="88" t="s">
-        <v>139</v>
-      </c>
-      <c r="C38" s="59"/>
-      <c r="D38" s="62"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="83" t="s">
-        <v>101</v>
-      </c>
-      <c r="B39" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="C39" s="59"/>
-      <c r="D39" s="62"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="83" t="s">
-        <v>102</v>
-      </c>
-      <c r="B40" s="88" t="s">
-        <v>141</v>
-      </c>
-      <c r="C40" s="59"/>
-      <c r="D40" s="62"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="83" t="s">
-        <v>70</v>
-      </c>
-      <c r="B41" s="88" t="s">
-        <v>142</v>
-      </c>
-      <c r="C41" s="59"/>
-      <c r="D41" s="62"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="83" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="88" t="s">
-        <v>143</v>
-      </c>
-      <c r="C42" s="59"/>
-      <c r="D42" s="62"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="83" t="s">
-        <v>228</v>
-      </c>
-      <c r="B43" s="88" t="s">
-        <v>227</v>
-      </c>
-      <c r="C43" s="59"/>
-      <c r="D43" s="62"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="83" t="s">
-        <v>238</v>
-      </c>
-      <c r="B44" s="88" t="s">
-        <v>237</v>
-      </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="60"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="83" t="s">
-        <v>229</v>
-      </c>
-      <c r="B45" s="88" t="s">
-        <v>236</v>
-      </c>
-      <c r="C45" s="63"/>
-      <c r="D45" s="64"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="83" t="s">
-        <v>230</v>
-      </c>
-      <c r="B46" s="88" t="s">
-        <v>235</v>
-      </c>
-      <c r="C46" s="59"/>
-      <c r="D46" s="62"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="83" t="s">
-        <v>231</v>
-      </c>
-      <c r="B47" s="88" t="s">
-        <v>234</v>
-      </c>
-      <c r="C47" s="57"/>
-      <c r="D47" s="60"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="83" t="s">
-        <v>232</v>
-      </c>
-      <c r="B48" s="88" t="s">
-        <v>233</v>
-      </c>
-      <c r="C48" s="63"/>
-      <c r="D48" s="64"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="57"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -7897,278 +8456,375 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81493CED-92E7-4A64-BF87-00E3B3B76718}">
-  <dimension ref="A1:AB17"/>
+  <dimension ref="A1:AB20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.125" style="90" customWidth="1"/>
+    <col min="1" max="1" width="14.125" style="81" customWidth="1"/>
     <col min="2" max="2" width="15.625" customWidth="1"/>
-    <col min="3" max="4" width="102.625" style="55" customWidth="1"/>
+    <col min="3" max="4" width="102.625" style="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
+    <row r="1" spans="1:28" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="51"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="74" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="59"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="74" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="74" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="59"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="74" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="58"/>
+      <c r="D5" s="59"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" s="74" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" s="58"/>
+      <c r="D6" s="59"/>
+    </row>
+    <row r="7" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+      <c r="A7" s="74" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="58"/>
+      <c r="D7" s="59"/>
+    </row>
+    <row r="8" spans="1:28" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="58"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="26"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="26"/>
+      <c r="X8" s="26"/>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="26"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="74" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="58"/>
+      <c r="D9" s="59"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B10" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="58"/>
+      <c r="D10" s="59"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="74" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" s="58"/>
+      <c r="D11" s="59"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="58"/>
+      <c r="D12" s="59"/>
+    </row>
+    <row r="13" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+      <c r="A13" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+    </row>
+    <row r="14" spans="1:28" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="C14" s="52"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="26"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="26"/>
+      <c r="AA14" s="26"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+    </row>
+    <row r="16" spans="1:28" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="74" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" s="79" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="26"/>
+      <c r="W16" s="26"/>
+      <c r="X16" s="26"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="26"/>
+      <c r="AA16" s="26"/>
+    </row>
+    <row r="17" spans="1:27" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="74" t="s">
+        <v>241</v>
+      </c>
+      <c r="B17" s="79" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="26"/>
+      <c r="S17" s="26"/>
+      <c r="T17" s="26"/>
+      <c r="U17" s="26"/>
+      <c r="V17" s="26"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="26"/>
+      <c r="Y17" s="26"/>
+      <c r="Z17" s="26"/>
+      <c r="AA17" s="26"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" s="74" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="66"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="54" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="66"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="66"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="66"/>
-    </row>
-    <row r="6" spans="1:28" ht="27" x14ac:dyDescent="0.25">
-      <c r="A6" s="83" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66"/>
-    </row>
-    <row r="7" spans="1:28" ht="27" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" s="54" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="66"/>
-    </row>
-    <row r="8" spans="1:28" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
-        <v>211</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="65"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-      <c r="O8" s="32"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="32"/>
-      <c r="R8" s="32"/>
-      <c r="S8" s="32"/>
-      <c r="T8" s="32"/>
-      <c r="U8" s="32"/>
-      <c r="V8" s="32"/>
-      <c r="W8" s="32"/>
-      <c r="X8" s="32"/>
-      <c r="Y8" s="32"/>
-      <c r="Z8" s="32"/>
-      <c r="AA8" s="32"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="83" t="s">
-        <v>159</v>
-      </c>
-      <c r="B9" s="54" t="s">
-        <v>165</v>
-      </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="66"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="83" t="s">
-        <v>107</v>
-      </c>
-      <c r="B10" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="66"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>167</v>
-      </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="66"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="83" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>168</v>
-      </c>
-      <c r="C12" s="65" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="66"/>
-    </row>
-    <row r="13" spans="1:28" ht="27" x14ac:dyDescent="0.25">
-      <c r="A13" s="83" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="54" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="66"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>170</v>
-      </c>
-      <c r="C14" s="91"/>
-      <c r="D14" s="92"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="83" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="54" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="67"/>
-      <c r="D15" s="68"/>
-    </row>
-    <row r="16" spans="1:28" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="83" t="s">
+      <c r="C18" s="60"/>
+      <c r="D18" s="61"/>
+    </row>
+    <row r="19" spans="1:27" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="52"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="26"/>
+      <c r="U19" s="26"/>
+      <c r="V19" s="26"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="26"/>
+      <c r="Y19" s="26"/>
+      <c r="Z19" s="26"/>
+      <c r="AA19" s="26"/>
+    </row>
+    <row r="20" spans="1:27" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="74" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="54" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="59"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="32"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="32"/>
-      <c r="AA16" s="32"/>
-    </row>
-    <row r="17" spans="1:27" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="54" t="s">
-        <v>145</v>
-      </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="32"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="32"/>
-      <c r="V17" s="32"/>
-      <c r="W17" s="32"/>
-      <c r="X17" s="32"/>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="32"/>
-      <c r="AA17" s="32"/>
+      <c r="B20" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="52"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
+      <c r="S20" s="26"/>
+      <c r="T20" s="26"/>
+      <c r="U20" s="26"/>
+      <c r="V20" s="26"/>
+      <c r="W20" s="26"/>
+      <c r="X20" s="26"/>
+      <c r="Y20" s="26"/>
+      <c r="Z20" s="26"/>
+      <c r="AA20" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -8177,35 +8833,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac37c1753acd5e330d2062ccec26ea66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b340c7101c92c5120abd06486f94548" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8505,27 +9132,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D4997A-F5D7-47B8-8021-08C076C5E1C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1BB4A4-C009-44B7-9F89-7FA7A7BF749B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98E7F3D6-785F-49FE-8501-BF769B99AE88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8546,6 +9182,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D4997A-F5D7-47B8-8021-08C076C5E1C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1BB4A4-C009-44B7-9F89-7FA7A7BF749B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/HealthReport.xlsx
+++ b/HealthReport.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A01C3E3-2861-4BC3-9046-B9D16283A824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC982250-5546-429A-86B7-10C8F503FE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,302 +39,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>作者</author>
-  </authors>
-  <commentList>
-    <comment ref="D29" authorId="0" shapeId="0" xr:uid="{9E41461E-B5F3-45AE-9099-A170B522429B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-查看主机负载情况,id为空闲时间百分比,值越高负载越小</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D30" authorId="0" shapeId="0" xr:uid="{CE8FA50E-BD3B-4973-83DB-480955872E6D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-查看内存是否频繁使用换页SWAP</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{BD3948E2-8A4C-436C-A251-46605C2AC180}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-查看主机IO及磁盘IO负载情况, 当有磁盘%util 超过85%时说明该磁盘非常繁忙, 需要进一步分析或优化IO负载</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D32" authorId="0" shapeId="0" xr:uid="{219BEDE6-F20F-41C0-8CEA-3DD317C4798C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-查看文件系统使用率,文件系统使用率小于80%为正常</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D33" authorId="0" shapeId="0" xr:uid="{6038BBA1-4371-4944-962E-EF8DAAF1E365}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-查看文件系统索引资源节点使用率小于80%为正常</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D34" authorId="0" shapeId="0" xr:uid="{72672DE2-604C-4E12-8D14-22FBCC7B2E8D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-查看主机透明大页配置情况,为提升系统稳定性建议关闭透明在大页</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{021971E8-0EF3-4147-A1FE-688FB0860E9A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-查看主机内核参数配置情况</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D36" authorId="0" shapeId="0" xr:uid="{388B4670-C978-444C-9E73-9808F46CB808}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-查看用户主机资源限制配置情况</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D37" authorId="0" shapeId="0" xr:uid="{C950E487-9BBE-47CD-837E-BFC7232D63DC}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-查看主机NUMA状态,NUMA特性会对数据库服务器稳定运行带来非常大的影响,为避免系统性能隐患,建议关闭NUMA</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D38" authorId="0" shapeId="0" xr:uid="{CAEAB304-D48F-42EF-854C-6ADD0CDE7561}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-数据库状态检查主要包括：数据库启动状态,Dataguard保护模式,保护级别,数据库角色等</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D39" authorId="0" shapeId="0" xr:uid="{25822FDF-1644-4F43-898F-A6C8A5398052}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-针对表空间使用率超过80%且剩余空间不足8G,进行预警</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
@@ -358,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="144">
   <si>
     <r>
       <rPr>
@@ -462,18 +166,6 @@
     <t>主机系统分析</t>
   </si>
   <si>
-    <t>数据库实例分析</t>
-  </si>
-  <si>
-    <t>其他项检查</t>
-  </si>
-  <si>
-    <t>数据库安全检查</t>
-  </si>
-  <si>
-    <t>数据库备份检查</t>
-  </si>
-  <si>
     <t>检查项</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -482,34 +174,14 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>内存使用检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>文件系统使用率</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>索引资源节点使用率</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机透明大页检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>内核参数</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>资源限制</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库状态检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>表空间使用率</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -522,14 +194,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>磁盘IO负载检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>NUMA使用检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>普通</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -606,34 +270,10 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>数据库日志检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>并行度&gt;1的表</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>DBA权限用户检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>SYSDBA权限用户检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库审计空间检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库审计对象检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>SCNHealthCheck检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>并行度&gt;1的索引</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -662,10 +302,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>数据文件状态检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>用户大小</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -678,30 +314,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>REDO文件检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>RMAN备份检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>DG同步延迟检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>DG同步报错检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUENCE设置检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUENCE使用检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>数据库状态</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -722,42 +334,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>游标&gt;300M检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户临期检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>PROFILE密码函数设置</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>无效对象检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>索引失效检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>控制文件冗余检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>业务使用系统表空间检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>错误口令登录锁定检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>病毒勒索攻击隐患检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>实例名</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -778,10 +354,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>归档切换检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>数据库运行效率</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -790,166 +362,10 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>节点</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dbname</t>
-  </si>
-  <si>
-    <t>Dbmaa</t>
-  </si>
-  <si>
-    <t>Dbver</t>
-  </si>
-  <si>
-    <t>Dbstatus</t>
-  </si>
-  <si>
-    <t>Dblang</t>
-  </si>
-  <si>
-    <t>Logmode</t>
-  </si>
-  <si>
-    <t>Dbtblcount</t>
-  </si>
-  <si>
-    <t>Dbrole</t>
-  </si>
-  <si>
-    <t>Dbtbsusage</t>
-  </si>
-  <si>
-    <t>Tmpfile_size</t>
-  </si>
-  <si>
-    <t>Dbcontrolfile</t>
-  </si>
-  <si>
-    <t>User_info</t>
-  </si>
-  <si>
-    <t>Tab_info</t>
-  </si>
-  <si>
-    <t>Dbresource</t>
-  </si>
-  <si>
-    <t>Db_seq_usage</t>
-  </si>
-  <si>
-    <t>Dboption</t>
-  </si>
-  <si>
-    <t>Dbfeatures</t>
-  </si>
-  <si>
-    <t>Db_expir_user</t>
-  </si>
-  <si>
-    <t>Dbdbapriv</t>
-  </si>
-  <si>
-    <t>Dbsysdba</t>
-  </si>
-  <si>
-    <t>Dbauditsegment</t>
-  </si>
-  <si>
-    <t>Dbauditcont</t>
-  </si>
-  <si>
-    <t>Db_nosys_in_system</t>
-  </si>
-  <si>
-    <t>Dbvirscheck</t>
-  </si>
-  <si>
-    <t>Dbscnhealthcheck</t>
-  </si>
-  <si>
-    <t>Dbrmancheck</t>
-  </si>
-  <si>
-    <t>Dbdglagcheck</t>
-  </si>
-  <si>
-    <t>Dbdgerrcheck</t>
-  </si>
-  <si>
-    <t>NodeID</t>
-  </si>
-  <si>
-    <t>Hostname</t>
-  </si>
-  <si>
-    <t>Ipaddr</t>
-  </si>
-  <si>
-    <t>Os</t>
-  </si>
-  <si>
-    <t>Relver</t>
-  </si>
-  <si>
-    <t>Cores</t>
-  </si>
-  <si>
-    <t>Cpumhz</t>
-  </si>
-  <si>
-    <t>Memtotal</t>
-  </si>
-  <si>
-    <t>Swaptotal</t>
-  </si>
-  <si>
-    <t>Osparameter</t>
-  </si>
-  <si>
-    <t>Ulimit</t>
-  </si>
-  <si>
-    <t>Tmzone</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Oslog</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>PSU&amp;RU</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>Instname</t>
-  </si>
-  <si>
-    <t>Loadprofile</t>
-  </si>
-  <si>
-    <t>Topevent</t>
-  </si>
-  <si>
-    <t>Dbpsu</t>
-  </si>
-  <si>
-    <t>Dbpatch</t>
-  </si>
-  <si>
-    <t>Dblsnrinfo</t>
-  </si>
-  <si>
-    <t>Dbparameter</t>
-  </si>
-  <si>
-    <t>Dbredoswitch</t>
-  </si>
-  <si>
-    <t>Dberrlog</t>
-  </si>
-  <si>
     <t>Top等待</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -958,10 +374,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>****</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>CPU Info</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -970,99 +382,11 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>Filesystem</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inodeusage</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cpustat</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>Selinux状态</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>Selinux</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>防火墙状态</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Firewall</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>NSSwitch配置检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nsswitch</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lo_mtu</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Machine_platform</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU_PERF_MODE</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>NOZEROCONF</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Memstat</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Iostat</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thpstat</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hugpage</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Numa</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ntp</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>lo网卡MTU检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU性能模式检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZEROCONF路由检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>安全漏洞RPM包检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>RPM_PACKAGES</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
@@ -1102,192 +426,212 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>资源使用检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dbcursize</t>
-  </si>
-  <si>
-    <t>Dbf_size</t>
-  </si>
-  <si>
-    <t>Dbf_cnt</t>
-  </si>
-  <si>
-    <t>Dbf_stat</t>
-  </si>
-  <si>
-    <t>数据库当前使用大小</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>数据文件总大小</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>临时表空间文件大小</t>
+    <t>集群资源状态</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCR状态</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASM磁盘组使用率</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库集群</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataGuard</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库备份</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库安全</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机系统</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库分析</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件使用</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>实例分析</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库性能</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>数据库大小
-(当前已使用)</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>User_size</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>TAB_PARALLEL</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>INVALID_OBJ</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>INVALID_INX</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>INX_PARALLEL</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dbsequence</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Db_password_verif</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crs_stat</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>集群资源状态</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>OCR状态</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>OCR备份检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASM磁盘组使用率</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASM磁盘偏移检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Asm_offset</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Asm_usage</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ocr_bak_check</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ocr_info</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crs_stat2</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>集群资源状态检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库集群</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>DataGuard</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库备份</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库安全</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机系统</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库分析</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>软件使用</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>实例分析</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库性能</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cursor_share_mem</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Flashback</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dbredocheck</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪回区使用检查</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪回区使用DETAIL</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Recovery_usage</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Recovery_detail</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Userfailedlogin</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Db_parameter_file</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instefficiency</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>Topsql_by_ela</t>
+(已使用GB)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否归档</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Result</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check Item</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>RPM安全漏洞包</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZEROCONF路由</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU性能模式</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>lo网卡MTU</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>NSSwitch配置</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据文件状态</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制文件冗余</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUENCE设置</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUENCE使用</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>无效对象</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引失效</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户临期</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>DBA权限用户</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYSDBA权限用户</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库审计空间</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库审计对象</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务使用系统表空间</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误口令登录锁定</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>病毒勒索攻击隐患</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCNHealthCheck</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>RMAN备份</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCR备份</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASM磁盘偏移</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>PROFILE密码函数</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时表空间文件</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库当前使用</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>REDO文件</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>归档切换</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪回区使用</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库日志</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG同步延迟</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG同步报错</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪回区空间</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>游标&gt;300M</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大资源使用</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -1295,11 +639,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="3"/>
@@ -1481,21 +826,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1514,13 +844,6 @@
       <color theme="0"/>
       <name val="宋体"/>
       <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFE6E6FA"/>
-      <name val="幼圆"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1544,8 +867,49 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cascadia Code Light"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
@@ -1553,30 +917,16 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFE6E6FA"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <color theme="3"/>
+      <name val="Microsoft YaHei Light"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color theme="1"/>
-      <name val="Cascadia Code Light"/>
-      <family val="3"/>
+      <name val="Corbel"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1628,7 +978,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1722,48 +1072,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="slantDashDot">
-        <color rgb="FFD8EFF1"/>
-      </left>
-      <right style="thin">
         <color theme="6"/>
-      </right>
-      <top style="slantDashDot">
-        <color rgb="FFD8EFF1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color theme="6"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
       </left>
       <right style="thin">
         <color theme="6"/>
@@ -1775,74 +1084,27 @@
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color theme="6"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="2" tint="-0.499984740745262"/>
       </top>
-      <bottom/>
+      <bottom style="dotted">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color theme="6"/>
-      </right>
+      <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="6"/>
-      </left>
-      <right style="thin">
-        <color theme="6"/>
-      </right>
-      <top style="slantDashDot">
-        <color rgb="FFD8EFF1"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="6"/>
-      </left>
-      <right style="thin">
-        <color theme="6"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="6"/>
-      </left>
-      <right style="thin">
-        <color theme="6"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="6"/>
-      </left>
+      <left/>
       <right style="thin">
         <color theme="6"/>
       </right>
@@ -1860,12 +1122,55 @@
         <color theme="6"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="hair">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
       </left>
       <right style="thin">
         <color theme="6"/>
@@ -1873,8 +1178,8 @@
       <top style="hair">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color theme="6"/>
+      <bottom style="hair">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1888,8 +1193,8 @@
       <top style="hair">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color theme="6"/>
+      <bottom style="hair">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1898,24 +1203,97 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color theme="6"/>
+        <color theme="2" tint="-0.249977111117893"/>
       </right>
       <top style="hair">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color theme="6"/>
+      <bottom style="hair">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thick">
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="hair">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </top>
+      <bottom style="hair">
         <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="hair">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
       </top>
-      <bottom style="dotted">
+      <bottom style="hair">
         <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="hair">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </top>
+      <bottom style="hair">
+        <color theme="2" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1974,9 +1352,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2055,10 +1433,10 @@
     <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="17" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="19" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="19" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="19"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2116,50 +1494,14 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="9" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="22" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="37" fontId="21" fillId="6" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2170,104 +1512,166 @@
     <xf numFmtId="37" fontId="21" fillId="6" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="5" xfId="14" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="14" applyFont="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="3" xfId="14" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="3" xfId="14" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="19" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="8" borderId="4" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="19" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="9" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="8" borderId="9" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="19" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="4" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="19" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="19" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="23" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="21" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="18" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="4" fillId="4" borderId="1" xfId="9" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="4" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="4" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" justifyLastLine="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="39" fillId="4" borderId="0" xfId="4" applyFont="1" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="11" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="7" fontId="22" fillId="4" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="7" fontId="38" fillId="4" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="7" fontId="22" fillId="4" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="7" fontId="22" fillId="4" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -2292,52 +1696,7 @@
     <cellStyle name="货币[0]" xfId="11" builtinId="7" customBuiltin="1"/>
     <cellStyle name="超链接" xfId="14" builtinId="8" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color theme="4" tint="-0.24994659260841701"/>
@@ -2429,20 +1788,20 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="College Checklist" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="13"/>
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="wholeTable" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
     </tableStyle>
     <tableStyle name="Shopping List" pivot="0" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="10"/>
-      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <colors>
     <mruColors>
-      <color rgb="FFF2543A"/>
       <color rgb="FFBE1F16"/>
       <color rgb="FF0066FF"/>
+      <color rgb="FFF2543A"/>
       <color rgb="FFD8EFF1"/>
       <color rgb="FFEAEAEA"/>
     </mruColors>
@@ -2785,6 +2144,12 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.10545777809832947"/>
+                  <c:y val="-7.886219855390288E-3"/>
+                </c:manualLayout>
+              </c:layout>
               <c:numFmt formatCode="0%" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -2795,17 +2160,14 @@
               </c:spPr>
               <c:txPr>
                 <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
+                  <a:noAutofit/>
                 </a:bodyPr>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="75000"/>
-                          <a:lumOff val="25000"/>
-                        </a:schemeClr>
+                        <a:srgbClr val="BE1F16"/>
                       </a:solidFill>
                       <a:latin typeface="+mn-lt"/>
                       <a:ea typeface="+mn-ea"/>
@@ -2822,6 +2184,14 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.11051975144704917"/>
+                      <c:h val="0.42561990655760917"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000001-129A-442B-AB08-6F070EE98C93}"/>
                 </c:ext>
@@ -2885,7 +2255,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>HealthReport!$L$27</c:f>
+              <c:f>HealthReport!$L$12</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
@@ -2894,12 +2264,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>HealthReport!$L$28</c:f>
+              <c:f>HealthReport!$L$14</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.52307692307692311</c:v>
+                  <c:v>0.96470588235294119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2931,7 +2301,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3618,13 +2988,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4982,15 +4352,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>935687</xdr:colOff>
+      <xdr:colOff>368949</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>354806</xdr:rowOff>
+      <xdr:rowOff>269761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1132608</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>11906</xdr:rowOff>
+      <xdr:colOff>986518</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>309561</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5282,18 +4652,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <tabColor theme="2" tint="-0.249977111117893"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:P62"/>
+  <dimension ref="B1:P70"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
     <col min="2" max="2" width="5.25" style="16" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
-    <col min="4" max="6" width="12.625" customWidth="1"/>
+    <col min="4" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="16" customWidth="1"/>
     <col min="7" max="7" width="6.375" customWidth="1"/>
     <col min="8" max="8" width="15.625" customWidth="1"/>
     <col min="9" max="10" width="12.625" customWidth="1"/>
@@ -5310,7 +4681,7 @@
       <c r="D1" s="22"/>
       <c r="E1" s="22"/>
       <c r="F1" s="25" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="23"/>
@@ -5324,7 +4695,7 @@
       <c r="C2" s="11"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="88"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -5339,7 +4710,7 @@
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="F3" s="89"/>
       <c r="G3" s="4"/>
       <c r="H3" s="5" t="s">
         <v>2</v>
@@ -5347,7 +4718,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
-      <c r="L3" s="4"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13"/>
@@ -5355,108 +4726,105 @@
         <v>3</v>
       </c>
       <c r="D4" s="42"/>
-      <c r="E4" s="98" t="s">
-        <v>190</v>
-      </c>
-      <c r="F4" s="98"/>
+      <c r="E4" s="103" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="103"/>
       <c r="G4" s="19"/>
       <c r="H4" s="46" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="46"/>
-      <c r="J4" s="97" t="s">
+      <c r="J4" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="97"/>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="102"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="2:16" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
       <c r="C5" s="43" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D5" s="44"/>
-      <c r="E5" s="99" t="s">
-        <v>191</v>
-      </c>
-      <c r="F5" s="99"/>
+      <c r="E5" s="104" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="104"/>
       <c r="G5" s="19"/>
       <c r="H5" s="43" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="43"/>
-      <c r="J5" s="93" t="s">
-        <v>199</v>
-      </c>
-      <c r="K5" s="93"/>
-      <c r="L5" s="8"/>
+      <c r="J5" s="101" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="101"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="13"/>
       <c r="C6" s="43" t="s">
-        <v>197</v>
+        <v>89</v>
       </c>
       <c r="D6" s="43"/>
-      <c r="E6" s="93" t="s">
-        <v>192</v>
-      </c>
-      <c r="F6" s="93"/>
+      <c r="E6" s="101" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="101"/>
       <c r="G6" s="19"/>
       <c r="H6" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I6" s="43"/>
-      <c r="J6" s="93" t="s">
+      <c r="J6" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="93"/>
-      <c r="L6" s="8"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="2"/>
     </row>
     <row r="7" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="13"/>
       <c r="C7" s="43" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D7" s="45"/>
-      <c r="E7" s="93" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" s="93"/>
+      <c r="E7" s="101" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="101"/>
       <c r="G7" s="19"/>
       <c r="H7" s="43" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="I7" s="43"/>
-      <c r="J7" s="93" t="s">
+      <c r="J7" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="93"/>
-      <c r="L7" s="8"/>
-      <c r="P7" s="1">
-        <f>19.8/12</f>
-        <v>1.6500000000000001</v>
-      </c>
+      <c r="K7" s="101"/>
+      <c r="L7" s="2"/>
+      <c r="P7" s="1"/>
     </row>
     <row r="8" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
       <c r="C8" s="43" t="s">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="D8" s="43"/>
-      <c r="E8" s="96" t="s">
-        <v>194</v>
-      </c>
-      <c r="F8" s="93"/>
+      <c r="E8" s="100" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="101"/>
       <c r="G8" s="20"/>
       <c r="H8" s="43" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="I8" s="43"/>
-      <c r="J8" s="93" t="s">
+      <c r="J8" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="93"/>
-      <c r="L8" s="8"/>
+      <c r="K8" s="101"/>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="13"/>
@@ -5464,61 +4832,61 @@
         <v>4</v>
       </c>
       <c r="D9" s="43"/>
-      <c r="E9" s="93" t="s">
-        <v>195</v>
-      </c>
-      <c r="F9" s="93"/>
+      <c r="E9" s="101" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="101"/>
       <c r="G9" s="20"/>
       <c r="H9" s="43" t="s">
         <v>12</v>
       </c>
       <c r="I9" s="43"/>
-      <c r="J9" s="93" t="s">
+      <c r="J9" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="93"/>
-      <c r="L9" s="8"/>
+      <c r="K9" s="101"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" spans="2:16" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="13"/>
       <c r="C10" s="43" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="D10" s="43"/>
-      <c r="E10" s="93" t="s">
-        <v>198</v>
-      </c>
-      <c r="F10" s="93"/>
+      <c r="E10" s="101" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="101"/>
       <c r="G10" s="20"/>
       <c r="H10" s="45" t="s">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="I10" s="43"/>
-      <c r="J10" s="93" t="s">
+      <c r="J10" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="K10" s="93"/>
-      <c r="L10" s="8"/>
+      <c r="K10" s="101"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="2:16" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="13"/>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="106"/>
       <c r="G11" s="20"/>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
-      <c r="J11" s="92"/>
-      <c r="K11" s="92"/>
-      <c r="L11" s="8"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="2:16" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B12" s="14"/>
       <c r="C12" s="9"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+      <c r="F12" s="90"/>
       <c r="G12" s="8"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
@@ -5533,16 +4901,16 @@
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="F13" s="89"/>
       <c r="G13" s="8"/>
       <c r="H13" s="5" t="str">
-        <f>"Health status ("&amp;COUNTIFS(HealthReport!$L$29:$L$41, "&gt;0")&amp;" of "&amp;COUNTIFS(HealthReport!$H$29:$H$41, "&gt;0")&amp;")"</f>
-        <v>Health status (0 of 0)</v>
+        <f>"Health status ("&amp;SUM(D15:F24)&amp;" of "&amp;85&amp;")"</f>
+        <v>Health status (3 of 85)</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
+      <c r="L13" s="97"/>
     </row>
     <row r="14" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="14"/>
@@ -5551,9 +4919,9 @@
         <v>18</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="91" t="s">
         <v>19</v>
       </c>
       <c r="G14" s="8"/>
@@ -5561,12 +4929,15 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="96">
+        <f>1-SUM(D15:F24)/85</f>
+        <v>0.96470588235294119</v>
+      </c>
     </row>
     <row r="15" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14"/>
       <c r="C15" s="17" t="s">
-        <v>232</v>
+        <v>100</v>
       </c>
       <c r="D15" s="6">
         <v>0</v>
@@ -5574,8 +4945,8 @@
       <c r="E15" s="6">
         <v>1</v>
       </c>
-      <c r="F15" s="6">
-        <v>0</v>
+      <c r="F15" s="92">
+        <v>1</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -5587,7 +4958,7 @@
     <row r="16" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14"/>
       <c r="C16" s="17" t="s">
-        <v>233</v>
+        <v>101</v>
       </c>
       <c r="D16" s="6">
         <v>0</v>
@@ -5595,7 +4966,7 @@
       <c r="E16" s="6">
         <v>0</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="92">
         <v>0</v>
       </c>
       <c r="G16" s="8"/>
@@ -5608,7 +4979,7 @@
     <row r="17" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="14"/>
       <c r="C17" s="17" t="s">
-        <v>235</v>
+        <v>103</v>
       </c>
       <c r="D17" s="6">
         <v>0</v>
@@ -5616,8 +4987,8 @@
       <c r="E17" s="6">
         <v>0</v>
       </c>
-      <c r="F17" s="6">
-        <v>0</v>
+      <c r="F17" s="92">
+        <v>1</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
@@ -5629,7 +5000,7 @@
     <row r="18" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="14"/>
       <c r="C18" s="17" t="s">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="D18" s="6">
         <v>0</v>
@@ -5637,7 +5008,7 @@
       <c r="E18" s="6">
         <v>0</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="92">
         <v>0</v>
       </c>
       <c r="G18" s="8"/>
@@ -5650,7 +5021,7 @@
     <row r="19" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="14"/>
       <c r="C19" s="17" t="s">
-        <v>228</v>
+        <v>96</v>
       </c>
       <c r="D19" s="6">
         <v>0</v>
@@ -5658,7 +5029,7 @@
       <c r="E19" s="6">
         <v>0</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="92">
         <v>0</v>
       </c>
       <c r="G19" s="8"/>
@@ -5671,7 +5042,7 @@
     <row r="20" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14"/>
       <c r="C20" s="17" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="D20" s="6">
         <v>0</v>
@@ -5679,7 +5050,7 @@
       <c r="E20" s="6">
         <v>0</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="92">
         <v>0</v>
       </c>
       <c r="G20" s="8"/>
@@ -5692,7 +5063,7 @@
     <row r="21" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="14"/>
       <c r="C21" s="17" t="s">
-        <v>230</v>
+        <v>98</v>
       </c>
       <c r="D21" s="6">
         <v>0</v>
@@ -5700,7 +5071,7 @@
       <c r="E21" s="6">
         <v>0</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="92">
         <v>0</v>
       </c>
       <c r="G21" s="8"/>
@@ -5713,7 +5084,7 @@
     <row r="22" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
       <c r="C22" s="17" t="s">
-        <v>231</v>
+        <v>99</v>
       </c>
       <c r="D22" s="6">
         <v>0</v>
@@ -5721,7 +5092,7 @@
       <c r="E22" s="6">
         <v>0</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="92">
         <v>0</v>
       </c>
       <c r="G22" s="4"/>
@@ -5734,7 +5105,7 @@
     <row r="23" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="14"/>
       <c r="C23" s="17" t="s">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="D23" s="6">
         <v>0</v>
@@ -5742,7 +5113,7 @@
       <c r="E23" s="6">
         <v>0</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="92">
         <v>0</v>
       </c>
       <c r="G23" s="4"/>
@@ -5763,7 +5134,7 @@
       <c r="E24" s="6">
         <v>0</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="92">
         <v>0</v>
       </c>
       <c r="G24" s="4"/>
@@ -5778,7 +5149,7 @@
       <c r="C25" s="12"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="F25" s="93"/>
       <c r="G25" s="4"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -5791,7 +5162,7 @@
       <c r="C26" s="9"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
+      <c r="F26" s="90"/>
       <c r="G26" s="4"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
@@ -5815,34 +5186,31 @@
       <c r="L27" s="14"/>
     </row>
     <row r="28" spans="2:12" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="82" t="s">
+      <c r="B28" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="83" t="s">
+      <c r="C28" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="84" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83" t="s">
+      <c r="D28" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="G28" s="85" t="s">
-        <v>40</v>
-      </c>
-      <c r="H28" s="86" t="s">
+      <c r="H28" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="82"/>
-      <c r="J28" s="82"/>
-      <c r="K28" s="87"/>
-      <c r="L28" s="88">
-        <f>SUM(HealthReport!$F$29:$F$41)/130</f>
-        <v>0.52307692307692311</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" ht="38.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="64"/>
+    </row>
+    <row r="29" spans="2:12" ht="39.950000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B29" s="28">
         <v>1</v>
       </c>
@@ -5850,26 +5218,26 @@
         <v>20</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E29" s="31"/>
       <c r="F29" s="32">
         <v>10</v>
       </c>
-      <c r="G29" s="62" t="str" cm="1">
+      <c r="G29" s="50" t="str" cm="1">
         <f t="array" ref="G29">_xlfn.IFS(HealthReport!$F29&gt;=10,"PASS",HealthReport!$F29=8,"轻微",HealthReport!$F29=5,"普通",HealthReport!$F29=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H29" s="95"/>
-      <c r="I29" s="95"/>
-      <c r="J29" s="95"/>
-      <c r="K29" s="95"/>
-      <c r="L29" s="66" t="str">
+      <c r="H29" s="107"/>
+      <c r="I29" s="107"/>
+      <c r="J29" s="107"/>
+      <c r="K29" s="107"/>
+      <c r="L29" s="54" t="str">
         <f>HYPERLINK("#OS!B5","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="33">
         <v>2</v>
       </c>
@@ -5877,610 +5245,476 @@
         <v>25</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E30" s="34"/>
       <c r="F30" s="36">
         <v>10</v>
       </c>
-      <c r="G30" s="63" t="str" cm="1">
+      <c r="G30" s="51" t="str" cm="1">
         <f t="array" ref="G30">_xlfn.IFS(HealthReport!$F30&gt;=10,"PASS",HealthReport!$F30=8,"轻微",HealthReport!$F30=5,"普通",HealthReport!$F30=0,"重要")</f>
         <v>PASS</v>
       </c>
-      <c r="H30" s="90"/>
-      <c r="I30" s="90"/>
-      <c r="J30" s="90"/>
-      <c r="K30" s="90"/>
-      <c r="L30" s="67" t="str">
+      <c r="H30" s="98"/>
+      <c r="I30" s="98"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="98"/>
+      <c r="L30" s="55" t="str">
         <f>HYPERLINK("#OS!B5","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="28">
-        <v>3</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>42</v>
-      </c>
+    <row r="31" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="28"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="37"/>
       <c r="E31" s="31"/>
-      <c r="F31" s="32">
-        <v>10</v>
-      </c>
-      <c r="G31" s="62" t="str" cm="1">
-        <f t="array" ref="G31">_xlfn.IFS(HealthReport!$F31&gt;=10,"PASS",HealthReport!$F31=8,"轻微",HealthReport!$F31=5,"普通",HealthReport!$F31=0,"重要")</f>
-        <v>PASS</v>
-      </c>
-      <c r="H31" s="91"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="91"/>
-      <c r="K31" s="91"/>
-      <c r="L31" s="66" t="str">
-        <f>HYPERLINK("#OS!B5","Detail")</f>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="33">
-        <v>4</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>33</v>
-      </c>
+      <c r="F31" s="32"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="99"/>
+      <c r="I31" s="99"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="54"/>
+    </row>
+    <row r="32" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="33"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="34"/>
-      <c r="F32" s="36">
-        <v>5</v>
-      </c>
-      <c r="G32" s="63" t="str" cm="1">
-        <f t="array" ref="G32">_xlfn.IFS(HealthReport!$F32&gt;=10,"PASS",HealthReport!$F32=8,"轻微",HealthReport!$F32=5,"普通",HealthReport!$F32=0,"重要")</f>
-        <v>普通</v>
-      </c>
-      <c r="H32" s="90"/>
-      <c r="I32" s="90"/>
-      <c r="J32" s="90"/>
-      <c r="K32" s="90"/>
-      <c r="L32" s="67" t="str">
-        <f>HYPERLINK("#OS!B5","Detail")</f>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="28">
-        <v>5</v>
-      </c>
-      <c r="C33" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="31"/>
-      <c r="F33" s="32">
-        <v>10</v>
-      </c>
-      <c r="G33" s="62" t="str" cm="1">
-        <f t="array" ref="G33">_xlfn.IFS(HealthReport!$F33&gt;=10,"PASS",HealthReport!$F33=8,"轻微",HealthReport!$F33=5,"普通",HealthReport!$F33=0,"重要")</f>
-        <v>PASS</v>
-      </c>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="91"/>
-      <c r="K33" s="91"/>
-      <c r="L33" s="66" t="str">
-        <f t="shared" ref="L33:L41" si="0">HYPERLINK("#OS!A1","Detail")</f>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="33">
-        <v>6</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="34"/>
-      <c r="F34" s="36">
-        <v>10</v>
-      </c>
-      <c r="G34" s="63" t="str" cm="1">
-        <f t="array" ref="G34">_xlfn.IFS(HealthReport!$F34&gt;=10,"PASS",HealthReport!$F34=8,"轻微",HealthReport!$F34=5,"普通",HealthReport!$F34=0,"重要")</f>
-        <v>PASS</v>
-      </c>
-      <c r="H34" s="90"/>
-      <c r="I34" s="90"/>
-      <c r="J34" s="90"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="67" t="str">
-        <f t="shared" si="0"/>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="28">
-        <v>7</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="31"/>
-      <c r="F35" s="32">
-        <v>8</v>
-      </c>
-      <c r="G35" s="62" t="str" cm="1">
-        <f t="array" ref="G35">_xlfn.IFS(HealthReport!$F35&gt;=10,"PASS",HealthReport!$F35=8,"轻微",HealthReport!$F35=5,"普通",HealthReport!$F35=0,"重要")</f>
-        <v>轻微</v>
-      </c>
-      <c r="H35" s="91"/>
-      <c r="I35" s="91"/>
-      <c r="J35" s="91"/>
-      <c r="K35" s="91"/>
-      <c r="L35" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="33">
-        <v>8</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="35" t="s">
-        <v>37</v>
-      </c>
+      <c r="F32" s="36"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="55"/>
+    </row>
+    <row r="33" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="15"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="99"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="99"/>
+      <c r="K33" s="99"/>
+      <c r="L33" s="56"/>
+    </row>
+    <row r="34" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="94"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="57"/>
+    </row>
+    <row r="35" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="15"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="99"/>
+      <c r="I35" s="99"/>
+      <c r="J35" s="99"/>
+      <c r="K35" s="99"/>
+      <c r="L35" s="56"/>
+    </row>
+    <row r="36" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="33"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="35"/>
       <c r="E36" s="34"/>
-      <c r="F36" s="36">
-        <v>5</v>
-      </c>
-      <c r="G36" s="63" t="str" cm="1">
-        <f t="array" ref="G36">_xlfn.IFS(HealthReport!$F36&gt;=10,"PASS",HealthReport!$F36=8,"轻微",HealthReport!$F36=5,"普通",HealthReport!$F36=0,"重要")</f>
-        <v>普通</v>
-      </c>
-      <c r="H36" s="90"/>
-      <c r="I36" s="90"/>
-      <c r="J36" s="90"/>
-      <c r="K36" s="90"/>
-      <c r="L36" s="67" t="str">
-        <f t="shared" si="0"/>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="28">
-        <v>9</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="E37" s="31"/>
-      <c r="F37" s="32">
-        <v>0</v>
-      </c>
-      <c r="G37" s="62" t="str" cm="1">
-        <f t="array" ref="G37">_xlfn.IFS(HealthReport!$F37&gt;=10,"PASS",HealthReport!$F37=8,"轻微",HealthReport!$F37=5,"普通",HealthReport!$F37=0,"重要")</f>
-        <v>重要</v>
-      </c>
-      <c r="H37" s="91"/>
-      <c r="I37" s="91"/>
-      <c r="J37" s="91"/>
-      <c r="K37" s="91"/>
-      <c r="L37" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="33">
-        <v>10</v>
-      </c>
-      <c r="C38" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="D38" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" s="34"/>
-      <c r="F38" s="36">
-        <v>0</v>
-      </c>
-      <c r="G38" s="63" t="str" cm="1">
-        <f t="array" ref="G38">_xlfn.IFS(HealthReport!$F38&gt;=10,"PASS",HealthReport!$F38=8,"轻微",HealthReport!$F38=5,"普通",HealthReport!$F38=0,"重要")</f>
-        <v>重要</v>
-      </c>
-      <c r="H38" s="90"/>
-      <c r="I38" s="90"/>
-      <c r="J38" s="90"/>
-      <c r="K38" s="90"/>
-      <c r="L38" s="67" t="str">
-        <f t="shared" si="0"/>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="28">
-        <v>11</v>
-      </c>
-      <c r="C39" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="E39" s="31"/>
-      <c r="F39" s="32">
-        <v>0</v>
-      </c>
-      <c r="G39" s="62" t="str" cm="1">
-        <f t="array" ref="G39">_xlfn.IFS(HealthReport!$F39&gt;=10,"PASS",HealthReport!$F39=8,"轻微",HealthReport!$F39=5,"普通",HealthReport!$F39=0,"重要")</f>
-        <v>重要</v>
-      </c>
-      <c r="H39" s="91"/>
-      <c r="I39" s="91"/>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="66" t="str">
-        <f t="shared" si="0"/>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="33">
-        <v>12</v>
-      </c>
-      <c r="C40" s="34" t="s">
-        <v>28</v>
-      </c>
+      <c r="F36" s="36"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="98"/>
+      <c r="I36" s="98"/>
+      <c r="J36" s="98"/>
+      <c r="K36" s="98"/>
+      <c r="L36" s="55"/>
+    </row>
+    <row r="37" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="15"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="99"/>
+      <c r="K37" s="99"/>
+      <c r="L37" s="56"/>
+    </row>
+    <row r="38" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="94"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="94"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="98"/>
+      <c r="I38" s="98"/>
+      <c r="J38" s="98"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="57"/>
+    </row>
+    <row r="39" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="15"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="99"/>
+      <c r="I39" s="99"/>
+      <c r="J39" s="99"/>
+      <c r="K39" s="99"/>
+      <c r="L39" s="56"/>
+    </row>
+    <row r="40" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="33"/>
+      <c r="C40" s="34"/>
       <c r="D40" s="35"/>
       <c r="E40" s="34"/>
-      <c r="F40" s="36">
-        <v>0</v>
-      </c>
-      <c r="G40" s="63" t="str" cm="1">
-        <f t="array" ref="G40">_xlfn.IFS(HealthReport!$F40&gt;=10,"PASS",HealthReport!$F40=8,"轻微",HealthReport!$F40=5,"普通",HealthReport!$F40=0,"重要")</f>
-        <v>重要</v>
-      </c>
-      <c r="H40" s="90"/>
-      <c r="I40" s="90"/>
-      <c r="J40" s="90"/>
-      <c r="K40" s="90"/>
-      <c r="L40" s="67" t="str">
-        <f t="shared" si="0"/>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="15">
-        <v>13</v>
-      </c>
-      <c r="C41" s="38" t="s">
-        <v>27</v>
-      </c>
+      <c r="F40" s="36"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="98"/>
+      <c r="I40" s="98"/>
+      <c r="J40" s="98"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="55"/>
+    </row>
+    <row r="41" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="15"/>
+      <c r="C41" s="38"/>
       <c r="D41" s="37"/>
       <c r="E41" s="38"/>
-      <c r="F41" s="39">
-        <v>0</v>
-      </c>
-      <c r="G41" s="64" t="str" cm="1">
-        <f t="array" ref="G41">_xlfn.IFS(HealthReport!$F41&gt;=10,"PASS",HealthReport!$F41=8,"轻微",HealthReport!$F41=5,"普通",HealthReport!$F41=0,"重要")</f>
-        <v>重要</v>
-      </c>
-      <c r="H41" s="91" t="s">
-        <v>163</v>
-      </c>
-      <c r="I41" s="91"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="91"/>
-      <c r="L41" s="68" t="str">
-        <f t="shared" si="0"/>
-        <v>Detail</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F41" s="39"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="99"/>
+      <c r="I41" s="99"/>
+      <c r="J41" s="99"/>
+      <c r="K41" s="99"/>
+      <c r="L41" s="56"/>
+    </row>
+    <row r="42" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="33"/>
       <c r="C42" s="34"/>
       <c r="D42" s="35"/>
       <c r="E42" s="34"/>
       <c r="F42" s="36"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="90"/>
-      <c r="I42" s="90"/>
-      <c r="J42" s="90"/>
-      <c r="K42" s="90"/>
-      <c r="L42" s="67"/>
-    </row>
-    <row r="43" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G42" s="51"/>
+      <c r="H42" s="98"/>
+      <c r="I42" s="98"/>
+      <c r="J42" s="98"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="55"/>
+    </row>
+    <row r="43" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="15"/>
       <c r="C43" s="38"/>
       <c r="D43" s="37"/>
       <c r="E43" s="38"/>
       <c r="F43" s="39"/>
-      <c r="G43" s="64"/>
-      <c r="H43" s="91"/>
-      <c r="I43" s="91"/>
-      <c r="J43" s="91"/>
-      <c r="K43" s="91"/>
-      <c r="L43" s="68"/>
-    </row>
-    <row r="44" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G43" s="52"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="56"/>
+    </row>
+    <row r="44" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="33"/>
       <c r="C44" s="34"/>
       <c r="D44" s="35"/>
       <c r="E44" s="34"/>
       <c r="F44" s="36"/>
-      <c r="G44" s="63"/>
-      <c r="H44" s="90"/>
-      <c r="I44" s="90"/>
-      <c r="J44" s="90"/>
-      <c r="K44" s="90"/>
-      <c r="L44" s="67"/>
-    </row>
-    <row r="45" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G44" s="51"/>
+      <c r="H44" s="98"/>
+      <c r="I44" s="98"/>
+      <c r="J44" s="98"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="55"/>
+    </row>
+    <row r="45" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="15"/>
       <c r="C45" s="38"/>
       <c r="D45" s="37"/>
       <c r="E45" s="38"/>
       <c r="F45" s="39"/>
-      <c r="G45" s="64"/>
-      <c r="H45" s="91"/>
-      <c r="I45" s="91"/>
-      <c r="J45" s="91"/>
-      <c r="K45" s="91"/>
-      <c r="L45" s="68"/>
-    </row>
-    <row r="46" spans="2:12" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="65"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="65"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="90"/>
-      <c r="I46" s="90"/>
-      <c r="J46" s="90"/>
-      <c r="K46" s="90"/>
-      <c r="L46" s="69"/>
-    </row>
-    <row r="47" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G45" s="52"/>
+      <c r="H45" s="99"/>
+      <c r="I45" s="99"/>
+      <c r="J45" s="99"/>
+      <c r="K45" s="99"/>
+      <c r="L45" s="56"/>
+    </row>
+    <row r="46" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="94"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="94"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="98"/>
+      <c r="I46" s="98"/>
+      <c r="J46" s="98"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="57"/>
+    </row>
+    <row r="47" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="15"/>
       <c r="C47" s="38"/>
       <c r="D47" s="37"/>
       <c r="E47" s="38"/>
       <c r="F47" s="39"/>
-      <c r="G47" s="64"/>
-      <c r="H47" s="91"/>
-      <c r="I47" s="91"/>
-      <c r="J47" s="91"/>
-      <c r="K47" s="91"/>
-      <c r="L47" s="68"/>
-    </row>
-    <row r="48" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G47" s="52"/>
+      <c r="H47" s="99"/>
+      <c r="I47" s="99"/>
+      <c r="J47" s="99"/>
+      <c r="K47" s="99"/>
+      <c r="L47" s="56"/>
+    </row>
+    <row r="48" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="33"/>
       <c r="C48" s="34"/>
       <c r="D48" s="35"/>
       <c r="E48" s="34"/>
       <c r="F48" s="36"/>
-      <c r="G48" s="63"/>
-      <c r="H48" s="90"/>
-      <c r="I48" s="90"/>
-      <c r="J48" s="90"/>
-      <c r="K48" s="90"/>
-      <c r="L48" s="67"/>
-    </row>
-    <row r="49" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G48" s="51"/>
+      <c r="H48" s="98"/>
+      <c r="I48" s="98"/>
+      <c r="J48" s="98"/>
+      <c r="K48" s="98"/>
+      <c r="L48" s="55"/>
+    </row>
+    <row r="49" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="15"/>
       <c r="C49" s="38"/>
       <c r="D49" s="37"/>
       <c r="E49" s="38"/>
       <c r="F49" s="39"/>
-      <c r="G49" s="64"/>
-      <c r="H49" s="91"/>
-      <c r="I49" s="91"/>
-      <c r="J49" s="91"/>
-      <c r="K49" s="91"/>
-      <c r="L49" s="68"/>
-    </row>
-    <row r="50" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="65"/>
-      <c r="C50" s="65"/>
-      <c r="D50" s="65"/>
-      <c r="E50" s="65"/>
-      <c r="F50" s="65"/>
-      <c r="G50" s="65"/>
-      <c r="H50" s="90"/>
-      <c r="I50" s="90"/>
-      <c r="J50" s="90"/>
-      <c r="K50" s="90"/>
-      <c r="L50" s="69"/>
-    </row>
-    <row r="51" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G49" s="52"/>
+      <c r="H49" s="99"/>
+      <c r="I49" s="99"/>
+      <c r="J49" s="99"/>
+      <c r="K49" s="99"/>
+      <c r="L49" s="56"/>
+    </row>
+    <row r="50" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="94"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="94"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="98"/>
+      <c r="I50" s="98"/>
+      <c r="J50" s="98"/>
+      <c r="K50" s="98"/>
+      <c r="L50" s="57"/>
+    </row>
+    <row r="51" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="15"/>
       <c r="C51" s="38"/>
       <c r="D51" s="37"/>
       <c r="E51" s="38"/>
       <c r="F51" s="39"/>
-      <c r="G51" s="64"/>
-      <c r="H51" s="91"/>
-      <c r="I51" s="91"/>
-      <c r="J51" s="91"/>
-      <c r="K51" s="91"/>
-      <c r="L51" s="68"/>
-    </row>
-    <row r="52" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G51" s="52"/>
+      <c r="H51" s="99"/>
+      <c r="I51" s="99"/>
+      <c r="J51" s="99"/>
+      <c r="K51" s="99"/>
+      <c r="L51" s="56"/>
+    </row>
+    <row r="52" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="33"/>
       <c r="C52" s="34"/>
       <c r="D52" s="35"/>
       <c r="E52" s="34"/>
       <c r="F52" s="36"/>
-      <c r="G52" s="63"/>
-      <c r="H52" s="90"/>
-      <c r="I52" s="90"/>
-      <c r="J52" s="90"/>
-      <c r="K52" s="90"/>
-      <c r="L52" s="67"/>
-    </row>
-    <row r="53" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G52" s="51"/>
+      <c r="H52" s="98"/>
+      <c r="I52" s="98"/>
+      <c r="J52" s="98"/>
+      <c r="K52" s="98"/>
+      <c r="L52" s="55"/>
+    </row>
+    <row r="53" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="15"/>
       <c r="C53" s="38"/>
       <c r="D53" s="37"/>
       <c r="E53" s="38"/>
       <c r="F53" s="39"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="91"/>
-      <c r="I53" s="91"/>
-      <c r="J53" s="91"/>
-      <c r="K53" s="91"/>
-      <c r="L53" s="68"/>
-    </row>
-    <row r="54" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="65"/>
-      <c r="C54" s="65"/>
-      <c r="D54" s="65"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="65"/>
-      <c r="H54" s="90"/>
-      <c r="I54" s="90"/>
-      <c r="J54" s="90"/>
-      <c r="K54" s="90"/>
-      <c r="L54" s="69"/>
-    </row>
-    <row r="55" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G53" s="52"/>
+      <c r="H53" s="99"/>
+      <c r="I53" s="99"/>
+      <c r="J53" s="99"/>
+      <c r="K53" s="99"/>
+      <c r="L53" s="56"/>
+    </row>
+    <row r="54" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="94"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="94"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="98"/>
+      <c r="I54" s="98"/>
+      <c r="J54" s="98"/>
+      <c r="K54" s="98"/>
+      <c r="L54" s="57"/>
+    </row>
+    <row r="55" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="15"/>
       <c r="C55" s="38"/>
       <c r="D55" s="37"/>
       <c r="E55" s="38"/>
       <c r="F55" s="39"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="91"/>
-      <c r="I55" s="91"/>
-      <c r="J55" s="91"/>
-      <c r="K55" s="91"/>
-      <c r="L55" s="68"/>
-    </row>
-    <row r="56" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G55" s="52"/>
+      <c r="H55" s="99"/>
+      <c r="I55" s="99"/>
+      <c r="J55" s="99"/>
+      <c r="K55" s="99"/>
+      <c r="L55" s="56"/>
+    </row>
+    <row r="56" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="33"/>
       <c r="C56" s="34"/>
       <c r="D56" s="35"/>
       <c r="E56" s="34"/>
       <c r="F56" s="36"/>
-      <c r="G56" s="63"/>
-      <c r="H56" s="90"/>
-      <c r="I56" s="90"/>
-      <c r="J56" s="90"/>
-      <c r="K56" s="90"/>
-      <c r="L56" s="67"/>
-    </row>
-    <row r="57" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G56" s="51"/>
+      <c r="H56" s="98"/>
+      <c r="I56" s="98"/>
+      <c r="J56" s="98"/>
+      <c r="K56" s="98"/>
+      <c r="L56" s="55"/>
+    </row>
+    <row r="57" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="15"/>
       <c r="C57" s="38"/>
       <c r="D57" s="37"/>
       <c r="E57" s="38"/>
       <c r="F57" s="39"/>
-      <c r="G57" s="64"/>
-      <c r="H57" s="91"/>
-      <c r="I57" s="91"/>
-      <c r="J57" s="91"/>
-      <c r="K57" s="91"/>
-      <c r="L57" s="68"/>
-    </row>
-    <row r="58" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="65"/>
-      <c r="C58" s="65"/>
-      <c r="D58" s="65"/>
-      <c r="E58" s="65"/>
-      <c r="F58" s="65"/>
-      <c r="G58" s="65"/>
-      <c r="H58" s="90"/>
-      <c r="I58" s="90"/>
-      <c r="J58" s="90"/>
-      <c r="K58" s="90"/>
-      <c r="L58" s="69"/>
-    </row>
-    <row r="59" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G57" s="52"/>
+      <c r="H57" s="99"/>
+      <c r="I57" s="99"/>
+      <c r="J57" s="99"/>
+      <c r="K57" s="99"/>
+      <c r="L57" s="56"/>
+    </row>
+    <row r="58" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="94"/>
+      <c r="C58" s="53"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="94"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="98"/>
+      <c r="I58" s="98"/>
+      <c r="J58" s="98"/>
+      <c r="K58" s="98"/>
+      <c r="L58" s="57"/>
+    </row>
+    <row r="59" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="15"/>
       <c r="C59" s="38"/>
       <c r="D59" s="37"/>
       <c r="E59" s="38"/>
       <c r="F59" s="39"/>
-      <c r="G59" s="64"/>
-      <c r="H59" s="91"/>
-      <c r="I59" s="91"/>
-      <c r="J59" s="91"/>
-      <c r="K59" s="91"/>
-      <c r="L59" s="68"/>
-    </row>
-    <row r="60" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G59" s="52"/>
+      <c r="H59" s="99"/>
+      <c r="I59" s="99"/>
+      <c r="J59" s="99"/>
+      <c r="K59" s="99"/>
+      <c r="L59" s="56"/>
+    </row>
+    <row r="60" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="33"/>
       <c r="C60" s="34"/>
       <c r="D60" s="35"/>
       <c r="E60" s="34"/>
       <c r="F60" s="36"/>
-      <c r="G60" s="63"/>
-      <c r="H60" s="90"/>
-      <c r="I60" s="90"/>
-      <c r="J60" s="90"/>
-      <c r="K60" s="90"/>
-      <c r="L60" s="67"/>
-    </row>
-    <row r="61" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G60" s="51"/>
+      <c r="H60" s="98"/>
+      <c r="I60" s="98"/>
+      <c r="J60" s="98"/>
+      <c r="K60" s="98"/>
+      <c r="L60" s="55"/>
+    </row>
+    <row r="61" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="15"/>
       <c r="C61" s="38"/>
       <c r="D61" s="37"/>
       <c r="E61" s="38"/>
       <c r="F61" s="39"/>
-      <c r="G61" s="64"/>
-      <c r="H61" s="91"/>
-      <c r="I61" s="91"/>
-      <c r="J61" s="91"/>
-      <c r="K61" s="91"/>
-      <c r="L61" s="68"/>
-    </row>
-    <row r="62" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="65"/>
-      <c r="C62" s="65"/>
-      <c r="D62" s="65"/>
-      <c r="E62" s="65"/>
-      <c r="F62" s="65"/>
-      <c r="G62" s="65"/>
-      <c r="H62" s="90"/>
-      <c r="I62" s="90"/>
-      <c r="J62" s="90"/>
-      <c r="K62" s="90"/>
-      <c r="L62" s="69"/>
-    </row>
+      <c r="G61" s="52"/>
+      <c r="H61" s="99"/>
+      <c r="I61" s="99"/>
+      <c r="J61" s="99"/>
+      <c r="K61" s="99"/>
+      <c r="L61" s="56"/>
+    </row>
+    <row r="62" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="94"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="94"/>
+      <c r="G62" s="53"/>
+      <c r="H62" s="98"/>
+      <c r="I62" s="98"/>
+      <c r="J62" s="98"/>
+      <c r="K62" s="98"/>
+      <c r="L62" s="57"/>
+    </row>
+    <row r="63" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="2:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="50">
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="H44:K44"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H60:K60"/>
+    <mergeCell ref="H61:K61"/>
+    <mergeCell ref="H62:K62"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="H56:K56"/>
+    <mergeCell ref="H57:K57"/>
+    <mergeCell ref="H58:K58"/>
+    <mergeCell ref="H59:K59"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="H31:K31"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="J9:K9"/>
@@ -6493,92 +5727,24 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="H53:K53"/>
-    <mergeCell ref="H54:K54"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="H60:K60"/>
-    <mergeCell ref="H61:K61"/>
-    <mergeCell ref="H62:K62"/>
-    <mergeCell ref="H55:K55"/>
-    <mergeCell ref="H56:K56"/>
-    <mergeCell ref="H57:K57"/>
-    <mergeCell ref="H58:K58"/>
-    <mergeCell ref="H59:K59"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="H44:K44"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="B13:B27">
-    <cfRule type="notContainsBlanks" dxfId="8" priority="63">
-      <formula>LEN(TRIM(B13))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14:C14">
-    <cfRule type="notContainsBlanks" dxfId="7" priority="64">
-      <formula>LEN(TRIM(B14))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12:L12 J13:L19 H19 H20:L26">
-    <cfRule type="notContainsBlanks" dxfId="6" priority="77">
-      <formula>LEN(TRIM(B12))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D27:L27">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="1">
-      <formula>LEN(TRIM(D27))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G11 G13:G21">
-    <cfRule type="notContainsBlanks" dxfId="4" priority="78">
-      <formula>LEN(TRIM(G8))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14:H15">
-    <cfRule type="notContainsBlanks" dxfId="3" priority="70">
-      <formula>LEN(TRIM(H14))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16:I18">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="76">
-      <formula>LEN(TRIM(H16))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13:I15">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="67">
-      <formula>LEN(TRIM(I13))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L11 P7">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="79">
-      <formula>LEN(TRIM(L4))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations xWindow="250" yWindow="706" count="12">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell C5. Shopping List Total in cell C6 and Remaining Cash in cell C7 are automatically calculated based on entries in Checklist table" sqref="C13:D14 E12:F14" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in cell at right" sqref="C15 C20" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in cell at right" sqref="C16:C18 C21" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Shopping List Total is automatically calculated in this cell" sqref="D21:F21 D16:F18" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Budget in this cell" sqref="D20:F20 D15:F15" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in cell at right" sqref="C12 C22:C26 H12:I12 C19" xr:uid="{00000000-0002-0000-0000-000006000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Remaining Cash is automatically calculated in this cell" sqref="F12 D19:F19 D12:E12 D22:F26 J12:K12" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells E5 through H7" sqref="P7 H12:I12 J12:L26 C12:F12 L4:L11 H20:I26 H19 H13 H14:I14 H16:I18 H15 G12:G21" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Shopping details in table below. Category list is automatically updated from Category table" sqref="C27" xr:uid="{00000000-0002-0000-0000-00000A000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells below" sqref="H13" xr:uid="{00000000-0002-0000-0000-000008000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C29:C41" xr:uid="{9A7EB216-EA1D-4A3D-B9E3-20B91A83DBC8}">
-      <formula1>$C$15:$C$24</formula1>
-    </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select Category from the list. Enter new categories in Category worksheet. Select CANCEL, then press ALT+DOWN ARROW for options, then DOWN ARROW and ENTER to make selection" sqref="D29:E41" xr:uid="{00000000-0002-0000-0000-000013000000}"/>
+  <dataValidations xWindow="250" yWindow="706" count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Purchasing Progress bar is in cells E5 through H7" sqref="P7" xr:uid="{00000000-0002-0000-0000-000009000000}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6587,298 +5753,12 @@
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="50" id="{3AD485F5-512A-4830-BA74-F6B14C2FEF34}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>B46:C46</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="39" id="{0F123DC0-E9CB-494F-9537-5267D0443334}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>B50:C50</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="28" id="{C75CBC66-D7CA-4A28-8777-654881069477}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>B54:C54</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="17" id="{88ED8CEC-2FA2-43DA-8ADA-0BDBE1D94E7F}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>B58:C58</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{18D66B4D-9470-4F8E-B72C-CD2C03C24492}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>B62:C62</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="49" id="{42B44E61-BD45-4B3B-A366-60DC3FA6E891}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>D46</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="38" id="{14B6D97C-3FC8-4777-B197-85596580A20F}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>D50</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="27" id="{2B77CF01-0B59-4A94-968C-F819B9BFC886}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>D54</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="16" id="{6A110090-049C-450A-84FF-B5C33643E19C}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>D58</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{23025D6F-F171-4B0A-A495-741EF450595B}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>D62</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="48" id="{9AE0B0A0-31AC-419A-8920-AF3FF686551C}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>E46</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="37" id="{BAA9148E-4C74-4C1C-A14C-98B823C60A38}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>E50</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="26" id="{A442FCE3-8944-4D53-8BFE-78C12683D968}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>E54</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{085671F5-C388-48EA-B946-69A906653317}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>E58</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{1CCBB599-0F02-4566-B4CA-822394CA31B8}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>E62</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="61" id="{D7E11CA3-AE2E-4AE0-8760-69AFD47E19CB}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+          <x14:cfRule type="iconSet" priority="1" id="{5A0B404C-F42C-4492-B16D-3985957F87AE}">
+            <x14:iconSet iconSet="4Rating" showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
               </x14:cfvo>
@@ -6888,772 +5768,16 @@
               <x14:cfvo type="num">
                 <xm:f>8</xm:f>
               </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
-              <x14:cfIcon iconSet="3Flags" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F29:F45</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="47" id="{3D962523-5725-48F8-9A20-D1500F15E2BB}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
               <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F46</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="44" id="{385FA039-B741-4960-9F2A-71D6C39C50C7}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>5</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>8</xm:f>
+                <xm:f>10</xm:f>
               </x14:cfvo>
               <x14:cfIcon iconSet="3Symbols" iconId="0"/>
               <x14:cfIcon iconSet="3Flags" iconId="0"/>
               <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>F47:F49</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="36" id="{CCF709D9-2591-4DAA-9315-C7A0355D6EA8}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F50</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="33" id="{EE2C29C5-1120-417B-89C1-A4074EDF4D05}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>5</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>8</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
-              <x14:cfIcon iconSet="3Flags" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F51:F53</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="25" id="{382D81D0-7236-4E93-AC9C-80DF5A6DE10A}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F54</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="22" id="{2E2DF39E-FCE4-494D-9ED5-2A48DAC77F81}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>5</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>8</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
-              <x14:cfIcon iconSet="3Flags" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F55:F57</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="14" id="{88EB00A5-156B-492D-85CB-0C5859CC38ED}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F58</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{330F031B-0D20-423C-A87C-02662C42927C}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>5</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>8</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
-              <x14:cfIcon iconSet="3Flags" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F59:F61</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{2F58AE20-A011-429D-A34F-429BFA1C9011}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F62</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="52" id="{EC29932F-78D6-4AC8-9D56-2F5F67B5688C}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>G46</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="40" id="{DEE3C81E-B484-4A72-9E13-E137E9862E3F}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>G50</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="29" id="{9D2BC978-9B76-40DC-BBE3-4FE422176FDC}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>G54</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="18" id="{2280D9D6-E10D-49C5-818E-A0E3B04DBFB6}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>G58</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{64445DF7-6492-4705-84DA-BB6A157D4154}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>G62</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="186" id="{904FC827-5D32-400A-97DB-D891D8D2E589}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H29:H42</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="56" id="{63B576F9-8DAA-41CF-AE73-5AB45F4F4032}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H43</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="54" id="{26C2D381-0C21-4A34-BF51-D0D70A2BBE5D}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H44</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="55" id="{6416AA23-656B-4E60-B17B-E9CCF66906E3}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H45</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="46" id="{55F288BA-48B1-4F42-A62E-AAE73E9A550A}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H46</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="43" id="{E30994DE-231B-4B68-996D-3E763907FA3C}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H47</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="41" id="{5729C3FD-9889-4497-A536-FFF0436A57F1}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H48</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="42" id="{40AFAEA4-3FCA-4567-9EEA-1BB8BD606A55}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H49</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="35" id="{893EE127-E4CD-4D52-A058-33508E1A8A65}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H50</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="32" id="{E49E2337-1248-464F-93AA-524E7A88F776}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H51</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="30" id="{D4D8A87E-191B-49BE-8020-6766AF5D5BF4}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H52</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="31" id="{58674D53-21A4-454B-A030-FB1AC98A28E7}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H53</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="24" id="{2B6F2A62-C5BD-445A-8744-A65F0CE63FC7}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H54</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="21" id="{87964D9C-BBDE-4055-86C3-0325D9EE2A04}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H55</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="19" id="{78D85B58-EB6F-4BF5-A949-D6B9FB21DEC9}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H56</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="20" id="{4D437682-03CE-4E4E-AC65-5D0E0945D807}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H57</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{231BF1BC-B7AB-433E-9409-D98755AF356D}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H58</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{968DE5F6-A421-4C85-9FFB-E701ABD18091}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H59</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{54B927FA-810D-48A4-A7FB-8B3F8831820E}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H60</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{1FAD6668-9FA5-4FB1-A02D-65F6CC919842}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H61</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{7DFFAE32-F89E-40E5-BBB3-D2764C6A85A7}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H62</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="187" id="{D6CA9112-E31E-493B-AC44-8CFD7A9AFAFB}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L29:L45</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="45" id="{807675E3-8123-408A-902D-C5F91F09F34C}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L47:L49</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="34" id="{96A2AA7D-5F86-4DB5-9EFC-E3D5A371360F}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L51:L53</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="23" id="{8828D4DD-5476-49CF-88AD-0D99C48FF04B}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L55:L57</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{1799AB56-073C-44A9-976B-79E653DC5E00}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L59:L61</xm:sqref>
+          <xm:sqref>F29:F62</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -7664,793 +5788,735 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7AA4F4-B1FA-4569-9A5C-4430E8288027}">
   <dimension ref="A1:AB30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.125" style="75" customWidth="1"/>
-    <col min="2" max="2" width="18.375" style="78" customWidth="1"/>
-    <col min="3" max="4" width="90.625" style="49" customWidth="1"/>
+    <col min="1" max="1" width="19.125" style="68" customWidth="1"/>
+    <col min="2" max="2" width="7.625" style="85" customWidth="1"/>
+    <col min="3" max="4" width="90.625" style="48" customWidth="1"/>
     <col min="5" max="5" width="9" style="26" customWidth="1"/>
     <col min="6" max="28" width="70" style="26" customWidth="1"/>
     <col min="29" max="16384" width="9" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="76" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="71"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="77" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="54"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="77" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="54"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="77" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="72"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="77" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="54"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="74" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="77" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="55"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="77" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="54"/>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1" s="95" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="95" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+    </row>
+    <row r="2" spans="1:28" s="66" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="80"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+    </row>
+    <row r="3" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
+    </row>
+    <row r="4" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="79"/>
+    </row>
+    <row r="5" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="83"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="78"/>
+    </row>
+    <row r="6" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="82"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="79"/>
+    </row>
+    <row r="7" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="67" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="83"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="78"/>
       <c r="E7" s="40" t="str">
         <f>HYPERLINK("#HealthReport!B30","Retrun")</f>
         <v>Retrun</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="74" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="77" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="54"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="74" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" s="77" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="55"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="74" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="77" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="55"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="74" t="s">
+    <row r="8" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="82"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="79"/>
+    </row>
+    <row r="9" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="83"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="78"/>
+    </row>
+    <row r="10" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="67" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="82"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="79"/>
+    </row>
+    <row r="11" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="83"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="78"/>
+    </row>
+    <row r="12" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="82"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="79"/>
+    </row>
+    <row r="13" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="83"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="78"/>
+    </row>
+    <row r="14" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="82"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="79"/>
+    </row>
+    <row r="15" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="83"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="78"/>
+    </row>
+    <row r="16" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="82"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="79"/>
+    </row>
+    <row r="17" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="77" t="s">
-        <v>147</v>
-      </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="54"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="74" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="77" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="53"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
+      <c r="B17" s="83"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="78"/>
+    </row>
+    <row r="18" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="67" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="82"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="79"/>
+    </row>
+    <row r="19" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="83"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="78"/>
+    </row>
+    <row r="20" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="82"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="79"/>
+    </row>
+    <row r="21" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="67" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="83"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="78"/>
+    </row>
+    <row r="22" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="77" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="72"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="77" t="s">
-        <v>166</v>
-      </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="59"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="74" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="77" t="s">
-        <v>167</v>
-      </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="54"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="77" t="s">
-        <v>168</v>
-      </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="55"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="74" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="54"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="77" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="54"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="74" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="77" t="s">
-        <v>181</v>
-      </c>
-      <c r="C19" s="73"/>
-      <c r="D19" s="55"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="74" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="77" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" s="73"/>
-      <c r="D20" s="55"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="74" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="77" t="s">
-        <v>183</v>
-      </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="55"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="74" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" s="77" t="s">
-        <v>184</v>
-      </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="59"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="77" t="s">
-        <v>149</v>
-      </c>
-      <c r="C23" s="73"/>
-      <c r="D23" s="54"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="74" t="s">
-        <v>169</v>
-      </c>
-      <c r="B24" s="77" t="s">
-        <v>170</v>
-      </c>
-      <c r="C24" s="73"/>
-      <c r="D24" s="55"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="74" t="s">
-        <v>171</v>
-      </c>
-      <c r="B25" s="77" t="s">
-        <v>172</v>
-      </c>
-      <c r="C25" s="73"/>
-      <c r="D25" s="54"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="74" t="s">
-        <v>173</v>
-      </c>
-      <c r="B26" s="77" t="s">
-        <v>174</v>
-      </c>
-      <c r="C26" s="73"/>
-      <c r="D26" s="54"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="74" t="s">
-        <v>185</v>
-      </c>
-      <c r="B27" s="77" t="s">
-        <v>175</v>
-      </c>
-      <c r="C27" s="73"/>
-      <c r="D27" s="55"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="74" t="s">
-        <v>186</v>
-      </c>
-      <c r="B28" s="77" t="s">
-        <v>177</v>
-      </c>
-      <c r="C28" s="73"/>
-      <c r="D28" s="55"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="74" t="s">
-        <v>187</v>
-      </c>
-      <c r="B29" s="77" t="s">
-        <v>178</v>
-      </c>
-      <c r="C29" s="73"/>
-      <c r="D29" s="55"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="74" t="s">
-        <v>188</v>
-      </c>
-      <c r="B30" s="77" t="s">
-        <v>189</v>
-      </c>
-      <c r="C30" s="54"/>
-      <c r="D30" s="55"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="79"/>
+    </row>
+    <row r="23" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="83"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="78"/>
+    </row>
+    <row r="24" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="67" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="82"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="79"/>
+    </row>
+    <row r="25" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="83"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="78"/>
+    </row>
+    <row r="26" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="82"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="79"/>
+    </row>
+    <row r="27" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="83"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="78"/>
+    </row>
+    <row r="28" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="82"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="79"/>
+    </row>
+    <row r="29" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="67" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="83"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="78"/>
+    </row>
+    <row r="30" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="84"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="72"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="吞吞吐吐他" sqref="B16:C16" xr:uid="{AAAA7C2D-0252-42F0-9FBA-2F1C8A993A03}"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{D97E0F2E-7D04-46E3-B6D0-66B86A3C3DF0}">
+            <x14:iconSet iconSet="4Rating" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>5</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>8</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>10</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Flags" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>B2:B30</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965D7FAC-338D-40AE-9A03-D56E1C0E6070}">
-  <dimension ref="A1:AB45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AB48"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="75" customWidth="1"/>
-    <col min="2" max="2" width="20" style="80" customWidth="1"/>
-    <col min="3" max="4" width="90.625" style="49" customWidth="1"/>
+    <col min="1" max="1" width="19.25" style="68" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.625" style="86" customWidth="1"/>
+    <col min="3" max="4" width="90.625" style="48" customWidth="1"/>
     <col min="5" max="27" width="87.5" style="26" customWidth="1"/>
     <col min="28" max="16384" width="9" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="79" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="53"/>
+      <c r="A1" s="95" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="95" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
       <c r="AB1" s="26"/>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+    <row r="2" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="80"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="49"/>
+    </row>
+    <row r="3" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="67" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
+      <c r="AB3" s="26"/>
+    </row>
+    <row r="4" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="67" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="79"/>
+    </row>
+    <row r="5" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="83"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="78"/>
+    </row>
+    <row r="6" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="82"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="79"/>
+    </row>
+    <row r="7" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="83"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="78"/>
+    </row>
+    <row r="8" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="82"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="79"/>
+    </row>
+    <row r="9" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="67" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="83"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="78"/>
+    </row>
+    <row r="10" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="82"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="79"/>
+    </row>
+    <row r="11" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="83"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="78"/>
+    </row>
+    <row r="12" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="67" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="82"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="79"/>
+    </row>
+    <row r="13" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="67" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="83"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="78"/>
+    </row>
+    <row r="14" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="82"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="79"/>
+    </row>
+    <row r="15" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="83"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="78"/>
+    </row>
+    <row r="16" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="82"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="79"/>
+    </row>
+    <row r="17" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="83"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="78"/>
+    </row>
+    <row r="18" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="82"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="79"/>
+    </row>
+    <row r="19" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="83"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="78"/>
+    </row>
+    <row r="20" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="76" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="54"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="77" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="55"/>
-      <c r="AB3" s="26"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="76" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="55"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="76" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="55"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="76" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="55"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="76" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="55"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="74" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="76" t="s">
-        <v>238</v>
-      </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="55"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="74" t="s">
-        <v>205</v>
-      </c>
-      <c r="B9" s="76" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="55"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="74" t="s">
-        <v>206</v>
-      </c>
-      <c r="B10" s="76" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="55"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="74" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="76" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="55"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="76" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="55"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="76" t="s">
+      <c r="B20" s="82"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="79"/>
+    </row>
+    <row r="21" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="83"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="78"/>
+    </row>
+    <row r="22" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="67" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="82"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="79"/>
+    </row>
+    <row r="23" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="83"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="78"/>
+    </row>
+    <row r="24" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="55"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="74" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="76" t="s">
+      <c r="B24" s="82"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="79"/>
+    </row>
+    <row r="25" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="55"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="76" t="s">
+      <c r="B25" s="83"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="78"/>
+    </row>
+    <row r="26" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="55"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="76" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="55"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="76" t="s">
+      <c r="B26" s="82"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="79"/>
+    </row>
+    <row r="27" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="83"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="78"/>
+    </row>
+    <row r="28" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="82"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="79"/>
+    </row>
+    <row r="29" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="55"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" s="76" t="s">
+      <c r="B29" s="83"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="78"/>
+    </row>
+    <row r="30" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="67" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="82"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="79"/>
+    </row>
+    <row r="31" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A31" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="55"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="76" t="s">
-        <v>209</v>
-      </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="55"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="76" t="s">
+      <c r="B31" s="83"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="78"/>
+    </row>
+    <row r="32" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="55"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="74" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="76" t="s">
-        <v>210</v>
-      </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="55"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="79" t="s">
-        <v>213</v>
-      </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="55"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="74" t="s">
+      <c r="B32" s="82"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="79"/>
+    </row>
+    <row r="33" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="83"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="78"/>
+    </row>
+    <row r="34" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A34" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="82"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="79"/>
+    </row>
+    <row r="35" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="83"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="78"/>
+    </row>
+    <row r="36" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="82"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="79"/>
+    </row>
+    <row r="37" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A37" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="83"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="78"/>
+    </row>
+    <row r="38" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="82"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="79"/>
+    </row>
+    <row r="39" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A39" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="83"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="78"/>
+    </row>
+    <row r="40" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A40" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="82"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="79"/>
+    </row>
+    <row r="41" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A41" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="83"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="78"/>
+    </row>
+    <row r="42" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A42" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="82"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="79"/>
+    </row>
+    <row r="43" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A43" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" s="83"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="78"/>
+    </row>
+    <row r="44" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A44" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="79" t="s">
-        <v>211</v>
-      </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="55"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="79" t="s">
-        <v>212</v>
-      </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="55"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="74" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" s="79" t="s">
-        <v>214</v>
-      </c>
-      <c r="C25" s="52"/>
-      <c r="D25" s="55"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="74" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="79" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="55"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="74" t="s">
-        <v>88</v>
-      </c>
-      <c r="B27" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="55"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="74" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" s="79" t="s">
-        <v>126</v>
-      </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="55"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="74" t="s">
-        <v>93</v>
-      </c>
-      <c r="B29" s="79" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" s="52"/>
-      <c r="D29" s="55"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="74" t="s">
-        <v>94</v>
-      </c>
-      <c r="B30" s="79" t="s">
-        <v>215</v>
-      </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="55"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="79" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" s="52"/>
-      <c r="D31" s="55"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="74" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="79" t="s">
-        <v>129</v>
-      </c>
-      <c r="C32" s="52"/>
-      <c r="D32" s="55"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="79" t="s">
-        <v>130</v>
-      </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="55"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="74" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="79" t="s">
+      <c r="B44" s="82"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="79"/>
+    </row>
+    <row r="45" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A45" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="52"/>
-      <c r="D34" s="55"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="74" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="79" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" s="52"/>
-      <c r="D35" s="55"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="74" t="s">
-        <v>99</v>
-      </c>
-      <c r="B36" s="79" t="s">
-        <v>244</v>
-      </c>
-      <c r="C36" s="52"/>
-      <c r="D36" s="55"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="74" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" s="79" t="s">
-        <v>133</v>
-      </c>
-      <c r="C37" s="52"/>
-      <c r="D37" s="55"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="79" t="s">
-        <v>134</v>
-      </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="55"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="74" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" s="79" t="s">
-        <v>135</v>
-      </c>
-      <c r="C39" s="52"/>
-      <c r="D39" s="55"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="74" t="s">
-        <v>217</v>
-      </c>
-      <c r="B40" s="79" t="s">
-        <v>216</v>
-      </c>
-      <c r="C40" s="52"/>
-      <c r="D40" s="55"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="74" t="s">
-        <v>227</v>
-      </c>
-      <c r="B41" s="79" t="s">
-        <v>226</v>
-      </c>
-      <c r="C41" s="50"/>
-      <c r="D41" s="53"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="74" t="s">
-        <v>218</v>
-      </c>
-      <c r="B42" s="79" t="s">
-        <v>225</v>
-      </c>
-      <c r="C42" s="56"/>
-      <c r="D42" s="57"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="74" t="s">
-        <v>219</v>
-      </c>
-      <c r="B43" s="79" t="s">
-        <v>224</v>
-      </c>
-      <c r="C43" s="52"/>
-      <c r="D43" s="55"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="74" t="s">
-        <v>220</v>
-      </c>
-      <c r="B44" s="79" t="s">
-        <v>223</v>
-      </c>
-      <c r="C44" s="50"/>
-      <c r="D44" s="53"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="74" t="s">
-        <v>221</v>
-      </c>
-      <c r="B45" s="79" t="s">
-        <v>222</v>
-      </c>
-      <c r="C45" s="56"/>
-      <c r="D45" s="57"/>
+      <c r="B45" s="84"/>
+      <c r="C45" s="73"/>
+      <c r="D45" s="72"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C48" s="70"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{EAAF7DD6-57C5-427F-BD84-B7CA83805024}">
+            <x14:iconSet iconSet="4Rating" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>5</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>8</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>10</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Flags" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>B2:B45</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -8459,20 +6525,20 @@
   <dimension ref="A1:AB20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.125" style="81" customWidth="1"/>
-    <col min="2" max="2" width="15.625" customWidth="1"/>
-    <col min="3" max="4" width="102.625" style="48" customWidth="1"/>
+    <col min="1" max="1" width="17.25" style="69" customWidth="1"/>
+    <col min="2" max="2" width="7.625" style="87" customWidth="1"/>
+    <col min="3" max="4" width="102.625" style="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="54"/>
+    <row r="1" spans="1:28" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="95" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="95" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
       <c r="E1" s="26"/>
       <c r="F1" s="26"/>
       <c r="G1" s="26"/>
@@ -8498,75 +6564,61 @@
       <c r="AA1" s="26"/>
       <c r="AB1" s="26"/>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="59"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="59"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="59"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
-        <v>161</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="59"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="74" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="59"/>
-    </row>
-    <row r="7" spans="1:28" ht="27" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="59"/>
-    </row>
-    <row r="8" spans="1:28" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="59"/>
+    <row r="2" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="75"/>
+    </row>
+    <row r="3" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="82"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="79"/>
+    </row>
+    <row r="4" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="83"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="78"/>
+    </row>
+    <row r="5" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="82"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="79"/>
+    </row>
+    <row r="6" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="83"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="78"/>
+    </row>
+    <row r="7" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="82"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="79"/>
+    </row>
+    <row r="8" spans="1:28" s="27" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="83"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="78"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
@@ -8591,65 +6643,53 @@
       <c r="Z8" s="26"/>
       <c r="AA8" s="26"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="74" t="s">
-        <v>151</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="59"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="74" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="59"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="74" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="59"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="74" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="59"/>
-    </row>
-    <row r="13" spans="1:28" ht="27" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
-    </row>
-    <row r="14" spans="1:28" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="76" t="s">
-        <v>239</v>
-      </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="55"/>
+    <row r="9" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="82"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="79"/>
+    </row>
+    <row r="10" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="83"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="78"/>
+    </row>
+    <row r="11" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="82"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="79"/>
+    </row>
+    <row r="12" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="83"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="78"/>
+    </row>
+    <row r="13" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="82"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="79"/>
+    </row>
+    <row r="14" spans="1:28" s="27" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="83"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="78"/>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
@@ -8674,25 +6714,21 @@
       <c r="Z14" s="26"/>
       <c r="AA14" s="26"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="74" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-    </row>
-    <row r="16" spans="1:28" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="74" t="s">
-        <v>240</v>
-      </c>
-      <c r="B16" s="79" t="s">
-        <v>242</v>
-      </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="55"/>
+    <row r="15" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="82"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="79"/>
+    </row>
+    <row r="16" spans="1:28" s="27" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="67" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="83"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="78"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
@@ -8717,15 +6753,13 @@
       <c r="Z16" s="26"/>
       <c r="AA16" s="26"/>
     </row>
-    <row r="17" spans="1:27" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="74" t="s">
-        <v>241</v>
-      </c>
-      <c r="B17" s="79" t="s">
-        <v>243</v>
-      </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="55"/>
+    <row r="17" spans="1:27" s="27" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="82"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="79"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
@@ -8750,25 +6784,21 @@
       <c r="Z17" s="26"/>
       <c r="AA17" s="26"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="74" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61"/>
-    </row>
-    <row r="19" spans="1:27" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="74" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="55"/>
+    <row r="18" spans="1:27" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="67" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="83"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="78"/>
+    </row>
+    <row r="19" spans="1:27" s="27" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="67" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="82"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="79"/>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
@@ -8793,15 +6823,13 @@
       <c r="Z19" s="26"/>
       <c r="AA19" s="26"/>
     </row>
-    <row r="20" spans="1:27" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="74" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="55"/>
+    <row r="20" spans="1:27" s="27" customFormat="1" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="84"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="72"/>
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
@@ -8829,10 +6857,68 @@
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{95F920C0-AED7-425E-818E-31788AE47CF5}">
+            <x14:iconSet iconSet="4Rating" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>5</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>8</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>10</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="3Flags" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="1"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>B2:B20</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac37c1753acd5e330d2062ccec26ea66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b340c7101c92c5120abd06486f94548" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9132,36 +7218,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1BB4A4-C009-44B7-9F89-7FA7A7BF749B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D4997A-F5D7-47B8-8021-08C076C5E1C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98E7F3D6-785F-49FE-8501-BF769B99AE88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9182,26 +7259,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D4997A-F5D7-47B8-8021-08C076C5E1C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1BB4A4-C009-44B7-9F89-7FA7A7BF749B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>